--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ub/code/fran/configurations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D7675F-84FF-784D-9B2C-E602FF1CC65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79EE3122-21D2-4245-B718-F7F06D1198A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20160" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29600" windowHeight="17600" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="model_params" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="198">
   <si>
     <t>var_name</t>
   </si>
@@ -478,6 +478,9 @@
     <t>use_fg_indices</t>
   </si>
   <si>
+    <t>nnz_allowed</t>
+  </si>
+  <si>
     <t>plan_valid</t>
   </si>
   <si>
@@ -511,13 +514,13 @@
     <t>0.8,.8,1.5</t>
   </si>
   <si>
-    <t>$cold_storage_folder/predictions/totalseg/LITS-1088</t>
+    <t>$cold_storage_folder/predictions/totalseg/LITS-1439</t>
   </si>
   <si>
     <t>lbd</t>
   </si>
   <si>
-    <t>TSL.all,TSL.all</t>
+    <t>TSL.label_localiser:TSL.label_localiser,TSL.label_localiser:TSL.label_localiser</t>
   </si>
   <si>
     <t>baseline</t>
@@ -526,6 +529,9 @@
     <t>plan1</t>
   </si>
   <si>
+    <t>TSL.label_localiser:TSL.label_localiser,TSL.label_localiser:TSL.localiser</t>
+  </si>
+  <si>
     <t>liver</t>
   </si>
   <si>
@@ -541,15 +547,12 @@
     <t>0.8,0.8,1.5</t>
   </si>
   <si>
-    <t>patch</t>
+    <t>pbd</t>
   </si>
   <si>
     <t>plan4</t>
   </si>
   <si>
-    <t>pbd</t>
-  </si>
-  <si>
     <t>LITS-860</t>
   </si>
   <si>
@@ -568,10 +571,7 @@
     <t>lidc</t>
   </si>
   <si>
-    <t>$cold_storage_folder/predictions/totalseg/LITS-1439</t>
-  </si>
-  <si>
-    <t>TSL.label_localiser,TSL.lungs</t>
+    <t>TSL.label_localiser:TSL.lungs</t>
   </si>
   <si>
     <t>totalseg</t>
@@ -580,7 +580,7 @@
     <t>whole</t>
   </si>
   <si>
-    <t>TSL.all,TSL.label_localiser</t>
+    <t>TSL.label_full:TSL.label_localiser</t>
   </si>
   <si>
     <t>1.5, 1.5,1.5</t>
@@ -592,7 +592,7 @@
     <t>1,1,1</t>
   </si>
   <si>
-    <t>TSL.all,TSL.label_minimal</t>
+    <t>TSL.label_full:TSL.label_minimal</t>
   </si>
   <si>
     <t>192</t>
@@ -604,7 +604,7 @@
     <t>uls23_bone</t>
   </si>
   <si>
-    <t>sourcepatch</t>
+    <t>sourcepbd</t>
   </si>
   <si>
     <t>colon</t>
@@ -613,13 +613,28 @@
     <t>colonmsd10</t>
   </si>
   <si>
-    <t>TSL.label_localiser,TSL.gi</t>
+    <t>TSL.label_localiser:TSL.gi</t>
   </si>
   <si>
     <t>pancreas</t>
   </si>
   <si>
-    <t>pancreasmsd07</t>
+    <t>pancreasmsd07, curvaspdac</t>
+  </si>
+  <si>
+    <t>DS.pancreasmsd07/lms,$cold_storage_folder/predictions/totalseg/LITS-1437</t>
+  </si>
+  <si>
+    <t>{1:0,2:1},None</t>
+  </si>
+  <si>
+    <t>{1:3},TSL.label_minimal: TSL.pancreas</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>drli_short, litsmc</t>
   </si>
 </sst>
 </file>
@@ -639,6 +654,7 @@
       <sz val="11"/>
       <name val="Cambria"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -676,11 +692,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -947,8 +964,8 @@
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>1E-3</v>
+      <c r="E3" s="2">
+        <v>0.01</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
@@ -1815,26 +1832,29 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:AE31"/>
+  <dimension ref="A1:AF33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="25.5" customWidth="1"/>
     <col min="4" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="36.6640625" customWidth="1"/>
-    <col min="7" max="12" width="8.6640625" customWidth="1"/>
-    <col min="13" max="16" width="20.5" customWidth="1"/>
+    <col min="6" max="6" width="64.6640625" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" customWidth="1"/>
+    <col min="8" max="8" width="24.5" customWidth="1"/>
+    <col min="9" max="12" width="8.6640625" customWidth="1"/>
+    <col min="13" max="15" width="20.5" customWidth="1"/>
+    <col min="16" max="16" width="34.5" customWidth="1"/>
     <col min="17" max="17" width="24.83203125" customWidth="1"/>
     <col min="18" max="18" width="8.6640625" customWidth="1"/>
     <col min="19" max="19" width="15" customWidth="1"/>
     <col min="20" max="20" width="13.1640625" customWidth="1"/>
     <col min="21" max="21" width="13.83203125" customWidth="1"/>
     <col min="22" max="22" width="22.1640625" customWidth="1"/>
-    <col min="23" max="31" width="8.6640625" customWidth="1"/>
+    <col min="23" max="32" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>125</v>
       </c>
@@ -1911,54 +1931,57 @@
         <v>147</v>
       </c>
       <c r="Z1" t="s">
+        <v>148</v>
+      </c>
+      <c r="AA1" t="s">
         <v>4</v>
       </c>
-      <c r="AA1" t="s">
-        <v>1</v>
-      </c>
       <c r="AB1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC1" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>3</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AE1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AF1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
       </c>
       <c r="I2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="R2" t="s">
         <v>49</v>
       </c>
       <c r="T2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U2" t="s">
         <v>4</v>
@@ -1967,46 +1990,50 @@
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W2" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D3" t="s">
         <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H3" t="s">
         <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="R3" t="s">
         <v>49</v>
       </c>
       <c r="T3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U3" t="s">
         <v>4</v>
@@ -2015,40 +2042,44 @@
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W3" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D4" t="s">
         <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="R4" t="s">
         <v>20</v>
       </c>
       <c r="S4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="T4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U4" t="s">
         <v>4</v>
@@ -2057,34 +2088,38 @@
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W4" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="T5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U5" t="s">
         <v>4</v>
@@ -2093,37 +2128,41 @@
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W5" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D6" t="s">
         <v>34</v>
       </c>
       <c r="I6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J6">
         <v>192</v>
       </c>
       <c r="K6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="R6" t="s">
         <v>49</v>
       </c>
       <c r="T6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U6" t="s">
         <v>4</v>
@@ -2132,43 +2171,47 @@
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W6" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D7">
         <v>50</v>
       </c>
       <c r="F7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P7" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="R7">
         <v>2</v>
       </c>
       <c r="T7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U7" t="s">
         <v>4</v>
@@ -2177,43 +2220,47 @@
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B8">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D8">
         <v>50</v>
       </c>
       <c r="F8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J8">
         <v>192</v>
       </c>
       <c r="K8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="R8">
         <v>2</v>
       </c>
       <c r="T8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U8" t="s">
         <v>4</v>
@@ -2222,43 +2269,47 @@
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W8" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B9">
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D9">
         <v>75</v>
       </c>
       <c r="F9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J9">
         <v>192</v>
       </c>
       <c r="K9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P9" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="R9">
         <v>2</v>
       </c>
       <c r="T9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U9" t="s">
         <v>4</v>
@@ -2267,307 +2318,347 @@
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W9" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
       </c>
       <c r="I10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R10" t="s">
         <v>49</v>
       </c>
       <c r="T10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V10" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W10" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B11">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R11" t="s">
         <v>49</v>
       </c>
       <c r="T11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V11" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W11" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B12">
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R12" t="s">
         <v>49</v>
       </c>
       <c r="T12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="V12" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W12" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B13">
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="R13" t="s">
         <v>20</v>
       </c>
       <c r="S13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="T13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V13" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W13" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B14">
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I14" t="s">
         <v>168</v>
       </c>
       <c r="J14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R14" t="s">
         <v>49</v>
       </c>
       <c r="T14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V14" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y14" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W14" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B15">
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R15" t="s">
         <v>49</v>
       </c>
       <c r="T15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V15" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W15" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B16">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="R16" t="s">
         <v>20</v>
       </c>
       <c r="S16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="V16" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W16" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B17">
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D17" t="s">
         <v>34</v>
       </c>
       <c r="I17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R17" t="s">
         <v>49</v>
       </c>
       <c r="T17" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="V17" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W17" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B18">
         <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D18" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E18" t="s">
         <v>20</v>
       </c>
       <c r="I18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R18" t="s">
         <v>20</v>
       </c>
       <c r="T18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V18" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W18" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D19">
         <v>40</v>
@@ -2576,50 +2667,54 @@
         <v>20</v>
       </c>
       <c r="I19" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="T19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V19" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W19" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D20" t="s">
         <v>34</v>
       </c>
       <c r="F20" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="H20" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P20" t="s">
         <v>176</v>
@@ -2628,7 +2723,7 @@
         <v>49</v>
       </c>
       <c r="T20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U20" t="s">
         <v>4</v>
@@ -2637,38 +2732,42 @@
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W20" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D21">
         <v>50</v>
       </c>
       <c r="F21" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="H21" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L21" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P21" t="s">
         <v>176</v>
@@ -2677,7 +2776,7 @@
         <v>49</v>
       </c>
       <c r="T21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U21" t="s">
         <v>4</v>
@@ -2686,8 +2785,12 @@
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W21" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>177</v>
       </c>
@@ -2701,16 +2804,16 @@
         <v>34</v>
       </c>
       <c r="I22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="T22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U22" t="s">
         <v>4</v>
@@ -2719,11 +2822,15 @@
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="AE22">
+      <c r="W22" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AF22">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>177</v>
       </c>
@@ -2740,16 +2847,16 @@
         <v>178</v>
       </c>
       <c r="J23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O23" t="s">
         <v>179</v>
       </c>
       <c r="S23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="U23" t="s">
         <v>4</v>
@@ -2758,11 +2865,15 @@
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W23" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>177</v>
       </c>
@@ -2776,13 +2887,13 @@
         <v>34</v>
       </c>
       <c r="I24" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R24" t="s">
         <v>49</v>
@@ -2797,11 +2908,15 @@
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="AE24">
+      <c r="W24" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AF24">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>177</v>
       </c>
@@ -2815,13 +2930,13 @@
         <v>181</v>
       </c>
       <c r="I25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J25" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K25" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R25" t="s">
         <v>49</v>
@@ -2836,11 +2951,15 @@
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="AE25">
+      <c r="W25" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AF25">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>177</v>
       </c>
@@ -2854,13 +2973,13 @@
         <v>181</v>
       </c>
       <c r="I26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J26" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N26" t="s">
         <v>183</v>
@@ -2878,11 +2997,15 @@
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="AE26">
+      <c r="W26" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AF26">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>177</v>
       </c>
@@ -2896,13 +3019,13 @@
         <v>181</v>
       </c>
       <c r="I27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J27" t="s">
         <v>184</v>
       </c>
       <c r="K27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M27" t="s">
         <v>183</v>
@@ -2920,11 +3043,15 @@
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="AE27">
+      <c r="W27" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AF27">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>185</v>
       </c>
@@ -2941,10 +3068,10 @@
         <v>187</v>
       </c>
       <c r="J28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R28" t="s">
         <v>49</v>
@@ -2959,11 +3086,15 @@
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y28" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W28" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>188</v>
       </c>
@@ -2977,23 +3108,23 @@
         <v>50</v>
       </c>
       <c r="F29" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="H29" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L29" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P29" t="s">
         <v>190</v>
@@ -3002,7 +3133,7 @@
         <v>49</v>
       </c>
       <c r="T29" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U29" t="s">
         <v>4</v>
@@ -3011,8 +3142,12 @@
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W29" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>188</v>
       </c>
@@ -3026,23 +3161,23 @@
         <v>50</v>
       </c>
       <c r="F30" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="H30" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J30">
         <v>192</v>
       </c>
       <c r="K30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L30" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P30" t="s">
         <v>190</v>
@@ -3051,7 +3186,7 @@
         <v>49</v>
       </c>
       <c r="T30" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U30" t="s">
         <v>4</v>
@@ -3060,13 +3195,17 @@
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W30" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>191</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" t="s">
         <v>192</v>
@@ -3074,32 +3213,155 @@
       <c r="D31">
         <v>50</v>
       </c>
+      <c r="F31" t="s">
+        <v>193</v>
+      </c>
       <c r="H31" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J31">
         <v>128</v>
       </c>
       <c r="K31" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L31" t="s">
-        <v>154</v>
+        <v>155</v>
+      </c>
+      <c r="M31" t="s">
+        <v>194</v>
+      </c>
+      <c r="P31" t="s">
+        <v>195</v>
       </c>
       <c r="R31">
         <v>1</v>
       </c>
       <c r="T31" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U31" t="s">
         <v>4</v>
       </c>
       <c r="V31" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="W31" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>191</v>
+      </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32" t="s">
+        <v>192</v>
+      </c>
+      <c r="D32">
+        <v>100</v>
+      </c>
+      <c r="F32" t="s">
+        <v>193</v>
+      </c>
+      <c r="H32" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I32" t="s">
+        <v>158</v>
+      </c>
+      <c r="J32">
+        <v>192</v>
+      </c>
+      <c r="K32" t="s">
+        <v>154</v>
+      </c>
+      <c r="L32" t="s">
+        <v>155</v>
+      </c>
+      <c r="M32" t="s">
+        <v>194</v>
+      </c>
+      <c r="P32" t="s">
+        <v>195</v>
+      </c>
+      <c r="R32">
+        <v>1</v>
+      </c>
+      <c r="T32" t="s">
+        <v>156</v>
+      </c>
+      <c r="U32" t="s">
+        <v>4</v>
+      </c>
+      <c r="V32" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="W32" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>196</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>197</v>
+      </c>
+      <c r="D33" t="s">
+        <v>34</v>
+      </c>
+      <c r="F33" t="s">
+        <v>157</v>
+      </c>
+      <c r="H33" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I33" t="s">
+        <v>158</v>
+      </c>
+      <c r="J33" t="s">
+        <v>153</v>
+      </c>
+      <c r="K33" t="s">
+        <v>154</v>
+      </c>
+      <c r="L33" t="s">
+        <v>155</v>
+      </c>
+      <c r="P33" t="s">
+        <v>176</v>
+      </c>
+      <c r="R33" t="s">
+        <v>49</v>
+      </c>
+      <c r="T33" t="s">
+        <v>156</v>
+      </c>
+      <c r="U33" t="s">
+        <v>4</v>
+      </c>
+      <c r="V33" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="W33" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="203">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -556,6 +556,9 @@
   </si>
   <si>
     <t xml:space="preserve">1, lbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{1:1,2:1,3:1,4:1,5:1}</t>
   </si>
   <si>
     <t xml:space="preserve">totalseg</t>
@@ -722,24 +725,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -938,312 +945,312 @@
   <dimension ref="A1:J17"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="47.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="47.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="20.17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="n">
+      <c r="D3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="D4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="0" t="s">
+      <c r="I5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="0" t="s">
+      <c r="J5" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="0" t="s">
+      <c r="D7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="0" t="s">
+      <c r="D8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="0" t="s">
+      <c r="D9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="0" t="s">
+      <c r="D10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="0" t="s">
+      <c r="D11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="0" t="s">
+      <c r="D12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="0" t="s">
+      <c r="D13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="0" t="s">
+      <c r="D14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="0" t="s">
+      <c r="D15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="0" t="s">
+      <c r="D16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="0" t="s">
+      <c r="D17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1266,190 +1273,190 @@
   <dimension ref="A1:K1048576"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="H6" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I6" s="0" t="s">
+      <c r="I6" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J6" s="0" t="s">
+      <c r="J6" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="K6" s="0" t="s">
+      <c r="K6" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="0" t="s">
+      <c r="D7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I7" s="0" t="s">
+      <c r="I7" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="0" t="s">
+      <c r="D8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="0" t="s">
+      <c r="D9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="1" t="n">
         <v>192</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="1" t="n">
         <v>128</v>
       </c>
     </row>
@@ -1474,220 +1481,220 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0" t="s">
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="0" t="s">
+      <c r="B3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="0" t="s">
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="0" t="s">
+      <c r="B5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="0" t="s">
+      <c r="B6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="0" t="s">
+      <c r="B7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="0" t="s">
+      <c r="B8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="0" t="s">
+      <c r="B9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1711,101 +1718,101 @@
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="0" t="s">
+      <c r="D3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1829,71 +1836,71 @@
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1913,1810 +1920,1860 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AF38"/>
+  <dimension ref="A1:AF39"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="25.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="0" width="20.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="41.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="24.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="13.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="13.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="22.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="23" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="25.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="40.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="1" width="20.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="41.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="24.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="13.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="13.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="22.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="23" style="1" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="R1" s="0" t="s">
+      <c r="R1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="S1" s="0" t="s">
+      <c r="S1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="T1" s="0" t="s">
+      <c r="T1" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="U1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="V1" s="0" t="s">
+      <c r="U1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="W1" s="0" t="s">
+      <c r="W1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="X1" s="0" t="s">
+      <c r="X1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="Y1" s="0" t="s">
+      <c r="Y1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="Z1" s="0" t="s">
+      <c r="Z1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AA1" s="0" t="s">
+      <c r="AA1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AB1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC1" s="0" t="s">
+      <c r="AB1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AD1" s="0" t="s">
+      <c r="AD1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="AE1" s="0" t="s">
+      <c r="AE1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="0" t="s">
+      <c r="AF1" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0" t="s">
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M2" s="0" t="s">
+      <c r="M2" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="S2" s="0" t="s">
+      <c r="S2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T2" s="0" t="s">
+      <c r="T2" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="U2" s="0" t="s">
+      <c r="U2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V2" s="4" t="b">
+      <c r="V2" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W2" s="4" t="b">
+      <c r="W2" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="K3" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L3" s="0" t="s">
+      <c r="L3" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M3" s="0" t="s">
+      <c r="M3" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="Q3" s="0" t="s">
+      <c r="Q3" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="S3" s="0" t="s">
+      <c r="S3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T3" s="0" t="s">
+      <c r="T3" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="U3" s="0" t="s">
+      <c r="U3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V3" s="4" t="b">
+      <c r="V3" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W3" s="4" t="b">
+      <c r="W3" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="0" t="s">
+      <c r="I4" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J4" s="0" t="s">
+      <c r="J4" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="K4" s="0" t="s">
+      <c r="K4" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L4" s="0" t="s">
+      <c r="L4" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M4" s="0" t="s">
+      <c r="M4" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="S4" s="0" t="s">
+      <c r="S4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T4" s="0" t="s">
+      <c r="T4" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="U4" s="0" t="s">
+      <c r="U4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V4" s="4" t="b">
+      <c r="V4" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W4" s="4" t="b">
+      <c r="W4" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="0" t="s">
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K5" s="0" t="s">
+      <c r="K5" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L5" s="0" t="s">
+      <c r="L5" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M5" s="0" t="s">
+      <c r="M5" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="T5" s="0" t="s">
+      <c r="T5" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="U5" s="0" t="s">
+      <c r="U5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V5" s="4" t="b">
+      <c r="V5" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W5" s="4" t="b">
+      <c r="W5" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="0" t="s">
+      <c r="I6" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="L6" s="0" t="s">
+      <c r="L6" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M6" s="0" t="s">
+      <c r="M6" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="S6" s="0" t="s">
+      <c r="S6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T6" s="0" t="s">
+      <c r="T6" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="U6" s="0" t="s">
+      <c r="U6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V6" s="4" t="b">
+      <c r="V6" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W6" s="4" t="b">
+      <c r="W6" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="I7" s="0" t="s">
+      <c r="I7" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K7" s="0" t="s">
+      <c r="K7" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L7" s="0" t="s">
+      <c r="L7" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M7" s="0" t="s">
+      <c r="M7" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="Q7" s="0" t="s">
+      <c r="Q7" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="S7" s="0" t="n">
+      <c r="S7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="T7" s="0" t="s">
+      <c r="T7" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="U7" s="0" t="s">
+      <c r="U7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V7" s="4" t="b">
+      <c r="V7" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W7" s="4" t="b">
+      <c r="W7" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="I8" s="0" t="s">
+      <c r="I8" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="K8" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="L8" s="0" t="s">
+      <c r="L8" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M8" s="0" t="s">
+      <c r="M8" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="Q8" s="0" t="s">
+      <c r="Q8" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="S8" s="0" t="n">
+      <c r="S8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="T8" s="0" t="s">
+      <c r="T8" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="U8" s="0" t="s">
+      <c r="U8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V8" s="4" t="b">
+      <c r="V8" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W8" s="4" t="b">
+      <c r="W8" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="I9" s="0" t="s">
+      <c r="I9" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K9" s="0" t="n">
+      <c r="K9" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="L9" s="0" t="s">
+      <c r="L9" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M9" s="0" t="s">
+      <c r="M9" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="Q9" s="0" t="s">
+      <c r="Q9" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="S9" s="0" t="n">
+      <c r="S9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="T9" s="0" t="s">
+      <c r="T9" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="U9" s="0" t="s">
+      <c r="U9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V9" s="4" t="b">
+      <c r="V9" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W9" s="4" t="b">
+      <c r="W9" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="0" t="s">
+      <c r="B10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="0" t="s">
+      <c r="I10" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K10" s="0" t="s">
+      <c r="K10" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L10" s="0" t="s">
+      <c r="L10" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="S10" s="0" t="s">
+      <c r="S10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T10" s="0" t="s">
+      <c r="T10" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="V10" s="4" t="b">
+      <c r="V10" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W10" s="4" t="b">
+      <c r="W10" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="I11" s="0" t="s">
+      <c r="I11" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="K11" s="0" t="s">
+      <c r="K11" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L11" s="0" t="s">
+      <c r="L11" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="S11" s="0" t="s">
+      <c r="S11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T11" s="0" t="s">
+      <c r="T11" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="V11" s="4" t="b">
+      <c r="V11" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W11" s="4" t="b">
+      <c r="W11" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="I12" s="0" t="s">
+      <c r="I12" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K12" s="0" t="s">
+      <c r="K12" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L12" s="0" t="s">
+      <c r="L12" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="S12" s="0" t="s">
+      <c r="S12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T12" s="0" t="s">
+      <c r="T12" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="V12" s="4" t="b">
+      <c r="V12" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W12" s="4" t="b">
+      <c r="W12" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="I13" s="0" t="s">
+      <c r="I13" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J13" s="0" t="s">
+      <c r="J13" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="M13" s="0" t="s">
+      <c r="M13" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="S13" s="0" t="s">
+      <c r="S13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T13" s="0" t="s">
+      <c r="T13" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="V13" s="4" t="b">
+      <c r="V13" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W13" s="4" t="b">
+      <c r="W13" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="I14" s="0" t="s">
+      <c r="I14" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="K14" s="0" t="s">
+      <c r="K14" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L14" s="0" t="s">
+      <c r="L14" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="S14" s="0" t="s">
+      <c r="S14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T14" s="0" t="s">
+      <c r="T14" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="V14" s="4" t="b">
+      <c r="V14" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W14" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z14" s="0" t="s">
+      <c r="W14" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="1" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="I15" s="0" t="s">
+      <c r="I15" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K15" s="0" t="s">
+      <c r="K15" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L15" s="0" t="s">
+      <c r="L15" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="S15" s="0" t="s">
+      <c r="S15" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T15" s="0" t="s">
+      <c r="T15" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="V15" s="4" t="b">
+      <c r="V15" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W15" s="4" t="b">
+      <c r="W15" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="I16" s="0" t="s">
+      <c r="I16" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J16" s="0" t="n">
+      <c r="J16" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="S16" s="0" t="s">
+      <c r="S16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V16" s="4" t="b">
+      <c r="V16" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W16" s="4" t="b">
+      <c r="W16" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I17" s="0" t="s">
+      <c r="I17" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K17" s="0" t="s">
+      <c r="K17" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="L17" s="0" t="s">
+      <c r="L17" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="S17" s="0" t="s">
+      <c r="S17" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T17" s="0" t="s">
+      <c r="T17" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="V17" s="4" t="b">
+      <c r="V17" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W17" s="4" t="b">
+      <c r="W17" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="0" t="s">
+      <c r="I18" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K18" s="0" t="s">
+      <c r="K18" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L18" s="0" t="s">
+      <c r="L18" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="S18" s="0" t="s">
+      <c r="S18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T18" s="0" t="s">
+      <c r="T18" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="V18" s="4" t="b">
+      <c r="V18" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W18" s="4" t="b">
+      <c r="W18" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D19" s="0" t="n">
+      <c r="D19" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="0" t="s">
+      <c r="I19" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M19" s="0" t="s">
+      <c r="M19" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="T19" s="0" t="s">
+      <c r="T19" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="V19" s="4" t="b">
+      <c r="V19" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W19" s="4" t="b">
+      <c r="W19" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B20" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="0" t="s">
+      <c r="B20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H20" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="0" t="s">
+      <c r="H20" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K20" s="0" t="s">
+      <c r="K20" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L20" s="0" t="s">
+      <c r="L20" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M20" s="0" t="s">
+      <c r="M20" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="Q20" s="0" t="s">
+      <c r="Q20" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="S20" s="0" t="s">
+      <c r="S20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T20" s="0" t="s">
+      <c r="T20" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="U20" s="0" t="s">
+      <c r="U20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V20" s="4" t="b">
+      <c r="V20" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W20" s="4" t="b">
+      <c r="W20" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D21" s="0" t="n">
+      <c r="D21" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H21" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="0" t="s">
+      <c r="H21" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K21" s="0" t="s">
+      <c r="K21" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L21" s="0" t="s">
+      <c r="L21" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M21" s="0" t="s">
+      <c r="M21" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="Q21" s="0" t="s">
+      <c r="Q21" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="S21" s="0" t="s">
+      <c r="S21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T21" s="0" t="s">
+      <c r="T21" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="U21" s="0" t="s">
+      <c r="U21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V21" s="4" t="b">
+      <c r="V21" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W21" s="4" t="b">
+      <c r="W21" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D22" s="0" t="n">
+      <c r="D22" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H22" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="0" t="s">
+      <c r="H22" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K22" s="0" t="s">
+      <c r="K22" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L22" s="0" t="s">
+      <c r="L22" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M22" s="0" t="s">
+      <c r="M22" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="O22" s="0" t="s">
+      <c r="O22" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="Q22" s="0" t="s">
+      <c r="Q22" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="S22" s="0" t="s">
+      <c r="S22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T22" s="0" t="s">
+      <c r="T22" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="U22" s="0" t="s">
+      <c r="U22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V22" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="W22" s="4" t="b">
+      <c r="V22" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="W22" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D23" s="0" t="n">
+      <c r="D23" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H23" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="0" t="s">
+      <c r="H23" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K23" s="0" t="s">
+      <c r="K23" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L23" s="0" t="s">
+      <c r="L23" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M23" s="0" t="s">
+      <c r="M23" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="O23" s="0" t="s">
+      <c r="O23" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="Q23" s="0" t="s">
+      <c r="Q23" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="S23" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" s="0" t="s">
+      <c r="S23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="U23" s="0" t="s">
+      <c r="U23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V23" s="4" t="b">
+      <c r="V23" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W23" s="4" t="b">
+      <c r="W23" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="H24" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="S24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V24" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="W24" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B25" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D24" s="0" t="n">
+      <c r="D25" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="H24" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="0" t="s">
+      <c r="H25" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J24" s="0" t="s">
+      <c r="J25" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="K24" s="0" t="s">
+      <c r="K25" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L24" s="0" t="s">
+      <c r="L25" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M24" s="0" t="s">
+      <c r="M25" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="O24" s="0" t="s">
+      <c r="O25" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="S24" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" s="0" t="s">
+      <c r="S25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="U24" s="0" t="s">
+      <c r="U25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V24" s="4" t="b">
+      <c r="V25" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W24" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="W25" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B26" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="S26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V26" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="W26" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V27" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="W27" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AF27" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V28" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="W28" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AF28" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V29" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="W29" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AF29" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V30" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="W30" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AF30" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B31" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C25" s="0" t="s">
-        <v>173</v>
-      </c>
-      <c r="D25" s="0" t="n">
+      <c r="C31" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V31" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="W31" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AF31" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V32" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="W32" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AF32" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V33" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="W33" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z33" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D34" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="H25" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="0" t="s">
+      <c r="F34" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H34" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K25" s="0" t="s">
+      <c r="K34" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L25" s="0" t="s">
+      <c r="L34" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M25" s="0" t="s">
+      <c r="M34" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="O25" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="S25" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" s="0" t="s">
+      <c r="Q34" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T34" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="U25" s="0" t="s">
+      <c r="U34" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V25" s="4" t="b">
+      <c r="V34" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W25" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="B26" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="D26" s="0" t="s">
+      <c r="W34" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H35" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V35" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="W35" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H36" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K36" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="S36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V36" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="W36" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H37" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K37" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="S37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V37" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H38" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="S38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="U38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V38" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="W38" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I26" s="0" t="s">
-        <v>152</v>
-      </c>
-      <c r="K26" s="0" t="s">
+      <c r="F39" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H39" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L26" s="0" t="s">
+      <c r="L39" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="T26" s="0" t="s">
+      <c r="M39" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="S39" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T39" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="U26" s="0" t="s">
+      <c r="U39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V26" s="4" t="b">
+      <c r="V39" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W26" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AF26" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="B27" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="D27" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="I27" s="0" t="s">
-        <v>178</v>
-      </c>
-      <c r="J27" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="K27" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="L27" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="P27" s="0" t="s">
-        <v>179</v>
-      </c>
-      <c r="U27" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="V27" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="W27" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AF27" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="B28" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="D28" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="I28" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="K28" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="L28" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="S28" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="T28" s="0" t="s">
-        <v>180</v>
-      </c>
-      <c r="U28" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="V28" s="4" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="W28" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AF28" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="B29" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="D29" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="I29" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="K29" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="L29" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="S29" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="T29" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="U29" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="V29" s="4" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="W29" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AF29" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="B30" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="D30" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="I30" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="K30" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="L30" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="O30" s="0" t="s">
-        <v>183</v>
-      </c>
-      <c r="S30" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="T30" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="U30" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="V30" s="4" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="W30" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AF30" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="B31" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="D31" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="I31" s="0" t="s">
-        <v>152</v>
-      </c>
-      <c r="K31" s="0" t="s">
-        <v>184</v>
-      </c>
-      <c r="L31" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="N31" s="0" t="s">
-        <v>183</v>
-      </c>
-      <c r="S31" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="T31" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="U31" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="V31" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="W31" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AF31" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>185</v>
-      </c>
-      <c r="B32" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="0" t="s">
-        <v>186</v>
-      </c>
-      <c r="D32" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="I32" s="0" t="s">
-        <v>187</v>
-      </c>
-      <c r="K32" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="L32" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="S32" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="T32" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="U32" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="V32" s="4" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="W32" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z32" s="0" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>188</v>
-      </c>
-      <c r="B33" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="0" t="s">
-        <v>189</v>
-      </c>
-      <c r="D33" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="F33" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="H33" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I33" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="K33" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="L33" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="M33" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q33" s="0" t="s">
-        <v>190</v>
-      </c>
-      <c r="S33" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="T33" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="U33" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="V33" s="4" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="W33" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>188</v>
-      </c>
-      <c r="B34" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" s="0" t="s">
-        <v>189</v>
-      </c>
-      <c r="D34" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="F34" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="H34" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I34" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="K34" s="0" t="n">
-        <v>192</v>
-      </c>
-      <c r="L34" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="M34" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q34" s="0" t="s">
-        <v>190</v>
-      </c>
-      <c r="S34" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="T34" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="U34" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="V34" s="4" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="W34" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>191</v>
-      </c>
-      <c r="B35" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="0" t="s">
-        <v>192</v>
-      </c>
-      <c r="D35" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="F35" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="H35" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I35" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="K35" s="0" t="n">
-        <v>128</v>
-      </c>
-      <c r="L35" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="M35" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="N35" s="0" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q35" s="0" t="s">
-        <v>195</v>
-      </c>
-      <c r="S35" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="T35" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="U35" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="V35" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="W35" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Y35" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
-        <v>191</v>
-      </c>
-      <c r="B36" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C36" s="0" t="s">
-        <v>192</v>
-      </c>
-      <c r="D36" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="F36" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="H36" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I36" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="K36" s="0" t="n">
-        <v>192</v>
-      </c>
-      <c r="L36" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="M36" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="N36" s="0" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q36" s="0" t="s">
-        <v>195</v>
-      </c>
-      <c r="S36" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="T36" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="U36" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="V36" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="W36" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
-        <v>196</v>
-      </c>
-      <c r="B37" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>197</v>
-      </c>
-      <c r="D37" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="F37" s="0" t="s">
-        <v>198</v>
-      </c>
-      <c r="H37" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I37" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="K37" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="L37" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="M37" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="O37" s="0" t="s">
-        <v>199</v>
-      </c>
-      <c r="S37" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="T37" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="U37" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="V37" s="4" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="W37" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>200</v>
-      </c>
-      <c r="B38" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="0" t="s">
-        <v>201</v>
-      </c>
-      <c r="D38" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="F38" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="H38" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I38" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="K38" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="L38" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="M38" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q38" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="S38" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="T38" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="U38" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="V38" s="4" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="W38" s="4" t="b">
+      <c r="W39" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -555,7 +555,7 @@
     <t xml:space="preserve">{1:1,2:1,3:2,4:3,5:3}</t>
   </si>
   <si>
-    <t xml:space="preserve">1, lbd</t>
+    <t xml:space="preserve">5, lbd</t>
   </si>
   <si>
     <t xml:space="preserve">{1:1,2:1,3:1,4:1,5:1}</t>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="model_params" sheetId="1" state="visible" r:id="rId3"/>
@@ -14,6 +14,7 @@
     <sheet name="affine3d" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="loss_params" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="plans" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="resnet" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="231">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -120,6 +121,12 @@
     <t xml:space="preserve">5</t>
   </si>
   <si>
+    <t xml:space="preserve">depth_reset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[18,10,34,50,101]</t>
+  </si>
+  <si>
     <t xml:space="preserve">optimizer</t>
   </si>
   <si>
@@ -402,6 +409,9 @@
     <t xml:space="preserve">softmax</t>
   </si>
   <si>
+    <t xml:space="preserve">include_background</t>
+  </si>
+  <si>
     <t xml:space="preserve">mnemonic</t>
   </si>
   <si>
@@ -471,9 +481,6 @@
     <t xml:space="preserve">plan_test</t>
   </si>
   <si>
-    <t xml:space="preserve">run_name</t>
-  </si>
-  <si>
     <t xml:space="preserve">periodict_test</t>
   </si>
   <si>
@@ -534,9 +541,6 @@
     <t xml:space="preserve">4, lbd</t>
   </si>
   <si>
-    <t xml:space="preserve">LITS-860</t>
-  </si>
-  <si>
     <t xml:space="preserve">70</t>
   </si>
   <si>
@@ -561,6 +565,9 @@
     <t xml:space="preserve">{1:1,2:1,3:1,4:1,5:1}</t>
   </si>
   <si>
+    <t xml:space="preserve">0.75, 0.75,0.75</t>
+  </si>
+  <si>
     <t xml:space="preserve">totalseg</t>
   </si>
   <si>
@@ -621,29 +628,108 @@
     <t xml:space="preserve">kidneys</t>
   </si>
   <si>
+    <t xml:space="preserve">no kidney labels</t>
+  </si>
+  <si>
     <t xml:space="preserve">kits21</t>
   </si>
   <si>
     <t xml:space="preserve">DS.kits21/lms</t>
   </si>
   <si>
-    <t xml:space="preserve">{1:0,2:1,3:0}</t>
+    <t xml:space="preserve">{1:0,2:1,3:1}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{1:1,2:2,3:2}</t>
   </si>
   <si>
     <t xml:space="preserve">test</t>
   </si>
   <si>
     <t xml:space="preserve">drli_short, litsmc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ResNet3D]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ResNet3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resnet_depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[10,18,34,50,101,152]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">num_classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spatial_dims</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conv1_t_size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[3,5,7]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conv1_t_stride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1,2]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no_max_pool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shortcut_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[A,B]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">widen_factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1.0,2.0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_forward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bias_downsample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">norm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[batch,instance]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">batch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">('relu', {'inplace': True})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pretrained</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00E+00"/>
-    <numFmt numFmtId="166" formatCode="General"/>
+    <numFmt numFmtId="166" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
+    <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -742,11 +828,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -942,7 +1028,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.17"/>
@@ -1015,7 +1101,7 @@
       <c r="E3" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1092,23 +1178,17 @@
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>32</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="D8" s="1" t="n">
         <v>0</v>
       </c>
@@ -1121,61 +1201,67 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="D10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="C11" s="1" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1186,49 +1272,43 @@
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="D14" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>20</v>
+      <c r="F15" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>0</v>
@@ -1239,7 +1319,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>19</v>
@@ -1251,7 +1331,24 @@
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1293,7 +1390,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
@@ -1308,34 +1405,34 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>30</v>
@@ -1343,44 +1440,44 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>12</v>
@@ -1389,15 +1486,15 @@
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
@@ -1409,29 +1506,29 @@
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>0</v>
@@ -1439,14 +1536,14 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>192</v>
@@ -1454,7 +1551,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>128</v>
@@ -1496,13 +1593,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>4</v>
@@ -1513,171 +1610,171 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0</v>
@@ -1686,7 +1783,7 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>19</v>
@@ -1734,86 +1831,86 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1832,7 +1929,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1852,12 +1949,12 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
@@ -1865,7 +1962,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>20</v>
@@ -1873,7 +1970,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -1884,24 +1981,32 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7" s="4" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1920,1862 +2025,2485 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AF39"/>
+  <dimension ref="A1:AG44"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="25.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="40.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="1" width="20.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="41.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="24.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="13.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="13.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="22.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="23" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="40.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="15" style="1" width="20.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="41.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="24.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="13.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="13.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="22.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="24" style="1" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>61</v>
+        <v>145</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AA1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AB1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="AC1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="1" t="s">
-        <v>149</v>
+      <c r="AG1" s="1" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="K2" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="L2" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>49</v>
+        <v>156</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>156</v>
+        <v>51</v>
       </c>
       <c r="U2" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V2" s="5" t="b">
+      <c r="W2" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W2" s="5" t="b">
+      <c r="X2" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="R3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U3" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="U3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V3" s="5" t="b">
+      <c r="W3" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W3" s="5" t="b">
+      <c r="X3" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="S4" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="T4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T4" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="U4" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V4" s="5" t="b">
+      <c r="W4" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W4" s="5" t="b">
+      <c r="X4" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="U5" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="U5" s="1" t="s">
+      <c r="V5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V5" s="5" t="b">
+      <c r="W5" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W5" s="5" t="b">
+      <c r="X5" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="K6" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="L6" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="M6" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>49</v>
+        <v>156</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>156</v>
+        <v>51</v>
       </c>
       <c r="U6" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V6" s="5" t="b">
+      <c r="W6" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W6" s="5" t="b">
+      <c r="X6" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="R7" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="S7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="U7" s="1" t="s">
+      <c r="V7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V7" s="5" t="b">
+      <c r="W7" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W7" s="5" t="b">
+      <c r="X7" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E8" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="R8" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K8" s="1" t="n">
-        <v>192</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="S8" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="U8" s="1" t="s">
+      <c r="V8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V8" s="5" t="b">
+      <c r="W8" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W8" s="5" t="b">
+      <c r="X8" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="D9" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E9" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="R9" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K9" s="1" t="n">
-        <v>192</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="U9" s="1" t="s">
+      <c r="V9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V9" s="5" t="b">
+      <c r="W9" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W9" s="5" t="b">
+      <c r="X9" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U10" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="V10" s="5" t="b">
+      <c r="W10" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W10" s="5" t="b">
+      <c r="X10" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>153</v>
+      <c r="D11" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>49</v>
+        <v>155</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="V11" s="5" t="b">
+        <v>51</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="W11" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W11" s="5" t="b">
+      <c r="X11" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="D12" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>153</v>
+      <c r="E12" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>49</v>
+        <v>155</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="V12" s="5" t="b">
+        <v>51</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="W12" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W12" s="5" t="b">
+      <c r="X12" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>167</v>
+      <c r="D13" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="S13" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="T13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T13" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="V13" s="5" t="b">
+      <c r="U13" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="W13" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W13" s="5" t="b">
+      <c r="X13" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>153</v>
+        <v>165</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>49</v>
+        <v>155</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="V14" s="5" t="b">
+        <v>51</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="W14" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W14" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z14" s="1" t="s">
-        <v>169</v>
+      <c r="X14" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="D15" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="I15" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U15" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="V15" s="5" t="b">
+      <c r="W15" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W15" s="5" t="b">
+      <c r="X15" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="J16" s="1" t="n">
+      <c r="D16" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="K16" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="S16" s="1" t="s">
+      <c r="T16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V16" s="5" t="b">
+      <c r="W16" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W16" s="5" t="b">
+      <c r="X16" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="D17" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>49</v>
+        <v>172</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="V17" s="5" t="b">
+        <v>51</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="W17" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W17" s="5" t="b">
+      <c r="X17" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U18" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="V18" s="5" t="b">
+      <c r="W18" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W18" s="5" t="b">
+      <c r="X18" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D19" s="1" t="n">
+      <c r="D19" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="V19" s="5" t="b">
+      <c r="J19" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="W19" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W19" s="5" t="b">
+      <c r="X19" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="D20" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I20" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N20" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H20" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="1" t="s">
+      <c r="R20" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U20" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="U20" s="1" t="s">
+      <c r="V20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V20" s="5" t="b">
+      <c r="W20" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W20" s="5" t="b">
+      <c r="X20" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D21" s="1" t="n">
+      <c r="D21" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E21" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I21" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H21" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="1" t="s">
+      <c r="R21" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U21" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="U21" s="1" t="s">
+      <c r="V21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V21" s="5" t="b">
+      <c r="W21" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W21" s="5" t="b">
+      <c r="X21" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D22" s="1" t="n">
+      <c r="D22" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E22" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I22" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H22" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="1" t="s">
+      <c r="P22" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U22" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="U22" s="1" t="s">
+      <c r="V22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V22" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
       <c r="W22" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="X22" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D23" s="1" t="n">
+      <c r="D23" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E23" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="G23" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I23" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H23" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="1" t="s">
+      <c r="P23" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="S23" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="U23" s="1" t="s">
+      <c r="V23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V23" s="5" t="b">
+      <c r="W23" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W23" s="5" t="b">
+      <c r="X23" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D24" s="1" t="n">
+      <c r="D24" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="H24" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="T24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="S24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="U24" s="1" t="s">
+      <c r="V24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V24" s="5" t="b">
+      <c r="W24" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W24" s="5" t="b">
+      <c r="X24" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D25" s="1" t="n">
+      <c r="D25" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E25" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="H25" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>167</v>
+      <c r="I25" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="J25" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="P25" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="S25" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>156</v>
+      <c r="T25" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="U25" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V25" s="5" t="b">
+      <c r="W25" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W25" s="5" t="b">
+      <c r="X25" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="1" t="s">
+      <c r="D26" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="T26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="S26" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="U26" s="1" t="s">
+      <c r="V26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V26" s="5" t="b">
+      <c r="W26" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W26" s="5" t="b">
+      <c r="X26" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L27" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="P27" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>156</v>
+      <c r="T27" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="U27" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="V27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V27" s="5" t="b">
+      <c r="W27" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W27" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AF27" s="1" t="n">
-        <v>10</v>
+      <c r="X27" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>178</v>
+        <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="K28" s="1" t="s">
         <v>154</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="P28" s="1" t="s">
-        <v>180</v>
+        <v>155</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="U28" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V28" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
       <c r="W28" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AF28" s="1" t="n">
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="X28" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG28" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>178</v>
+        <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>158</v>
+        <v>180</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="U29" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="V29" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V29" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
       <c r="W29" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="AF29" s="1" t="n">
-        <v>10</v>
+      <c r="X29" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG29" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B30" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="V30" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="V30" s="5" t="b">
+      <c r="W30" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W30" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AF30" s="1" t="n">
+      <c r="X30" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG30" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>178</v>
+        <v>4</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>153</v>
+        <v>180</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>49</v>
+        <v>155</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>183</v>
+        <v>51</v>
       </c>
       <c r="U31" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="V31" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V31" s="5" t="b">
+      <c r="W31" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W31" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AF31" s="1" t="n">
+      <c r="X31" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG31" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>178</v>
+        <v>5</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="K32" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U32" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="L32" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="U32" s="1" t="s">
+      <c r="V32" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V32" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
       <c r="W32" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AF32" s="1" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="X32" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG32" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="O33" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B33" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="S33" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="T33" s="1" t="s">
-        <v>183</v>
+        <v>51</v>
       </c>
       <c r="U33" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="V33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V33" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
       <c r="W33" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="Z33" s="1" t="s">
-        <v>169</v>
+      <c r="X33" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG33" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B34" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="1" t="s">
+      <c r="E34" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D34" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="H34" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="L34" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q34" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>49</v>
+        <v>156</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>156</v>
+        <v>51</v>
       </c>
       <c r="U34" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="V34" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V34" s="5" t="b">
+      <c r="W34" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W34" s="5" t="b">
+      <c r="X34" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E35" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="G35" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I35" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N35" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H35" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I35" s="1" t="s">
+      <c r="R35" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U35" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K35" s="1" t="n">
-        <v>192</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q35" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="S35" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T35" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="U35" s="1" t="s">
+      <c r="V35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V35" s="5" t="b">
+      <c r="W35" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W35" s="5" t="b">
+      <c r="X35" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B36" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="E36" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I36" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L36" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="R36" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D36" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="H36" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I36" s="1" t="s">
+      <c r="T36" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U36" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K36" s="1" t="n">
-        <v>128</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q36" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="S36" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T36" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="U36" s="1" t="s">
+      <c r="V36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V36" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
       <c r="W36" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="1" t="n">
-        <v>1</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="X36" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="H37" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I37" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L37" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="T37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K37" s="1" t="n">
-        <v>192</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="S37" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="U37" s="1" t="s">
+      <c r="V37" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V37" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
       <c r="W37" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="Y37" s="1" t="n">
+      <c r="X37" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z37" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I38" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L38" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="O38" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B38" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="1" t="s">
+      <c r="R38" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D38" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="H38" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I38" s="1" t="s">
+      <c r="T38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O38" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="S38" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T38" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="U38" s="1" t="s">
+      <c r="V38" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="V38" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
       <c r="W38" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="X38" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z38" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B39" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="1" t="s">
+      <c r="E39" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="I39" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="T39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="W39" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="X39" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="I40" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="T40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="W40" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="X40" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I41" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L41" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="T41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="W41" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="X41" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I42" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L42" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="M42" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="T42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="W42" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="X42" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I43" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L43" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="M43" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="T43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="W43" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="X43" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I44" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="R44" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="W44" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="X44" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="H39" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q39" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="S39" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="U39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="V39" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="W39" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="model_params" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="208">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -196,6 +196,9 @@
     <t xml:space="preserve">compiled</t>
   </si>
   <si>
+    <t xml:space="preserve">nnunet_use_residual</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unnamed: 5</t>
   </si>
   <si>
@@ -647,78 +650,6 @@
   </si>
   <si>
     <t xml:space="preserve">drli_short, litsmc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ResNet3D]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ResNet3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resnet_depth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[10,18,34,50,101,152]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">num_classes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spatial_dims</t>
-  </si>
-  <si>
-    <t xml:space="preserve">conv1_t_size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[3,5,7]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">conv1_t_stride</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[1,2]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no_max_pool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shortcut_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[A,B]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">widen_factor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[1.0,2.0]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_forward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bias_downsample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">norm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[batch,instance]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">batch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">('relu', {'inplace': True})</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pretrained</t>
   </si>
 </sst>
 </file>
@@ -1028,7 +959,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.17"/>
@@ -1349,6 +1280,23 @@
       </c>
       <c r="E18" s="1" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1390,7 +1338,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
@@ -1405,34 +1353,34 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>30</v>
@@ -1440,7 +1388,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>51</v>
@@ -1448,36 +1396,36 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>12</v>
@@ -1486,15 +1434,15 @@
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
@@ -1511,24 +1459,24 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>0</v>
@@ -1536,14 +1484,14 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>192</v>
@@ -1551,7 +1499,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>128</v>
@@ -1593,13 +1541,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>4</v>
@@ -1610,114 +1558,114 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>0.1</v>
@@ -1728,53 +1676,53 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0</v>
@@ -1783,7 +1731,7 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>19</v>
@@ -1831,32 +1779,32 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>0</v>
@@ -1865,29 +1813,29 @@
         <v>36</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>0</v>
@@ -1898,19 +1846,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1949,12 +1897,12 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
@@ -1962,7 +1910,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>20</v>
@@ -1970,7 +1918,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -1981,18 +1929,18 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>0</v>
@@ -2003,9 +1951,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E7" s="4" t="b">
+        <v>128</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2025,7 +1974,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AG44"/>
+  <dimension ref="A1:AG45"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.67"/>
@@ -2051,82 +2000,82 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>4</v>
@@ -2144,39 +2093,39 @@
         <v>5</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V2" s="1" t="s">
         <v>4</v>
@@ -2192,43 +2141,43 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V3" s="1" t="s">
         <v>4</v>
@@ -2244,37 +2193,37 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V4" s="1" t="s">
         <v>4</v>
@@ -2290,31 +2239,31 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V5" s="1" t="s">
         <v>4</v>
@@ -2330,34 +2279,34 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V6" s="1" t="s">
         <v>4</v>
@@ -2373,40 +2322,40 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="T7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V7" s="1" t="s">
         <v>4</v>
@@ -2422,40 +2371,40 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="T8" s="1" t="n">
         <v>2</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V8" s="1" t="s">
         <v>4</v>
@@ -2471,40 +2420,40 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>75</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L9" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="T9" s="1" t="n">
         <v>2</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V9" s="1" t="s">
         <v>4</v>
@@ -2520,34 +2469,34 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T10" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="W10" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2560,28 +2509,28 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T11" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="W11" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2594,31 +2543,31 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T12" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="W12" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2631,28 +2580,28 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="W13" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2665,31 +2614,31 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T14" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="W14" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2702,31 +2651,31 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T15" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="W15" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2739,16 +2688,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>7</v>
@@ -2767,31 +2716,31 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T17" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="W17" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2804,34 +2753,34 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="W18" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2844,13 +2793,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>40</v>
@@ -2859,13 +2808,13 @@
         <v>20</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="W19" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2878,44 +2827,44 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I20" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T20" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V20" s="1" t="s">
         <v>4</v>
@@ -2931,44 +2880,44 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I21" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T21" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V21" s="1" t="s">
         <v>4</v>
@@ -2984,47 +2933,47 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I22" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P22" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="R22" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="T22" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V22" s="1" t="s">
         <v>4</v>
@@ -3040,47 +2989,47 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I23" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="I23" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="T23" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="V23" s="1" t="s">
         <v>4</v>
@@ -3096,13 +3045,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>50</v>
@@ -3112,25 +3061,25 @@
         <v>0</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V24" s="1" t="s">
         <v>4</v>
@@ -3146,13 +3095,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>20</v>
@@ -3162,28 +3111,28 @@
         <v>0</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K25" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="P25" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="T25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V25" s="1" t="s">
         <v>4</v>
@@ -3199,13 +3148,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>0</v>
@@ -3215,25 +3164,25 @@
         <v>0</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="T26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V26" s="1" t="s">
         <v>4</v>
@@ -3249,13 +3198,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>0</v>
@@ -3265,25 +3214,25 @@
         <v>0</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L27" s="1" t="n">
         <v>96</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="T27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="V27" s="1" t="s">
         <v>4</v>
@@ -3299,28 +3248,28 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V28" s="1" t="s">
         <v>4</v>
@@ -3339,31 +3288,31 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>43</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="V29" s="1" t="s">
         <v>4</v>
@@ -3382,31 +3331,31 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B30" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T30" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="V30" s="1" t="s">
         <v>4</v>
@@ -3425,31 +3374,31 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B31" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T31" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="V31" s="1" t="s">
         <v>4</v>
@@ -3468,34 +3417,34 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B32" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T32" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="V32" s="1" t="s">
         <v>4</v>
@@ -3514,34 +3463,34 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L33" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="O33" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>186</v>
       </c>
       <c r="T33" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="V33" s="1" t="s">
         <v>4</v>
@@ -3560,31 +3509,31 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T34" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="V34" s="1" t="s">
         <v>4</v>
@@ -3600,44 +3549,44 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I35" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="T35" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V35" s="1" t="s">
         <v>4</v>
@@ -3653,44 +3602,44 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B36" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I36" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L36" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="T36" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V36" s="1" t="s">
         <v>4</v>
@@ -3706,47 +3655,47 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I37" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L37" s="1" t="n">
         <v>128</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="T37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V37" s="1" t="s">
         <v>4</v>
@@ -3765,47 +3714,47 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B38" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>100</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I38" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="T38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U38" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V38" s="1" t="s">
         <v>4</v>
@@ -3824,47 +3773,47 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I39" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="T39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U39" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V39" s="1" t="s">
         <v>4</v>
@@ -3880,13 +3829,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B40" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>50</v>
@@ -3896,25 +3845,25 @@
         <v>0</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T40" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V40" s="1" t="s">
         <v>4</v>
@@ -3930,13 +3879,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B41" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E41" s="1" t="n">
         <v>100</v>
@@ -3946,25 +3895,25 @@
         <v>0</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>160</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T41" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U41" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V41" s="1" t="s">
         <v>4</v>
@@ -3980,13 +3929,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B42" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E42" s="1" t="n">
         <v>100</v>
@@ -3996,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>160</v>
@@ -4005,16 +3954,16 @@
         <v>64</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T42" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V42" s="1" t="s">
         <v>4</v>
@@ -4030,23 +3979,23 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B43" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E43" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="I43" s="5" t="b">
+      <c r="I43" s="4" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L43" s="1" t="n">
         <v>160</v>
@@ -4055,78 +4004,128 @@
         <v>64</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T43" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V43" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="W43" s="5" t="b">
+      <c r="W43" s="4" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X43" s="5" t="b">
+      <c r="X43" s="4" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="L44" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="M44" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="P44" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B44" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="1" t="s">
+      <c r="T44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="V44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="W44" s="4" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="X44" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="B45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G45" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="R45" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="T45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U45" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="I44" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="R44" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="T44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U44" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="V44" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W44" s="5" t="b">
+      <c r="V45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="W45" s="4" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X44" s="5" t="b">
+      <c r="X45" s="4" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4149,6 +4148,9 @@
   </sheetPr>
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.16"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -4171,340 +4173,142 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>208</v>
-      </c>
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>18</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>2</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>3</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>7</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>220</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>227</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>229</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F19" s="1" t="n">
-        <v>0.0005</v>
-      </c>
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>0.85</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="model_params" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="211">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -94,7 +94,10 @@
     <t xml:space="preserve">arch</t>
   </si>
   <si>
-    <t xml:space="preserve">[ResidualUNet3D,UNet3D,VTUNet, nnUNet,SwinUNETR,DynUNet]</t>
+    <t xml:space="preserve">[ResidualUNet3D,UNet3D,VTUNet, nnUNet,SwinUNETR,DynUNet, ResUnet]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ResUNet</t>
   </si>
   <si>
     <t xml:space="preserve">nnUNet</t>
@@ -199,6 +202,9 @@
     <t xml:space="preserve">nnunet_use_residual</t>
   </si>
   <si>
+    <t xml:space="preserve">n_blocks_per_level</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unnamed: 5</t>
   </si>
   <si>
@@ -650,6 +656,9 @@
   </si>
   <si>
     <t xml:space="preserve">drli_short, litsmc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\</t>
   </si>
 </sst>
 </file>
@@ -742,7 +751,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -764,6 +773,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -959,7 +972,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.17"/>
@@ -1070,36 +1083,36 @@
         <v>23</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="J5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>20</v>
@@ -1107,10 +1120,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>18</v>
@@ -1118,18 +1131,18 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
@@ -1141,46 +1154,46 @@
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>19</v>
@@ -1192,23 +1205,23 @@
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>0</v>
@@ -1219,27 +1232,27 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>0</v>
@@ -1250,7 +1263,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>19</v>
@@ -1267,7 +1280,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>19</v>
@@ -1279,12 +1292,12 @@
         <v>0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>19</v>
@@ -1295,8 +1308,17 @@
       <c r="D19" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="4" t="b">
-        <v>1</v>
+      <c r="E19" s="4" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1338,7 +1360,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
@@ -1353,79 +1375,79 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>12</v>
@@ -1434,15 +1456,15 @@
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
@@ -1454,29 +1476,29 @@
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>0</v>
@@ -1484,14 +1506,14 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>192</v>
@@ -1499,7 +1521,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>128</v>
@@ -1541,13 +1563,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>4</v>
@@ -1558,171 +1580,171 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0</v>
@@ -1731,7 +1753,7 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>19</v>
@@ -1779,86 +1801,86 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1897,12 +1919,12 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
@@ -1910,7 +1932,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>20</v>
@@ -1918,7 +1940,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -1929,18 +1951,18 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>0</v>
@@ -1951,7 +1973,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E7" s="4" t="n">
         <f aca="false">FALSE()</f>
@@ -1974,7 +1996,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AG45"/>
+  <dimension ref="A1:AF45"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.67"/>
@@ -1995,137 +2017,137 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="13.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="13.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="22.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="24" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="24" style="1" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="V2" s="1" t="s">
         <v>4</v>
@@ -2141,43 +2163,43 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="R3" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U3" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V3" s="1" t="s">
         <v>4</v>
@@ -2193,37 +2215,37 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="T4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="V4" s="1" t="s">
         <v>4</v>
@@ -2239,31 +2261,31 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="U5" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V5" s="1" t="s">
         <v>4</v>
@@ -2279,34 +2301,34 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="V6" s="1" t="s">
         <v>4</v>
@@ -2322,40 +2344,40 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="R7" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="T7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="V7" s="1" t="s">
         <v>4</v>
@@ -2371,40 +2393,40 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="T8" s="1" t="n">
         <v>2</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="V8" s="1" t="s">
         <v>4</v>
@@ -2420,40 +2442,40 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>75</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L9" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="T9" s="1" t="n">
         <v>2</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="V9" s="1" t="s">
         <v>4</v>
@@ -2469,34 +2491,34 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U10" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="W10" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2509,28 +2531,28 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="W11" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2543,31 +2565,31 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="W12" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2580,28 +2602,28 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="T13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="W13" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2614,31 +2636,31 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="W14" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2651,31 +2673,31 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J15" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U15" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="W15" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2688,16 +2710,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>7</v>
@@ -2716,31 +2738,31 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="W17" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2753,34 +2775,34 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="T18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="W18" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2793,13 +2815,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>40</v>
@@ -2808,13 +2830,13 @@
         <v>20</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="W19" s="5" t="b">
         <f aca="false">TRUE()</f>
@@ -2827,44 +2849,44 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I20" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N20" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I20" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="1" t="s">
+      <c r="R20" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U20" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V20" s="1" t="s">
         <v>4</v>
@@ -2880,44 +2902,44 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I21" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I21" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="1" t="s">
+      <c r="R21" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U21" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V21" s="1" t="s">
         <v>4</v>
@@ -2933,47 +2955,47 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I22" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I22" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="1" t="s">
+      <c r="P22" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U22" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V22" s="1" t="s">
         <v>4</v>
@@ -2989,47 +3011,47 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I23" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I23" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="1" t="s">
+      <c r="P23" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="T23" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V23" s="1" t="s">
         <v>4</v>
@@ -3045,13 +3067,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>50</v>
@@ -3061,25 +3083,25 @@
         <v>0</v>
       </c>
       <c r="J24" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="T24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="T24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V24" s="1" t="s">
         <v>4</v>
@@ -3095,13 +3117,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>20</v>
@@ -3111,28 +3133,28 @@
         <v>0</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="T25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="V25" s="1" t="s">
         <v>4</v>
@@ -3148,13 +3170,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>0</v>
@@ -3164,25 +3186,25 @@
         <v>0</v>
       </c>
       <c r="J26" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="T26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="T26" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V26" s="1" t="s">
         <v>4</v>
@@ -3198,13 +3220,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>0</v>
@@ -3214,25 +3236,25 @@
         <v>0</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L27" s="1" t="n">
         <v>96</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="T27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="V27" s="1" t="s">
         <v>4</v>
@@ -3248,28 +3270,28 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="V28" s="1" t="s">
         <v>4</v>
@@ -3282,37 +3304,37 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="AG28" s="1" t="n">
+      <c r="AF28" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="V29" s="1" t="s">
         <v>4</v>
@@ -3325,37 +3347,37 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="AG29" s="1" t="n">
+      <c r="AF29" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B30" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="V30" s="1" t="s">
         <v>4</v>
@@ -3368,37 +3390,37 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="AG30" s="1" t="n">
+      <c r="AF30" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B31" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="V31" s="1" t="s">
         <v>4</v>
@@ -3411,40 +3433,40 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="AG31" s="1" t="n">
+      <c r="AF31" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B32" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="V32" s="1" t="s">
         <v>4</v>
@@ -3457,41 +3479,41 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="AG32" s="1" t="n">
+      <c r="AF32" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L33" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U33" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="M33" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U33" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="V33" s="1" t="s">
         <v>4</v>
       </c>
@@ -3503,37 +3525,37 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="AG33" s="1" t="n">
+      <c r="AF33" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="V34" s="1" t="s">
         <v>4</v>
@@ -3549,44 +3571,44 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G35" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I35" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N35" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I35" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="1" t="s">
+      <c r="R35" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U35" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="T35" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U35" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V35" s="1" t="s">
         <v>4</v>
@@ -3602,44 +3624,44 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B36" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I36" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L36" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="V36" s="1" t="s">
         <v>4</v>
@@ -3655,47 +3677,47 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I37" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L37" s="1" t="n">
         <v>128</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="T37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="V37" s="1" t="s">
         <v>4</v>
@@ -3707,54 +3729,51 @@
       <c r="X37" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
-      </c>
-      <c r="Z37" s="1" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B38" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>100</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I38" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="T38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U38" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="V38" s="1" t="s">
         <v>4</v>
@@ -3766,54 +3785,51 @@
       <c r="X38" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
-      </c>
-      <c r="Z38" s="1" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I39" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J39" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="T39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="P39" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="T39" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V39" s="1" t="s">
         <v>4</v>
@@ -3826,16 +3842,19 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="Y39" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B40" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>50</v>
@@ -3845,25 +3864,25 @@
         <v>0</v>
       </c>
       <c r="J40" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="T40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="T40" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U40" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V40" s="1" t="s">
         <v>4</v>
@@ -3876,16 +3895,19 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="Y40" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B41" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E41" s="1" t="n">
         <v>100</v>
@@ -3895,25 +3917,25 @@
         <v>0</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>160</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="T41" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U41" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="V41" s="1" t="s">
         <v>4</v>
@@ -3926,16 +3948,19 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="Y41" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B42" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E42" s="1" t="n">
         <v>100</v>
@@ -3945,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>160</v>
@@ -3954,16 +3979,16 @@
         <v>64</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="T42" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="V42" s="1" t="s">
         <v>4</v>
@@ -3976,16 +4001,19 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="Y42" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B43" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E43" s="1" t="n">
         <v>100</v>
@@ -3995,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L43" s="1" t="n">
         <v>160</v>
@@ -4004,16 +4032,16 @@
         <v>64</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="T43" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="V43" s="1" t="s">
         <v>4</v>
@@ -4026,16 +4054,19 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="Y43" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B44" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E44" s="1" t="n">
         <v>20</v>
@@ -4045,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L44" s="1" t="n">
         <v>160</v>
@@ -4054,16 +4085,16 @@
         <v>96</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="T44" s="1" t="n">
         <v>1</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="V44" s="1" t="s">
         <v>4</v>
@@ -4076,47 +4107,50 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="Y44" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B45" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G45" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N45" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I45" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J45" s="1" t="s">
+      <c r="R45" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="T45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U45" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="R45" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="T45" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U45" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V45" s="1" t="s">
         <v>4</v>
@@ -4146,10 +4180,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="48.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4173,116 +4207,101 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
+      <c r="I8" s="6" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -4290,21 +4309,18 @@
       <c r="F19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="211">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -640,10 +640,10 @@
     <t xml:space="preserve">no kidney labels</t>
   </si>
   <si>
-    <t xml:space="preserve">kits21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DS.kits21/lms</t>
+    <t xml:space="preserve">kits23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DS.kits23/lms</t>
   </si>
   <si>
     <t xml:space="preserve">{1:0,2:1,3:1}</t>
@@ -1996,7 +1996,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AF45"/>
+  <dimension ref="A1:AF46"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.67"/>
@@ -4113,19 +4113,16 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>162</v>
+        <v>204</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>50</v>
       </c>
       <c r="I45" s="4" t="n">
         <f aca="false">FALSE()</f>
@@ -4134,20 +4131,20 @@
       <c r="J45" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L45" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>159</v>
+      <c r="L45" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="M45" s="1" t="n">
+        <v>96</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="R45" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="T45" s="1" t="s">
-        <v>52</v>
+      <c r="P45" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="T45" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="U45" s="1" t="s">
         <v>161</v>
@@ -4160,6 +4157,62 @@
         <v>1</v>
       </c>
       <c r="X45" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="1" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="R46" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="T46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U46" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="V46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="W46" s="4" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="X46" s="4" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="209">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -637,16 +637,10 @@
     <t xml:space="preserve">kidneys</t>
   </si>
   <si>
-    <t xml:space="preserve">no kidney labels</t>
+    <t xml:space="preserve">all labels</t>
   </si>
   <si>
     <t xml:space="preserve">kits23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DS.kits23/lms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{1:0,2:1,3:1}</t>
   </si>
   <si>
     <t xml:space="preserve">{1:1,2:2,3:2}</t>
@@ -3803,28 +3797,22 @@
       <c r="E39" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="I39" s="5" t="b">
+      <c r="I39" s="4" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L39" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>159</v>
+      <c r="L39" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="M39" s="1" t="n">
+        <v>96</v>
       </c>
       <c r="N39" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="P39" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="T39" s="1" t="n">
         <v>1</v>
       </c>
@@ -3834,16 +3822,16 @@
       <c r="V39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="W39" s="5" t="b">
+      <c r="W39" s="4" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X39" s="5" t="b">
+      <c r="X39" s="4" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3876,7 +3864,7 @@
         <v>160</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="T40" s="1" t="n">
         <v>1</v>
@@ -3929,7 +3917,7 @@
         <v>160</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="T41" s="1" t="n">
         <v>1</v>
@@ -3982,7 +3970,7 @@
         <v>160</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="T42" s="1" t="n">
         <v>1</v>
@@ -4035,7 +4023,7 @@
         <v>160</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="T43" s="1" t="n">
         <v>1</v>
@@ -4088,7 +4076,7 @@
         <v>160</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="T44" s="1" t="n">
         <v>1</v>
@@ -4141,7 +4129,7 @@
         <v>160</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="T45" s="1" t="n">
         <v>1</v>
@@ -4166,13 +4154,13 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B46" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>37</v>
@@ -4295,7 +4283,7 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="I8" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="210">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -461,6 +461,9 @@
   </si>
   <si>
     <t xml:space="preserve">remapping_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vip_label</t>
   </si>
   <si>
     <t xml:space="preserve">remapping_lbd</t>
@@ -1990,7 +1993,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AF46"/>
+  <dimension ref="A1:AG46"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.67"/>
@@ -2004,14 +2007,14 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="15" style="1" width="20.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="41.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="24.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="13.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="13.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="22.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="24" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="15" style="1" width="20.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="41.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="24.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="13.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="13.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="22.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="25" style="1" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2073,16 +2076,16 @@
         <v>148</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="V1" s="1" t="s">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>151</v>
@@ -2094,728 +2097,731 @@
         <v>153</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>4</v>
+        <v>154</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="1" t="s">
-        <v>154</v>
+      <c r="AG1" s="1" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>37</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="T2" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="V2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W2" s="5" t="b">
+        <v>162</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X2" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X2" s="5" t="b">
+      <c r="Y2" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>37</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>37</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="T3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="U3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="U3" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="V3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W3" s="5" t="b">
+        <v>162</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X3" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X3" s="5" t="b">
+      <c r="Y3" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>37</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="T4" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="U4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U4" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="V4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W4" s="5" t="b">
+        <v>162</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X4" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X4" s="5" t="b">
+      <c r="Y4" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="U5" s="1" t="s">
         <v>161</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W5" s="5" t="b">
+        <v>162</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X5" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X5" s="5" t="b">
+      <c r="Y5" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>37</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="T6" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="U6" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="U6" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="V6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W6" s="5" t="b">
+        <v>162</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X6" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X6" s="5" t="b">
+      <c r="Y6" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="T7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W7" s="5" t="b">
+      <c r="W7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X7" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X7" s="5" t="b">
+      <c r="Y7" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="T8" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="U8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="U8" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="V8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W8" s="5" t="b">
+        <v>162</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X8" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X8" s="5" t="b">
+      <c r="Y8" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>75</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L9" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="T9" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="U9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="U9" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="V9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W9" s="5" t="b">
+        <v>162</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X9" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X9" s="5" t="b">
+      <c r="Y9" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T10" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="U10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="U10" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="W10" s="5" t="b">
+      <c r="V10" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="X10" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X10" s="5" t="b">
+      <c r="Y10" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T11" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="U11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="U11" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="W11" s="5" t="b">
+      <c r="V11" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="X11" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X11" s="5" t="b">
+      <c r="Y11" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T12" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="U12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="W12" s="5" t="b">
+      <c r="V12" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="X12" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X12" s="5" t="b">
+      <c r="Y12" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="T13" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="U13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U13" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="W13" s="5" t="b">
+      <c r="V13" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="X13" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X13" s="5" t="b">
+      <c r="Y13" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T14" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="U14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="U14" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="W14" s="5" t="b">
+      <c r="V14" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="X14" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X14" s="5" t="b">
+      <c r="Y14" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T15" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="U15" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="U15" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="W15" s="5" t="b">
+      <c r="V15" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="X15" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X15" s="5" t="b">
+      <c r="Y15" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="T16" s="1" t="s">
+      <c r="U16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W16" s="5" t="b">
+      <c r="X16" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X16" s="5" t="b">
+      <c r="Y16" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>37</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T17" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="U17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="U17" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="W17" s="5" t="b">
+      <c r="V17" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="X17" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X17" s="5" t="b">
+      <c r="Y17" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T18" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="U18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U18" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="W18" s="5" t="b">
+      <c r="V18" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="X18" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X18" s="5" t="b">
+      <c r="Y18" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>40</v>
@@ -2824,250 +2830,250 @@
         <v>20</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="U19" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="W19" s="5" t="b">
+      <c r="V19" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="X19" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X19" s="5" t="b">
+      <c r="Y19" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>37</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I20" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V20" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="I20" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="V20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W20" s="5" t="b">
+      <c r="W20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X20" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X20" s="5" t="b">
+      <c r="Y20" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I21" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V21" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="I21" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="V21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W21" s="5" t="b">
+      <c r="W21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X21" s="5" t="b">
+      <c r="Y21" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I22" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V22" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="I22" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="V22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W22" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="W22" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="X22" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I23" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="I23" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="T23" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="V23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W23" s="5" t="b">
+      <c r="W23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X23" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X23" s="5" t="b">
+      <c r="Y23" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>50</v>
@@ -3077,47 +3083,47 @@
         <v>0</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="T24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" s="1" t="s">
         <v>161</v>
       </c>
+      <c r="Q24" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="U24" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="V24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W24" s="5" t="b">
+        <v>162</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X24" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X24" s="5" t="b">
+      <c r="Y24" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>20</v>
@@ -3127,50 +3133,50 @@
         <v>0</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K25" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q25" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="T25" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>161</v>
+      <c r="U25" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W25" s="5" t="b">
+        <v>162</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X25" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X25" s="5" t="b">
+      <c r="Y25" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>0</v>
@@ -3180,47 +3186,47 @@
         <v>0</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="T26" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" s="1" t="s">
         <v>161</v>
       </c>
+      <c r="Q26" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="U26" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="V26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W26" s="5" t="b">
+        <v>162</v>
+      </c>
+      <c r="W26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X26" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X26" s="5" t="b">
+      <c r="Y26" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>0</v>
@@ -3230,569 +3236,569 @@
         <v>0</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L27" s="1" t="n">
         <v>96</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="P27" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="T27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q27" s="1" t="s">
         <v>182</v>
       </c>
+      <c r="U27" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="V27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W27" s="5" t="b">
+        <v>183</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X27" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X27" s="5" t="b">
+      <c r="Y27" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>37</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="U28" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W28" s="5" t="b">
+        <v>162</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X28" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X28" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AF28" s="1" t="n">
+      <c r="Y28" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG28" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>44</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q29" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="V29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W29" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <v>160</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="W29" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="X29" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="AF29" s="1" t="n">
+      <c r="Y29" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG29" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B30" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>37</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T30" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="U30" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="U30" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="V30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W30" s="5" t="b">
+        <v>187</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X30" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X30" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AF30" s="1" t="n">
+      <c r="Y30" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG30" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B31" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T31" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="U31" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="U31" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="V31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W31" s="5" t="b">
+        <v>189</v>
+      </c>
+      <c r="W31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X31" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X31" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AF31" s="1" t="n">
+      <c r="Y31" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG31" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B32" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="P32" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V32" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="T32" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="V32" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W32" s="5" t="b">
+      <c r="W32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X32" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X32" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AF32" s="1" t="n">
+      <c r="Y32" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG32" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L33" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="O33" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="M33" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O33" s="1" t="s">
+      <c r="U33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V33" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="T33" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U33" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="V33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W33" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="W33" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="X33" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="AF33" s="1" t="n">
+      <c r="Y33" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG33" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T34" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="U34" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="U34" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="V34" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W34" s="5" t="b">
+        <v>189</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X34" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X34" s="5" t="b">
+      <c r="Y34" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G35" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I35" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V35" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="I35" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="T35" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U35" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="V35" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W35" s="5" t="b">
+      <c r="W35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X35" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X35" s="5" t="b">
+      <c r="Y35" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B36" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I36" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L36" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="R36" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="T36" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="U36" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="U36" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="V36" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W36" s="5" t="b">
+        <v>162</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X36" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X36" s="5" t="b">
+      <c r="Y36" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I37" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L37" s="1" t="n">
         <v>128</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="R37" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="T37" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U37" s="1" t="s">
-        <v>161</v>
+      <c r="S37" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="U37" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="V37" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W37" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <v>162</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="X37" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B38" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>100</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I38" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="R38" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="T38" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>161</v>
+      <c r="S38" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="U38" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="V38" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W38" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <v>162</v>
+      </c>
+      <c r="W38" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="X38" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>50</v>
@@ -3802,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L39" s="1" t="n">
         <v>160</v>
@@ -3811,38 +3817,41 @@
         <v>96</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="T39" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" s="1" t="s">
         <v>161</v>
       </c>
+      <c r="P39" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="V39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W39" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X39" s="4" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X39" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Y39" s="1" t="n">
+      <c r="Y39" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z39" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B40" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>50</v>
@@ -3852,50 +3861,53 @@
         <v>0</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="T40" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U40" s="1" t="s">
         <v>161</v>
       </c>
+      <c r="P40" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q40" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="U40" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="V40" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W40" s="5" t="b">
+        <v>162</v>
+      </c>
+      <c r="W40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X40" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X40" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Y40" s="1" t="n">
+      <c r="Y40" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z40" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B41" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E41" s="1" t="n">
         <v>100</v>
@@ -3905,50 +3917,53 @@
         <v>0</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>160</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="T41" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" s="1" t="s">
         <v>161</v>
       </c>
+      <c r="P41" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="U41" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="V41" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W41" s="5" t="b">
+        <v>162</v>
+      </c>
+      <c r="W41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X41" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X41" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Y41" s="1" t="n">
+      <c r="Y41" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z41" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B42" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E42" s="1" t="n">
         <v>100</v>
@@ -3958,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>160</v>
@@ -3967,41 +3982,44 @@
         <v>64</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="P42" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="T42" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U42" s="1" t="s">
         <v>161</v>
       </c>
+      <c r="P42" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="U42" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="V42" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W42" s="5" t="b">
+        <v>162</v>
+      </c>
+      <c r="W42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X42" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X42" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Y42" s="1" t="n">
+      <c r="Y42" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z42" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B43" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E43" s="1" t="n">
         <v>100</v>
@@ -4011,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L43" s="1" t="n">
         <v>160</v>
@@ -4020,41 +4038,44 @@
         <v>64</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="P43" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="T43" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" s="1" t="s">
         <v>161</v>
       </c>
+      <c r="P43" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="U43" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="V43" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W43" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="W43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X43" s="4" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X43" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Y43" s="1" t="n">
+      <c r="Y43" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z43" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B44" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E44" s="1" t="n">
         <v>20</v>
@@ -4064,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L44" s="1" t="n">
         <v>160</v>
@@ -4073,41 +4094,44 @@
         <v>96</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="T44" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U44" s="1" t="s">
         <v>161</v>
       </c>
+      <c r="P44" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q44" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="U44" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="V44" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W44" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="W44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X44" s="4" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X44" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Y44" s="1" t="n">
+      <c r="Y44" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z44" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B45" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E45" s="1" t="n">
         <v>50</v>
@@ -4117,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L45" s="1" t="n">
         <v>160</v>
@@ -4126,81 +4150,84 @@
         <v>96</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="P45" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="T45" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U45" s="1" t="s">
         <v>161</v>
       </c>
+      <c r="P45" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q45" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="U45" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="V45" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W45" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="W45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X45" s="4" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X45" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Y45" s="1" t="n">
+      <c r="Y45" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z45" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B46" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>37</v>
       </c>
       <c r="G46" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="S46" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V46" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="I46" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="R46" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="T46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U46" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="V46" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W46" s="4" t="n">
+      <c r="W46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X46" s="4" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X46" s="4" t="n">
+      <c r="Y46" s="4" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4283,7 +4310,7 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="I8" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -3839,9 +3839,6 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="Z39" s="1" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="211">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -647,6 +647,9 @@
   </si>
   <si>
     <t xml:space="preserve">{1:1,2:2,3:2}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8,.8,0.8</t>
   </si>
   <si>
     <t xml:space="preserve">test</t>
@@ -1993,7 +1996,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AG46"/>
+  <dimension ref="A1:AG47"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.67"/>
@@ -4178,19 +4181,16 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>163</v>
+        <v>205</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>50</v>
       </c>
       <c r="I46" s="4" t="n">
         <f aca="false">FALSE()</f>
@@ -4199,23 +4199,26 @@
       <c r="J46" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="L46" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>160</v>
+      <c r="L46" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="M46" s="1" t="n">
+        <v>128</v>
       </c>
       <c r="N46" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="S46" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="U46" s="1" t="s">
-        <v>52</v>
+      <c r="P46" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q46" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="U46" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="V46" s="1" t="s">
-        <v>162</v>
+        <v>207</v>
       </c>
       <c r="W46" s="1" t="s">
         <v>4</v>
@@ -4225,6 +4228,62 @@
         <v>1</v>
       </c>
       <c r="Y46" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z46" s="1" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="S47" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V47" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="W47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X47" s="4" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Y47" s="4" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4307,7 +4366,7 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="I8" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -4184,7 +4184,7 @@
         <v>203</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>205</v>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="213">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -655,7 +655,13 @@
     <t xml:space="preserve">test</t>
   </si>
   <si>
-    <t xml:space="preserve">drli_short, litsmc</t>
+    <t xml:space="preserve">drli_short, lidc_short,kits23_short</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{1:0,2:1,3:1},{1:1,2:1,3:2,4:2,5:2},{1:1,2:2,3:2}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL.label_localiser:TSL.lungs,None,None</t>
   </si>
   <si>
     <t xml:space="preserve">\</t>
@@ -2010,7 +2016,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="15" style="1" width="20.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="20.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="13.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="20.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="41.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="24.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="8.67"/>
@@ -4267,8 +4276,11 @@
       <c r="N47" s="1" t="s">
         <v>161</v>
       </c>
+      <c r="O47" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="S47" s="1" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="U47" s="1" t="s">
         <v>52</v>
@@ -4366,7 +4378,7 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="I8" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="model_params" sheetId="1" state="visible" r:id="rId3"/>
@@ -15,6 +15,7 @@
     <sheet name="loss_params" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="plans" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="resnet" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="plans_dot" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="218">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -665,6 +666,21 @@
   </si>
   <si>
     <t xml:space="preserve">\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expand_mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2,0.1,0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{1:0}</t>
   </si>
 </sst>
 </file>
@@ -757,7 +773,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -783,6 +799,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4267,14 +4287,11 @@
       <c r="J47" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="L47" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>161</v>
+      <c r="L47" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="M47" s="1" t="n">
+        <v>64</v>
       </c>
       <c r="O47" s="1" t="s">
         <v>210</v>
@@ -4471,4 +4488,165 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:AG2"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="25.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="15.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="17.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="17" style="1" width="23.9"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="L2" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -548,7 +548,7 @@
     <t xml:space="preserve">lbd</t>
   </si>
   <si>
-    <t xml:space="preserve">TSL.label_localiser:TSL.label_localiser,TSL.label_localiser:TSL.label_localiser</t>
+    <t xml:space="preserve">TSL.label_region:TSL.label_region,TSL.label_region:TSL.label_region</t>
   </si>
   <si>
     <t xml:space="preserve">baseline</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">lidc</t>
   </si>
   <si>
-    <t xml:space="preserve">TSL.label_localiser:TSL.lungs</t>
+    <t xml:space="preserve">TSL.label_region:TSL.lungs</t>
   </si>
   <si>
     <t xml:space="preserve">{1:1,2:1,3:2,4:3,5:3}</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">whole</t>
   </si>
   <si>
-    <t xml:space="preserve">TSL.label_full:TSL.label_localiser</t>
+    <t xml:space="preserve">TSL.label_full:TSL.label_region</t>
   </si>
   <si>
     <t xml:space="preserve">1.5, 1.5,1.5</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">colonmsd10</t>
   </si>
   <si>
-    <t xml:space="preserve">TSL.label_localiser:TSL.gi</t>
+    <t xml:space="preserve">TSL.label_region:TSL.gi</t>
   </si>
   <si>
     <t xml:space="preserve">pancreas</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">all labels, abdomen lbd</t>
   </si>
   <si>
-    <t xml:space="preserve">TSL.label_localiser:TSL.abdomen</t>
+    <t xml:space="preserve">TSL.label_region:TSL.abdomen</t>
   </si>
   <si>
     <t xml:space="preserve">test</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">{1:0,2:1,3:1},{1:1,2:1,3:2,4:2,5:2},{1:1,2:2,3:2}</t>
   </si>
   <si>
-    <t xml:space="preserve">TSL.label_localiser:TSL.lungs,None,None</t>
+    <t xml:space="preserve">TSL.label_region:TSL.lungs,None,None</t>
   </si>
   <si>
     <t xml:space="preserve">[ResNet3D]</t>
@@ -824,28 +824,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1044,419 +1048,419 @@
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="47.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="47.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="20.17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="n">
+      <c r="D3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="D4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="0" t="s">
+      <c r="I5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="0" t="s">
+      <c r="J5" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="0" t="s">
+      <c r="D8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="0" t="s">
+      <c r="D9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="0" t="s">
+      <c r="D10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="0" t="s">
+      <c r="D11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="0" t="s">
+      <c r="D12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="0" t="s">
+      <c r="D13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="0" t="s">
+      <c r="D14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="0" t="s">
+      <c r="D15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="0" t="s">
+      <c r="D16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="0" t="s">
+      <c r="D17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="0" t="s">
+      <c r="D18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="4" t="n">
+      <c r="D19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="0" t="s">
+      <c r="D21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="0" t="s">
+      <c r="D22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="0" t="n">
+      <c r="D23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="0" t="s">
+      <c r="D24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="0" t="n">
+      <c r="D25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="0" t="n">
+      <c r="D26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="0" t="n">
+      <c r="D27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -1479,190 +1483,190 @@
   <dimension ref="A1:K1048576"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="H6" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I6" s="0" t="s">
+      <c r="I6" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J6" s="0" t="s">
+      <c r="J6" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K6" s="0" t="s">
+      <c r="K6" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="0" t="s">
+      <c r="D7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="0" t="s">
+      <c r="I7" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="0" t="s">
+      <c r="D8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="0" t="s">
+      <c r="D9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="1" t="n">
         <v>192</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="1" t="n">
         <v>128</v>
       </c>
     </row>
@@ -1687,220 +1691,220 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0" t="s">
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="0" t="s">
+      <c r="B3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="0" t="s">
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="0" t="s">
+      <c r="B5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="0" t="s">
+      <c r="B6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="0" t="s">
+      <c r="B7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="0" t="s">
+      <c r="B8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="0" t="s">
+      <c r="B9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1924,101 +1928,101 @@
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="0" t="s">
+      <c r="D3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>91</v>
       </c>
     </row>
@@ -2042,79 +2046,79 @@
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="5" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2138,2350 +2142,2350 @@
   <dimension ref="A1:AG48"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="25.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="24.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="15" style="0" width="15.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="41.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="24.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="13.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="13.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="22.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="25" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="40.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="15" style="1" width="15.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="51.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="24.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="13.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="13.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="22.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="25" style="1" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="R1" s="0" t="s">
+      <c r="R1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="S1" s="0" t="s">
+      <c r="S1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T1" s="0" t="s">
+      <c r="T1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="U1" s="0" t="s">
+      <c r="U1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="V1" s="0" t="s">
+      <c r="V1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="W1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="X1" s="0" t="s">
+      <c r="W1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="Y1" s="0" t="s">
+      <c r="Y1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="Z1" s="0" t="s">
+      <c r="Z1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="AA1" s="0" t="s">
+      <c r="AA1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="AB1" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD1" s="0" t="s">
+      <c r="AB1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AE1" s="0" t="s">
+      <c r="AE1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="AF1" s="0" t="s">
+      <c r="AF1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="0" t="s">
+      <c r="AG1" s="1" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M2" s="0" t="s">
+      <c r="M2" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="N2" s="0" t="s">
+      <c r="N2" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="U2" s="0" t="s">
+      <c r="U2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V2" s="0" t="s">
+      <c r="V2" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="W2" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X2" s="5" t="b">
+      <c r="W2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X2" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y2" s="5" t="b">
+      <c r="Y2" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J3" s="0" t="s">
+      <c r="J3" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="L3" s="0" t="s">
+      <c r="L3" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M3" s="0" t="s">
+      <c r="M3" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="N3" s="0" t="s">
+      <c r="N3" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="S3" s="0" t="s">
+      <c r="S3" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="U3" s="0" t="s">
+      <c r="U3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V3" s="0" t="s">
+      <c r="V3" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="W3" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X3" s="5" t="b">
+      <c r="W3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X3" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y3" s="5" t="b">
+      <c r="Y3" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="0" t="s">
+      <c r="J4" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="K4" s="0" t="s">
+      <c r="K4" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="L4" s="0" t="s">
+      <c r="L4" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M4" s="0" t="s">
+      <c r="M4" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="N4" s="0" t="s">
+      <c r="N4" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="U4" s="0" t="s">
+      <c r="U4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V4" s="0" t="s">
+      <c r="V4" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="W4" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X4" s="5" t="b">
+      <c r="W4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X4" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y4" s="5" t="b">
+      <c r="Y4" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="B5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="0" t="s">
+      <c r="E5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="L5" s="0" t="s">
+      <c r="L5" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M5" s="0" t="s">
+      <c r="M5" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="N5" s="0" t="s">
+      <c r="N5" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="V5" s="0" t="s">
+      <c r="V5" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="W5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X5" s="5" t="b">
+      <c r="W5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X5" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y5" s="5" t="b">
+      <c r="Y5" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="0" t="s">
+      <c r="J6" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="M6" s="0" t="s">
+      <c r="M6" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="N6" s="0" t="s">
+      <c r="N6" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="U6" s="0" t="s">
+      <c r="U6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V6" s="0" t="s">
+      <c r="V6" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="W6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X6" s="5" t="b">
+      <c r="W6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X6" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y6" s="5" t="b">
+      <c r="Y6" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="J7" s="0" t="s">
+      <c r="J7" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="L7" s="0" t="s">
+      <c r="L7" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M7" s="0" t="s">
+      <c r="M7" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="N7" s="0" t="s">
+      <c r="N7" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="S7" s="0" t="s">
+      <c r="S7" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="U7" s="0" t="n">
+      <c r="U7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="V7" s="0" t="s">
+      <c r="V7" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="W7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X7" s="5" t="b">
+      <c r="W7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X7" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y7" s="5" t="b">
+      <c r="Y7" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="J8" s="0" t="s">
+      <c r="J8" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="M8" s="0" t="s">
+      <c r="M8" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="N8" s="0" t="s">
+      <c r="N8" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="S8" s="0" t="s">
+      <c r="S8" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="U8" s="0" t="n">
+      <c r="U8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="0" t="s">
+      <c r="V8" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="W8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X8" s="5" t="b">
+      <c r="W8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X8" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y8" s="5" t="b">
+      <c r="Y8" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="J9" s="0" t="s">
+      <c r="J9" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="L9" s="0" t="n">
+      <c r="L9" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="M9" s="0" t="s">
+      <c r="M9" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="N9" s="0" t="s">
+      <c r="N9" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="S9" s="0" t="s">
+      <c r="S9" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="U9" s="0" t="n">
+      <c r="U9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="V9" s="0" t="s">
+      <c r="V9" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="W9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X9" s="5" t="b">
+      <c r="W9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X9" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y9" s="5" t="b">
+      <c r="Y9" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="0" t="s">
+      <c r="B10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="0" t="s">
+      <c r="J10" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="L10" s="0" t="s">
+      <c r="L10" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M10" s="0" t="s">
+      <c r="M10" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="U10" s="0" t="s">
+      <c r="U10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V10" s="0" t="s">
+      <c r="V10" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="X10" s="5" t="b">
+      <c r="X10" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y10" s="5" t="b">
+      <c r="Y10" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J11" s="0" t="s">
+      <c r="J11" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="L11" s="0" t="s">
+      <c r="L11" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M11" s="0" t="s">
+      <c r="M11" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="U11" s="0" t="s">
+      <c r="U11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V11" s="0" t="s">
+      <c r="V11" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="X11" s="5" t="b">
+      <c r="X11" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y11" s="5" t="b">
+      <c r="Y11" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B12" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" s="0" t="s">
+      <c r="B12" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="J12" s="0" t="s">
+      <c r="J12" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="L12" s="0" t="s">
+      <c r="L12" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M12" s="0" t="s">
+      <c r="M12" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="U12" s="0" t="s">
+      <c r="U12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V12" s="0" t="s">
+      <c r="V12" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="X12" s="5" t="b">
+      <c r="X12" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y12" s="5" t="b">
+      <c r="Y12" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J13" s="0" t="s">
+      <c r="J13" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="K13" s="0" t="s">
+      <c r="K13" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="N13" s="0" t="s">
+      <c r="N13" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="U13" s="0" t="s">
+      <c r="U13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V13" s="0" t="s">
+      <c r="V13" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="X13" s="5" t="b">
+      <c r="X13" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y13" s="5" t="b">
+      <c r="Y13" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J14" s="0" t="s">
+      <c r="J14" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="L14" s="0" t="s">
+      <c r="L14" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M14" s="0" t="s">
+      <c r="M14" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="U14" s="0" t="s">
+      <c r="U14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V14" s="0" t="s">
+      <c r="V14" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="X14" s="5" t="b">
+      <c r="X14" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y14" s="5" t="b">
+      <c r="Y14" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="J15" s="0" t="s">
+      <c r="J15" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="L15" s="0" t="s">
+      <c r="L15" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M15" s="0" t="s">
+      <c r="M15" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="U15" s="0" t="s">
+      <c r="U15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V15" s="0" t="s">
+      <c r="V15" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="X15" s="5" t="b">
+      <c r="X15" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y15" s="5" t="b">
+      <c r="Y15" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J16" s="0" t="s">
+      <c r="J16" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="K16" s="0" t="n">
+      <c r="K16" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="U16" s="0" t="s">
+      <c r="U16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="X16" s="5" t="b">
+      <c r="X16" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y16" s="5" t="b">
+      <c r="Y16" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="0" t="s">
+      <c r="J17" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="L17" s="0" t="s">
+      <c r="L17" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="M17" s="0" t="s">
+      <c r="M17" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="U17" s="0" t="s">
+      <c r="U17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V17" s="0" t="s">
+      <c r="V17" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="X17" s="5" t="b">
+      <c r="X17" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y17" s="5" t="b">
+      <c r="Y17" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J18" s="0" t="s">
+      <c r="J18" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="L18" s="0" t="s">
+      <c r="L18" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M18" s="0" t="s">
+      <c r="M18" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="U18" s="0" t="s">
+      <c r="U18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V18" s="0" t="s">
+      <c r="V18" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="X18" s="5" t="b">
+      <c r="X18" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y18" s="5" t="b">
+      <c r="Y18" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J19" s="0" t="s">
+      <c r="J19" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="N19" s="0" t="s">
+      <c r="N19" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="V19" s="0" t="s">
+      <c r="V19" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="X19" s="5" t="b">
+      <c r="X19" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y19" s="5" t="b">
+      <c r="Y19" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B20" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="0" t="s">
+      <c r="B20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G20" s="0" t="s">
+      <c r="G20" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="I20" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
+      <c r="I20" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L20" s="3" t="s">
+      <c r="L20" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="M20" s="3" t="s">
+      <c r="M20" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="N20" s="3" t="s">
+      <c r="N20" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="S20" s="3" t="s">
+      <c r="S20" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="U20" s="3" t="s">
+      <c r="U20" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="V20" s="3" t="s">
+      <c r="V20" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X20" s="5" t="b">
+      <c r="W20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X20" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y20" s="5" t="b">
+      <c r="Y20" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="E21" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="G21" s="0" t="s">
+      <c r="G21" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="I21" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="s">
+      <c r="I21" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="L21" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="M21" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="N21" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="S21" s="3" t="s">
+      <c r="S21" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="U21" s="3" t="s">
+      <c r="U21" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="V21" s="3" t="s">
+      <c r="V21" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X21" s="5" t="b">
+      <c r="W21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y21" s="5" t="b">
+      <c r="Y21" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E22" s="0" t="n">
+      <c r="E22" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="G22" s="0" t="s">
+      <c r="G22" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="I22" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
+      <c r="I22" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="L22" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="M22" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="N22" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="Q22" s="3" t="s">
+      <c r="Q22" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="S22" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="U22" s="3" t="s">
+      <c r="U22" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="V22" s="3" t="s">
+      <c r="V22" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X22" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="5" t="b">
+      <c r="W22" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X22" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B23" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" s="0" t="s">
+      <c r="B23" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="E23" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="G23" s="0" t="s">
+      <c r="G23" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="I23" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="s">
+      <c r="I23" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L23" s="3" t="s">
+      <c r="L23" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="M23" s="3" t="s">
+      <c r="M23" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="N23" s="3" t="s">
+      <c r="N23" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="Q23" s="3" t="s">
+      <c r="Q23" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="S23" s="3" t="s">
+      <c r="S23" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="U23" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="3" t="s">
+      <c r="U23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X23" s="5" t="b">
+      <c r="W23" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X23" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y23" s="5" t="b">
+      <c r="Y23" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="E24" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="I24" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
+      <c r="I24" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="L24" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="M24" s="3" t="s">
+      <c r="M24" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="N24" s="3" t="s">
+      <c r="N24" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="Q24" s="3" t="s">
+      <c r="Q24" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="U24" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" s="3" t="s">
+      <c r="U24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X24" s="5" t="b">
+      <c r="W24" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X24" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y24" s="5" t="b">
+      <c r="Y24" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="E25" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I25" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="s">
+      <c r="I25" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="K25" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="L25" s="3" t="s">
+      <c r="L25" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="M25" s="3" t="s">
+      <c r="M25" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="N25" s="3" t="s">
+      <c r="N25" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="Q25" s="3" t="s">
+      <c r="Q25" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="U25" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" s="3" t="s">
+      <c r="U25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X25" s="5" t="b">
+      <c r="W25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X25" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y25" s="5" t="b">
+      <c r="Y25" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="s">
+      <c r="E26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L26" s="3" t="s">
+      <c r="L26" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="M26" s="3" t="s">
+      <c r="M26" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="N26" s="3" t="s">
+      <c r="N26" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="Q26" s="3" t="s">
+      <c r="Q26" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="U26" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="3" t="s">
+      <c r="U26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X26" s="5" t="b">
+      <c r="W26" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X26" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y26" s="5" t="b">
+      <c r="Y26" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="s">
+      <c r="E27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L27" s="0" t="n">
+      <c r="L27" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="M27" s="3" t="s">
+      <c r="M27" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="N27" s="3" t="s">
+      <c r="N27" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="Q27" s="3" t="s">
+      <c r="Q27" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="U27" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="3" t="s">
+      <c r="U27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X27" s="5" t="b">
+      <c r="W27" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X27" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y27" s="5" t="b">
+      <c r="Y27" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B28" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="0" t="s">
+      <c r="B28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E28" s="0" t="s">
+      <c r="E28" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J28" s="0" t="s">
+      <c r="J28" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="L28" s="0" t="s">
+      <c r="L28" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M28" s="0" t="s">
+      <c r="M28" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="V28" s="0" t="s">
+      <c r="V28" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="W28" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X28" s="5" t="b">
+      <c r="W28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X28" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y28" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AG28" s="0" t="n">
+      <c r="Y28" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG28" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E29" s="0" t="s">
+      <c r="E29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J29" s="0" t="s">
+      <c r="J29" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="K29" s="0" t="s">
+      <c r="K29" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="L29" s="0" t="s">
+      <c r="L29" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="M29" s="0" t="s">
+      <c r="M29" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="R29" s="0" t="s">
+      <c r="R29" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="W29" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X29" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AG29" s="0" t="n">
+      <c r="W29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X29" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG29" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E30" s="0" t="s">
+      <c r="E30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J30" s="0" t="s">
+      <c r="J30" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="L30" s="0" t="s">
+      <c r="L30" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="M30" s="0" t="s">
+      <c r="M30" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="U30" s="0" t="s">
+      <c r="U30" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V30" s="0" t="s">
+      <c r="V30" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="W30" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X30" s="5" t="b">
+      <c r="W30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X30" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y30" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AG30" s="0" t="n">
+      <c r="Y30" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG30" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B31" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="D31" s="0" t="s">
+      <c r="B31" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E31" s="0" t="s">
+      <c r="E31" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="J31" s="0" t="s">
+      <c r="J31" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="L31" s="0" t="s">
+      <c r="L31" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M31" s="0" t="s">
+      <c r="M31" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="U31" s="0" t="s">
+      <c r="U31" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V31" s="0" t="s">
+      <c r="V31" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="W31" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X31" s="5" t="b">
+      <c r="W31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X31" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y31" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AG31" s="0" t="n">
+      <c r="Y31" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG31" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E32" s="0" t="s">
+      <c r="E32" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="J32" s="0" t="s">
+      <c r="J32" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="L32" s="0" t="s">
+      <c r="L32" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M32" s="0" t="s">
+      <c r="M32" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="Q32" s="0" t="s">
+      <c r="Q32" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="U32" s="0" t="s">
+      <c r="U32" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V32" s="0" t="s">
+      <c r="V32" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="W32" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X32" s="5" t="b">
+      <c r="W32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X32" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y32" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AG32" s="0" t="n">
+      <c r="Y32" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG32" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E33" s="0" t="s">
+      <c r="E33" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="J33" s="0" t="s">
+      <c r="J33" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="L33" s="0" t="s">
+      <c r="L33" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="M33" s="0" t="s">
+      <c r="M33" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="O33" s="0" t="s">
+      <c r="O33" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="U33" s="0" t="s">
+      <c r="U33" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V33" s="0" t="s">
+      <c r="V33" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="W33" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X33" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AG33" s="0" t="n">
+      <c r="W33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X33" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AG33" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B34" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="0" t="s">
+      <c r="B34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E34" s="0" t="n">
+      <c r="E34" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="J34" s="0" t="s">
+      <c r="J34" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="L34" s="0" t="s">
+      <c r="L34" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M34" s="0" t="s">
+      <c r="M34" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="U34" s="0" t="s">
+      <c r="U34" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V34" s="0" t="s">
+      <c r="V34" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="W34" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X34" s="5" t="b">
+      <c r="W34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X34" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y34" s="5" t="b">
+      <c r="Y34" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B35" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="0" t="s">
+      <c r="B35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E35" s="0" t="n">
+      <c r="E35" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="G35" s="0" t="s">
+      <c r="G35" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="I35" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="s">
+      <c r="I35" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L35" s="3" t="s">
+      <c r="L35" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="M35" s="3" t="s">
+      <c r="M35" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="N35" s="3" t="s">
+      <c r="N35" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="S35" s="3" t="s">
+      <c r="S35" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="U35" s="3" t="s">
+      <c r="U35" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="V35" s="3" t="s">
+      <c r="V35" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X35" s="5" t="b">
+      <c r="W35" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X35" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y35" s="5" t="b">
+      <c r="Y35" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E36" s="0" t="n">
+      <c r="E36" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="G36" s="0" t="s">
+      <c r="G36" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="I36" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="s">
+      <c r="I36" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L36" s="0" t="n">
+      <c r="L36" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="M36" s="3" t="s">
+      <c r="M36" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="N36" s="3" t="s">
+      <c r="N36" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="S36" s="3" t="s">
+      <c r="S36" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="U36" s="3" t="s">
+      <c r="U36" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="V36" s="3" t="s">
+      <c r="V36" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W36" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X36" s="5" t="b">
+      <c r="W36" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X36" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y36" s="5" t="b">
+      <c r="Y36" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B37" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="0" t="s">
+      <c r="B37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E37" s="0" t="n">
+      <c r="E37" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="G37" s="0" t="s">
+      <c r="G37" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="I37" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="s">
+      <c r="I37" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L37" s="0" t="n">
+      <c r="L37" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="M37" s="3" t="s">
+      <c r="M37" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="N37" s="3" t="s">
+      <c r="N37" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="O37" s="3" t="s">
+      <c r="O37" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="S37" s="3" t="s">
+      <c r="S37" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="U37" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" s="3" t="s">
+      <c r="U37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W37" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X37" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="5" t="b">
+      <c r="W37" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X37" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B38" s="0" t="n">
+      <c r="B38" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E38" s="0" t="n">
+      <c r="E38" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="G38" s="0" t="s">
+      <c r="G38" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="I38" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="s">
+      <c r="I38" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L38" s="0" t="n">
+      <c r="L38" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="M38" s="3" t="s">
+      <c r="M38" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="N38" s="3" t="s">
+      <c r="N38" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="O38" s="3" t="s">
+      <c r="O38" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="S38" s="3" t="s">
+      <c r="S38" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="U38" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" s="3" t="s">
+      <c r="U38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W38" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X38" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Y38" s="5" t="b">
+      <c r="W38" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X38" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B39" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="0" t="s">
+      <c r="B39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E39" s="0" t="n">
+      <c r="E39" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="I39" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="s">
+      <c r="I39" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L39" s="0" t="n">
+      <c r="L39" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="M39" s="0" t="n">
+      <c r="M39" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="N39" s="3" t="s">
+      <c r="N39" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="P39" s="0" t="n">
+      <c r="P39" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="U39" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V39" s="3" t="s">
+      <c r="U39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W39" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X39" s="4" t="n">
+      <c r="W39" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X39" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y39" s="4" t="n">
+      <c r="Y39" s="5" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E40" s="0" t="n">
+      <c r="E40" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="I40" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="s">
+      <c r="I40" s="1" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L40" s="3" t="s">
+      <c r="L40" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="M40" s="3" t="s">
+      <c r="M40" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="N40" s="3" t="s">
+      <c r="N40" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="P40" s="0" t="n">
+      <c r="P40" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q40" s="3" t="s">
+      <c r="Q40" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="U40" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V40" s="3" t="s">
+      <c r="U40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W40" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X40" s="5" t="n">
+      <c r="W40" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X40" s="1" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y40" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z40" s="0" t="n">
+      <c r="Y40" s="1" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z40" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B41" s="0" t="n">
+      <c r="B41" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E41" s="0" t="n">
+      <c r="E41" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="I41" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="s">
+      <c r="I41" s="1" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L41" s="0" t="n">
+      <c r="L41" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="M41" s="3" t="s">
+      <c r="M41" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="N41" s="3" t="s">
+      <c r="N41" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="P41" s="0" t="n">
+      <c r="P41" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="3" t="s">
+      <c r="Q41" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="U41" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V41" s="3" t="s">
+      <c r="U41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V41" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X41" s="5" t="n">
+      <c r="W41" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X41" s="1" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y41" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z41" s="0" t="n">
+      <c r="Y41" s="1" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z41" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B42" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="D42" s="0" t="s">
+      <c r="B42" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E42" s="0" t="n">
+      <c r="E42" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="I42" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="s">
+      <c r="I42" s="1" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L42" s="0" t="n">
+      <c r="L42" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="M42" s="0" t="n">
+      <c r="M42" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="N42" s="3" t="s">
+      <c r="N42" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="P42" s="0" t="n">
+      <c r="P42" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" s="3" t="s">
+      <c r="Q42" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="U42" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V42" s="3" t="s">
+      <c r="U42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X42" s="5" t="n">
+      <c r="W42" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X42" s="1" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y42" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z42" s="0" t="n">
+      <c r="Y42" s="1" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z42" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E43" s="0" t="n">
+      <c r="E43" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="I43" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="s">
+      <c r="I43" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L43" s="0" t="n">
+      <c r="L43" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="M43" s="0" t="n">
+      <c r="M43" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="N43" s="3" t="s">
+      <c r="N43" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="P43" s="0" t="n">
+      <c r="P43" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q43" s="3" t="s">
+      <c r="Q43" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="U43" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V43" s="3" t="s">
+      <c r="U43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X43" s="4" t="n">
+      <c r="W43" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X43" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y43" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z43" s="0" t="n">
+      <c r="Y43" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z43" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B44" s="0" t="n">
+      <c r="B44" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D44" s="0" t="s">
+      <c r="D44" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E44" s="0" t="n">
+      <c r="E44" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I44" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="s">
+      <c r="I44" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L44" s="0" t="n">
+      <c r="L44" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="M44" s="0" t="n">
+      <c r="M44" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="N44" s="3" t="s">
+      <c r="N44" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="P44" s="0" t="n">
+      <c r="P44" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q44" s="3" t="s">
+      <c r="Q44" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="U44" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V44" s="3" t="s">
+      <c r="U44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X44" s="4" t="n">
+      <c r="W44" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X44" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y44" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z44" s="0" t="n">
+      <c r="Y44" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z44" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B45" s="0" t="n">
+      <c r="B45" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="D45" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E45" s="0" t="n">
+      <c r="E45" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="I45" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="s">
+      <c r="I45" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L45" s="0" t="n">
+      <c r="L45" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="M45" s="0" t="n">
+      <c r="M45" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="N45" s="3" t="s">
+      <c r="N45" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="P45" s="0" t="n">
+      <c r="P45" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q45" s="3" t="s">
+      <c r="Q45" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="U45" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V45" s="3" t="s">
+      <c r="U45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X45" s="4" t="n">
+      <c r="W45" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X45" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y45" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z45" s="0" t="n">
+      <c r="Y45" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z45" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B46" s="0" t="n">
+      <c r="B46" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D46" s="0" t="s">
+      <c r="D46" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E46" s="0" t="n">
+      <c r="E46" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="I46" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J46" s="3" t="s">
+      <c r="I46" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L46" s="0" t="n">
+      <c r="L46" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="M46" s="0" t="n">
+      <c r="M46" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="N46" s="3" t="s">
+      <c r="N46" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="P46" s="0" t="n">
+      <c r="P46" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q46" s="3" t="s">
+      <c r="Q46" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="U46" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V46" s="3" t="s">
+      <c r="U46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X46" s="4" t="n">
+      <c r="W46" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X46" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y46" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z46" s="0" t="n">
+      <c r="Y46" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z46" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B47" s="0" t="n">
+      <c r="B47" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C47" s="0" t="s">
+      <c r="C47" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D47" s="0" t="s">
+      <c r="D47" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E47" s="0" t="n">
+      <c r="E47" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="G47" s="0" t="s">
+      <c r="G47" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="I47" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="s">
+      <c r="I47" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L47" s="0" t="n">
+      <c r="L47" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="M47" s="0" t="n">
+      <c r="M47" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="N47" s="3" t="s">
+      <c r="N47" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="P47" s="0" t="n">
+      <c r="P47" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="S47" s="3" t="s">
+      <c r="S47" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="U47" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" s="3" t="s">
+      <c r="U47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X47" s="4" t="n">
+      <c r="W47" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X47" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y47" s="4" t="n">
+      <c r="Y47" s="5" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B48" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="0" t="s">
+      <c r="B48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E48" s="0" t="s">
+      <c r="E48" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G48" s="0" t="s">
+      <c r="G48" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="I48" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="s">
+      <c r="I48" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L48" s="0" t="n">
+      <c r="L48" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="M48" s="0" t="n">
+      <c r="M48" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="O48" s="3" t="s">
+      <c r="O48" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="S48" s="3" t="s">
+      <c r="S48" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U48" s="3" t="s">
+      <c r="U48" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="V48" s="3" t="s">
+      <c r="V48" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X48" s="4" t="n">
+      <c r="W48" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X48" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y48" s="4" t="n">
+      <c r="Y48" s="5" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4505,89 +4509,89 @@
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="19.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="48.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="1" width="19.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="0" t="s">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="0" t="n">
+      <c r="D3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="0" t="n">
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="n">
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4595,28 +4599,28 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E9" s="4"/>
+      <c r="E9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E12" s="4"/>
+      <c r="E12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E13" s="4"/>
+      <c r="E13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E16" s="4"/>
+      <c r="E16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E17" s="4"/>
+      <c r="E17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E20" s="4"/>
+      <c r="E20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4639,148 +4643,148 @@
   <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="25.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="17.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="17" style="0" width="23.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="25.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="17.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="17" style="1" width="23.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="R1" s="0" t="s">
+      <c r="R1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="S1" s="0" t="s">
+      <c r="S1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T1" s="0" t="s">
+      <c r="T1" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="U1" s="0" t="s">
+      <c r="U1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="V1" s="0" t="s">
+      <c r="V1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="W1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="X1" s="0" t="s">
+      <c r="W1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="Y1" s="0" t="s">
+      <c r="Y1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="Z1" s="0" t="s">
+      <c r="Z1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="AA1" s="0" t="s">
+      <c r="AA1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="AB1" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD1" s="0" t="s">
+      <c r="AB1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AE1" s="0" t="s">
+      <c r="AE1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="AF1" s="0" t="s">
+      <c r="AF1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="0" t="s">
+      <c r="AG1" s="1" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="M2" s="0" t="n">
+      <c r="M2" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="N2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="0" t="s">
+      <c r="N2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="T2" s="0" t="s">
+      <c r="T2" s="1" t="s">
         <v>234</v>
       </c>
     </row>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -686,13 +686,13 @@
     <t xml:space="preserve">test</t>
   </si>
   <si>
-    <t xml:space="preserve">drli_short, lidc_short,kits23_short</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{1:0,2:1,3:1},{1:1,2:1,3:2,4:2,5:2},{1:1,2:2,3:2}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSL.label_region:TSL.lungs,None,None</t>
+    <t xml:space="preserve">drli_short, lidc_short,kits23_short,nodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{1:0,2:1,3:1},{1:1,2:1,3:2,4:2,5:2},{1:1,2:2,3:2},None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL.label_region:TSL.lungs,None,None,None</t>
   </si>
   <si>
     <t xml:space="preserve">[ResNet3D]</t>
@@ -2145,7 +2145,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="40.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8.67"/>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -2145,7 +2145,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="40.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8.67"/>
@@ -2153,7 +2153,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="15" style="1" width="15.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="15.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="30.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="1" width="15.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="51.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="24.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="8.67"/>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="237">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -491,229 +491,235 @@
     <t xml:space="preserve">vip_label</t>
   </si>
   <si>
+    <t xml:space="preserve">localiser_regions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remapping_lbd_kbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remapping_whole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remapping_imported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remapping_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spacing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">use_fg_indices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nnz_allowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plan_valid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plan_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">periodict_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nodesthick,nodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8,.8,1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$cold_storage_folder/predictions/totalseg/LITS-1439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL.label_region:TSL.label_region,TSL.label_region:TSL.label_region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1, source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lits,drli,litq,litqsmall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8,0.8,1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4, lbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lungs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lidc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL.label_region:TSL.lungs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{1:1,2:1,3:2,4:3,5:3}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5, lbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{1:1,2:1,3:1,4:1,5:1}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.75, 0.75,0.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">totalseg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">whole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL.label_full:TSL.label_region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5, 1.5,1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,1,1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL.label_full:TSL.label_minimal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uls23_bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sourcepbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colonmsd10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL.label_region:TSL.gi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pancreas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pancreasmsd07, curvaspdac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DS.pancreasmsd07/lms,$cold_storage_folder/predictions/totalseg/LITS-1437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{1:0,2:1},None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{1:3},TSL.label_minimal: TSL.pancreas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kidneys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all labels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kits23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abdomen, pelvis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all labels, abdomen lbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL.label_region:TSL.abdomen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drli_short, lidc_short,kits23_short,nodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{1:0,2:1,3:1},{1:1,2:1,3:2,4:2,5:2},{1:1,2:2,3:2},None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL.label_region:TSL.lungs,None,None,None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ResNet3D]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ResNet3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resnet_depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[10,18,34,50,101,152]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_scalars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pretrained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expand_mode</t>
+  </si>
+  <si>
     <t xml:space="preserve">remapping_lbd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remapping_whole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remapping_imported</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remapping_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spacing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">use_fg_indices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nnz_allowed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plan_valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plan_test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">periodict_test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nodesthick,nodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8,.8,1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$cold_storage_folder/predictions/totalseg/LITS-1439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lbd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSL.label_region:TSL.label_region,TSL.label_region:TSL.label_region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">baseline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1, source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">liver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lits,drli,litq,litqsmall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8,0.8,1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pbd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4, lbd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lungs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lidc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSL.label_region:TSL.lungs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{1:1,2:1,3:2,4:3,5:3}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5, lbd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{1:1,2:1,3:1,4:1,5:1}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75, 0.75,0.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">totalseg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">whole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSL.label_full:TSL.label_region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5, 1.5,1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,1,1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSL.label_full:TSL.label_minimal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uls23_bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sourcepbd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">colon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">colonmsd10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSL.label_region:TSL.gi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pancreas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pancreasmsd07, curvaspdac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DS.pancreasmsd07/lms,$cold_storage_folder/predictions/totalseg/LITS-1437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{1:0,2:1},None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{1:3},TSL.label_minimal: TSL.pancreas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kidneys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">all labels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kits23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{1:1,2:2,3:2}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8,.8,0.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">all labels, abdomen lbd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSL.label_region:TSL.abdomen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drli_short, lidc_short,kits23_short,nodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{1:0,2:1,3:1},{1:1,2:1,3:2,4:2,5:2},{1:1,2:2,3:2},None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSL.label_region:TSL.lungs,None,None,None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ResNet3D]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ResNet3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resnet_depth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[10,18,34,50,101,152]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_scalars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pretrained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expand_mode</t>
   </si>
   <si>
     <t xml:space="preserve">remapping_train_resnet</t>
@@ -2139,11 +2145,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AG48"/>
+  <dimension ref="A1:AH42"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="8.67"/>
@@ -2154,15 +2160,17 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="15.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="30.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="1" width="15.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="51.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="24.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="13.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="13.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="22.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="25" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="22.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="15.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="21.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="27.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="29.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="24.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="13.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="13.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="22.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="26" style="1" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2227,16 +2235,16 @@
         <v>157</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="W1" s="1" t="s">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>160</v>
@@ -2248,728 +2256,731 @@
         <v>162</v>
       </c>
       <c r="AB1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AC1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="AD1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="1" t="s">
-        <v>163</v>
+      <c r="AH1" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="U2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V2" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="W2" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X2" s="6" t="b">
+      <c r="Y2" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y2" s="6" t="b">
+      <c r="Z2" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="U3" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="V3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V3" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="W3" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="X3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X3" s="6" t="b">
+      <c r="Y3" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y3" s="6" t="b">
+      <c r="Z3" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="U4" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="V4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V4" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="W4" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="X4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X4" s="6" t="b">
+      <c r="Y4" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y4" s="6" t="b">
+      <c r="Z4" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="V5" s="1" t="s">
         <v>170</v>
       </c>
       <c r="W5" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="X5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X5" s="6" t="b">
+      <c r="Y5" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y5" s="6" t="b">
+      <c r="Z5" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="U6" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="V6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V6" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="W6" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="X6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X6" s="6" t="b">
+      <c r="Y6" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y6" s="6" t="b">
+      <c r="Z6" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="V7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W7" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="U7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="W7" s="1" t="s">
+      <c r="X7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X7" s="6" t="b">
+      <c r="Y7" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y7" s="6" t="b">
+      <c r="Z7" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="U8" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="V8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="W8" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="X8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X8" s="6" t="b">
+      <c r="Y8" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y8" s="6" t="b">
+      <c r="Z8" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>75</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L9" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="U9" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="V9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="V9" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="W9" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="X9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X9" s="6" t="b">
+      <c r="Y9" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y9" s="6" t="b">
+      <c r="Z9" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="U10" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="V10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V10" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="X10" s="6" t="b">
+      <c r="W10" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y10" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y10" s="6" t="b">
+      <c r="Z10" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="U11" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="V11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V11" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="X11" s="6" t="b">
+      <c r="W11" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y11" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y11" s="6" t="b">
+      <c r="Z11" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="U12" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="V12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V12" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="X12" s="6" t="b">
+      <c r="W12" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y12" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y12" s="6" t="b">
+      <c r="Z12" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="U13" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="V13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V13" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="X13" s="6" t="b">
+      <c r="W13" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y13" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y13" s="6" t="b">
+      <c r="Z13" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="U14" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="V14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V14" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="X14" s="6" t="b">
+      <c r="W14" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y14" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y14" s="6" t="b">
+      <c r="Z14" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="U15" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="V15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V15" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="X15" s="6" t="b">
+      <c r="W15" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y15" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y15" s="6" t="b">
+      <c r="Z15" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="U16" s="1" t="s">
+      <c r="V16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="X16" s="6" t="b">
+      <c r="Y16" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y16" s="6" t="b">
+      <c r="Z16" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="U17" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="V17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V17" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="X17" s="6" t="b">
+      <c r="W17" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y17" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y17" s="6" t="b">
+      <c r="Z17" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="U18" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="V18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V18" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="X18" s="6" t="b">
+      <c r="W18" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y18" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y18" s="6" t="b">
+      <c r="Z18" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>40</v>
@@ -2978,250 +2989,250 @@
         <v>20</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="V19" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="X19" s="6" t="b">
+      <c r="W19" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y19" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y19" s="6" t="b">
+      <c r="Z19" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I20" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="V20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="W20" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="I20" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="S20" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="U20" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="V20" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="W20" s="4" t="s">
+      <c r="X20" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="X20" s="6" t="b">
+      <c r="Y20" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y20" s="6" t="b">
+      <c r="Z20" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I21" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="T21" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="V21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="W21" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="I21" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="S21" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="U21" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="V21" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="W21" s="4" t="s">
+      <c r="X21" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="X21" s="6" t="b">
+      <c r="Y21" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y21" s="6" t="b">
+      <c r="Z21" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I22" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="T22" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="V22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="W22" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="I22" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q22" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="S22" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="U22" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="V22" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="W22" s="4" t="s">
+      <c r="X22" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="X22" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
       <c r="Y22" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I23" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="R23" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="T23" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="V23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="I23" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="N23" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q23" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="S23" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="U23" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="W23" s="4" t="s">
+      <c r="X23" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="X23" s="6" t="b">
+      <c r="Y23" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y23" s="6" t="b">
+      <c r="Z23" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>50</v>
@@ -3231,47 +3242,47 @@
         <v>0</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q24" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="U24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" s="4" t="s">
         <v>170</v>
       </c>
+      <c r="R24" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="V24" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="W24" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="X24" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="X24" s="6" t="b">
+      <c r="Y24" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y24" s="6" t="b">
+      <c r="Z24" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>20</v>
@@ -3281,50 +3292,50 @@
         <v>0</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K25" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="R25" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="L25" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="N25" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q25" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="U25" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" s="4" t="s">
-        <v>170</v>
+      <c r="V25" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="W25" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="X25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="X25" s="6" t="b">
+      <c r="Y25" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y25" s="6" t="b">
+      <c r="Z25" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>0</v>
@@ -3334,47 +3345,47 @@
         <v>0</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q26" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="U26" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="4" t="s">
         <v>170</v>
       </c>
+      <c r="R26" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="V26" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="W26" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="X26" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="X26" s="6" t="b">
+      <c r="Y26" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y26" s="6" t="b">
+      <c r="Z26" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>0</v>
@@ -3384,569 +3395,569 @@
         <v>0</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L27" s="1" t="n">
         <v>96</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q27" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="U27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="R27" s="4" t="s">
         <v>191</v>
       </c>
+      <c r="V27" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="W27" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="X27" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="X27" s="6" t="b">
+      <c r="Y27" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y27" s="6" t="b">
+      <c r="Z27" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="V28" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W28" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="X28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X28" s="6" t="b">
+      <c r="Y28" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y28" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AG28" s="1" t="n">
+      <c r="Z28" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH28" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>42</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="W29" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="X29" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X29" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
       <c r="Y29" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="AG29" s="1" t="n">
+      <c r="Z29" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH29" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B30" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="U30" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="V30" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V30" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="W30" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="X30" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X30" s="6" t="b">
+      <c r="Y30" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y30" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AG30" s="1" t="n">
+      <c r="Z30" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH30" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B31" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="U31" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="V31" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V31" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="W31" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="X31" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X31" s="6" t="b">
+      <c r="Y31" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y31" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AG31" s="1" t="n">
+      <c r="Z31" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH31" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B32" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q32" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="W32" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="U32" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="V32" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="W32" s="1" t="s">
+      <c r="X32" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X32" s="6" t="b">
+      <c r="Y32" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y32" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AG32" s="1" t="n">
+      <c r="Z32" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH32" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L33" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="O33" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="M33" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="O33" s="1" t="s">
+      <c r="V33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="W33" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="U33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="V33" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="W33" s="1" t="s">
+      <c r="X33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X33" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
       <c r="Y33" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="AG33" s="1" t="n">
+      <c r="Z33" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH33" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="U34" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="V34" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V34" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="W34" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="X34" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X34" s="6" t="b">
+      <c r="Y34" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y34" s="6" t="b">
+      <c r="Z34" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G35" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I35" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="T35" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="V35" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="W35" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="I35" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L35" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="M35" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="N35" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="S35" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="U35" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="V35" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="W35" s="4" t="s">
+      <c r="X35" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="X35" s="6" t="b">
+      <c r="Y35" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y35" s="6" t="b">
+      <c r="Z35" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B36" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I36" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L36" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="S36" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="U36" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="T36" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="V36" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="V36" s="4" t="s">
-        <v>170</v>
-      </c>
       <c r="W36" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="X36" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="X36" s="6" t="b">
+      <c r="Y36" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y36" s="6" t="b">
+      <c r="Z36" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I37" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L37" s="1" t="n">
         <v>128</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="S37" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="U37" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" s="4" t="s">
-        <v>170</v>
+      <c r="T37" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="V37" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="W37" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="X37" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="X37" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
       <c r="Y37" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z37" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B38" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>100</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I38" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="S38" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="U38" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" s="4" t="s">
-        <v>170</v>
+      <c r="T38" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="V38" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="W38" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="X38" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="X38" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
       <c r="Y38" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z38" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>50</v>
@@ -3956,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L39" s="1" t="n">
         <v>160</v>
@@ -3965,529 +3976,191 @@
         <v>96</v>
       </c>
       <c r="N39" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P39" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="U39" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V39" s="4" t="s">
-        <v>170</v>
+      <c r="Q39" s="0"/>
+      <c r="V39" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="W39" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="X39" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="X39" s="5" t="n">
+      <c r="Y39" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y39" s="5" t="n">
+      <c r="Z39" s="5" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B40" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="I40" s="1" t="n">
+      <c r="I40" s="5" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L40" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="M40" s="4" t="s">
-        <v>168</v>
+        <v>215</v>
+      </c>
+      <c r="L40" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="M40" s="1" t="n">
+        <v>96</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q40" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="U40" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V40" s="4" t="s">
-        <v>170</v>
+        <v>3</v>
+      </c>
+      <c r="Q40" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="V40" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="W40" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="X40" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="X40" s="1" t="n">
+      <c r="Y40" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y40" s="1" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z40" s="1" t="n">
-        <v>6</v>
+      <c r="Z40" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I41" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I41" s="5" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="M41" s="4" t="s">
-        <v>168</v>
+      <c r="M41" s="1" t="n">
+        <v>96</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q41" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="U41" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V41" s="4" t="s">
-        <v>170</v>
+        <v>3</v>
+      </c>
+      <c r="T41" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="V41" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="W41" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="X41" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="X41" s="1" t="n">
+      <c r="Y41" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y41" s="1" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z41" s="1" t="n">
-        <v>6</v>
+      <c r="Z41" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E42" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I42" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I42" s="5" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="M42" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="N42" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="P42" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q42" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="U42" s="1" t="n">
-        <v>1</v>
+      <c r="O42" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="T42" s="4" t="s">
+        <v>222</v>
       </c>
       <c r="V42" s="4" t="s">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="W42" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="X42" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="X42" s="1" t="n">
+      <c r="Y42" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Y42" s="1" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z42" s="1" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B43" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E43" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I43" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L43" s="1" t="n">
-        <v>160</v>
-      </c>
-      <c r="M43" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="N43" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="P43" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q43" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="U43" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V43" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="W43" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="X43" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Y43" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z43" s="1" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B44" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E44" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L44" s="1" t="n">
-        <v>160</v>
-      </c>
-      <c r="M44" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="N44" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="P44" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q44" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="U44" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V44" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="W44" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="X44" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Y44" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z44" s="1" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B45" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="I45" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L45" s="1" t="n">
-        <v>160</v>
-      </c>
-      <c r="M45" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="N45" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="P45" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q45" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="U45" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V45" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="W45" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="X45" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Y45" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z45" s="1" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B46" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E46" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="I46" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L46" s="1" t="n">
-        <v>192</v>
-      </c>
-      <c r="M46" s="1" t="n">
-        <v>128</v>
-      </c>
-      <c r="N46" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="P46" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q46" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="U46" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V46" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="W46" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="X46" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Y46" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z46" s="1" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B47" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I47" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L47" s="1" t="n">
-        <v>160</v>
-      </c>
-      <c r="M47" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="N47" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="P47" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="S47" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="U47" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="W47" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="X47" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Y47" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B48" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I48" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L48" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="M48" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="O48" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="S48" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="U48" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="V48" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="W48" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="X48" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Y48" s="5" t="n">
+      <c r="Z42" s="5" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4540,7 +4213,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>12</v>
@@ -4549,15 +4222,15 @@
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>12</v>
@@ -4571,7 +4244,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -4582,7 +4255,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>19</v>
@@ -4671,7 +4344,7 @@
         <v>142</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>144</v>
@@ -4704,37 +4377,37 @@
         <v>153</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>154</v>
+        <v>230</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>74</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>4</v>
@@ -4752,27 +4425,27 @@
         <v>5</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L2" s="1" t="n">
         <v>64</v>
@@ -4784,10 +4457,10 @@
         <v>0</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="model_params" sheetId="1" state="visible" r:id="rId3"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="227">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -251,259 +251,229 @@
     <t xml:space="preserve">batch_size</t>
   </si>
   <si>
+    <t xml:space="preserve">fgbg_ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[None,tumour]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[4,2,2,2,2,2]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fake_tumours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">random_sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0,1.]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cache_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ds_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tune_p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manual_p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contrast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">double_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.0,1.0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.25,0.5],[1.5,2.0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.7,1.3]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-1,-0.5],[0.5,1.0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-1.0,1.0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute value shift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noise_ub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0,.25],[.25,.5]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0,.25]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noise_monai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.05,.25]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brightness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.5,1.0],[1.0,2.0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.7,2.0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rotate_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0,0.785]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.20,0.2,0.15]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">translate_factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.05,0.15]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uniform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">translate worsens dice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scale_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.15,0.15,0.15]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.,1.]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ce_weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lambda_ce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lambda_dice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">softmax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">include_background</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mnemonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">datasources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expand_by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fg_indices_exclude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imported_folder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lm_groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">merge_imported_labels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source_plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patch_dim0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patch_dim1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patch_overlap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remapping_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vip_label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">localiser_regions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remapping_lbd_kbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remapping_whole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remapping_imported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remapping_train</t>
+  </si>
+  <si>
     <t xml:space="preserve">samples_per_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">src_dims</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[192,192,128]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[192,192,96]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[256,256,64]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[160,160,160]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[192,192,160]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[220,220,110]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[256,256,128]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fgbg_ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[None,tumour]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[4,2,2,2,2,2]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fake_tumours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">random_sample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0,1.]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cache_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ds_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">src_dim0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">src_dim1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tune_p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manual_p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contrast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">double_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.0,1.0]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.25,0.5],[1.5,2.0]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.7,1.3]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-1,-0.5],[0.5,1.0]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-1.0,1.0]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">absolute value shift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">noise_ub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0,.25],[.25,.5]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0,.25]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">noise_monai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.05,.25]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">noise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brightness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.5,1.0],[1.0,2.0]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.7,2.0]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rotate_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0,0.785]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.20,0.2,0.35]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">translate_factor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.05,0.15]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uniform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">translate worsens dice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scale_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.15,0.15,0.15]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.,1.]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ce_weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lambda_ce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lambda_dice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reduction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">softmax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">include_background</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mnemonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">datasources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expand_by</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fg_indices_exclude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">imported_folder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lm_groups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">merge_imported_labels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">source_plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patch_dim0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patch_dim1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patch_overlap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remapping_source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vip_label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">localiser_regions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remapping_lbd_kbd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remapping_whole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remapping_imported</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remapping_train</t>
   </si>
   <si>
     <t xml:space="preserve">spacing</t>
@@ -1489,6 +1459,7 @@
   <dimension ref="A1:K1048576"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24.83"/>
   </cols>
   <sheetData>
@@ -1561,123 +1532,77 @@
       <c r="A5" s="1" t="s">
         <v>74</v>
       </c>
+      <c r="B5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="E5" s="1" t="s">
-        <v>50</v>
+        <v>70</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>35</v>
+        <v>82</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1048569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1712,13 +1637,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>4</v>
@@ -1729,114 +1654,114 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>0.1</v>
@@ -1847,53 +1772,53 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0</v>
@@ -1902,7 +1827,7 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>19</v>
@@ -1932,6 +1857,10 @@
   </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="22.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.61"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
@@ -1950,32 +1879,32 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>0</v>
@@ -1984,29 +1913,29 @@
         <v>35</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>0</v>
@@ -2017,19 +1946,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2068,12 +1997,12 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
@@ -2081,7 +2010,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>20</v>
@@ -2089,7 +2018,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -2100,18 +2029,18 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>0</v>
@@ -2122,7 +2051,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="E7" s="5" t="n">
         <f aca="false">FALSE()</f>
@@ -2175,88 +2104,88 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="X1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="AC1" s="1" t="s">
         <v>4</v>
@@ -2274,39 +2203,39 @@
         <v>5</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="V2" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X2" s="1" t="s">
         <v>4</v>
@@ -2322,43 +2251,43 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="V3" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X3" s="1" t="s">
         <v>4</v>
@@ -2374,37 +2303,37 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="V4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X4" s="1" t="s">
         <v>4</v>
@@ -2420,31 +2349,31 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X5" s="1" t="s">
         <v>4</v>
@@ -2460,34 +2389,34 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="V6" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X6" s="1" t="s">
         <v>4</v>
@@ -2503,40 +2432,40 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="V7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X7" s="1" t="s">
         <v>4</v>
@@ -2552,40 +2481,40 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="V8" s="1" t="n">
         <v>2</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X8" s="1" t="s">
         <v>4</v>
@@ -2601,40 +2530,40 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>75</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L9" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="V9" s="1" t="n">
         <v>2</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X9" s="1" t="s">
         <v>4</v>
@@ -2650,34 +2579,34 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="V10" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="Y10" s="6" t="b">
         <f aca="false">TRUE()</f>
@@ -2690,28 +2619,28 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="V11" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="Y11" s="6" t="b">
         <f aca="false">TRUE()</f>
@@ -2724,31 +2653,31 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="V12" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="Y12" s="6" t="b">
         <f aca="false">TRUE()</f>
@@ -2761,28 +2690,28 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="V13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="Y13" s="6" t="b">
         <f aca="false">TRUE()</f>
@@ -2795,31 +2724,31 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="V14" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="Y14" s="6" t="b">
         <f aca="false">TRUE()</f>
@@ -2832,31 +2761,31 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="V15" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="Y15" s="6" t="b">
         <f aca="false">TRUE()</f>
@@ -2869,16 +2798,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>7</v>
@@ -2897,31 +2826,31 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="V17" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="Y17" s="6" t="b">
         <f aca="false">TRUE()</f>
@@ -2934,34 +2863,34 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="V18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="Y18" s="6" t="b">
         <f aca="false">TRUE()</f>
@@ -2974,13 +2903,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>40</v>
@@ -2989,13 +2918,13 @@
         <v>20</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="Y19" s="6" t="b">
         <f aca="false">TRUE()</f>
@@ -3008,44 +2937,44 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="I20" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="V20" s="4" t="s">
         <v>50</v>
       </c>
       <c r="W20" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X20" s="4" t="s">
         <v>4</v>
@@ -3061,44 +2990,44 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="I21" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="V21" s="4" t="s">
         <v>50</v>
       </c>
       <c r="W21" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X21" s="4" t="s">
         <v>4</v>
@@ -3114,47 +3043,47 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="I22" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="V22" s="4" t="s">
         <v>50</v>
       </c>
       <c r="W22" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X22" s="4" t="s">
         <v>4</v>
@@ -3170,47 +3099,47 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="I23" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="V23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="W23" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X23" s="4" t="s">
         <v>4</v>
@@ -3226,13 +3155,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>50</v>
@@ -3242,25 +3171,25 @@
         <v>0</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="V24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="W24" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X24" s="4" t="s">
         <v>4</v>
@@ -3276,13 +3205,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>20</v>
@@ -3292,28 +3221,28 @@
         <v>0</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="V25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="W25" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X25" s="4" t="s">
         <v>4</v>
@@ -3329,13 +3258,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>0</v>
@@ -3345,25 +3274,25 @@
         <v>0</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="V26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="W26" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X26" s="4" t="s">
         <v>4</v>
@@ -3379,13 +3308,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>0</v>
@@ -3395,25 +3324,25 @@
         <v>0</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L27" s="1" t="n">
         <v>96</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="V27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="W27" s="4" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="X27" s="4" t="s">
         <v>4</v>
@@ -3429,28 +3358,28 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X28" s="1" t="s">
         <v>4</v>
@@ -3469,31 +3398,31 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>42</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="X29" s="1" t="s">
         <v>4</v>
@@ -3512,31 +3441,31 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="B30" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="V30" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="X30" s="1" t="s">
         <v>4</v>
@@ -3555,31 +3484,31 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="B31" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="V31" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="X31" s="1" t="s">
         <v>4</v>
@@ -3598,34 +3527,34 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="B32" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="V32" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="X32" s="1" t="s">
         <v>4</v>
@@ -3644,34 +3573,34 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="V33" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="X33" s="1" t="s">
         <v>4</v>
@@ -3690,31 +3619,31 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="B34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="V34" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="X34" s="1" t="s">
         <v>4</v>
@@ -3730,44 +3659,44 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="I35" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N35" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="T35" s="4" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="V35" s="4" t="s">
         <v>50</v>
       </c>
       <c r="W35" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X35" s="4" t="s">
         <v>4</v>
@@ -3783,44 +3712,44 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B36" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="I36" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L36" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="T36" s="4" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="V36" s="4" t="s">
         <v>50</v>
       </c>
       <c r="W36" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X36" s="4" t="s">
         <v>4</v>
@@ -3836,47 +3765,47 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="I37" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L37" s="1" t="n">
         <v>128</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="T37" s="4" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="V37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="W37" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X37" s="4" t="s">
         <v>4</v>
@@ -3892,47 +3821,47 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B38" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>100</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="I38" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="T38" s="4" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="V38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="W38" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X38" s="4" t="s">
         <v>4</v>
@@ -3948,16 +3877,16 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>50</v>
@@ -3967,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L39" s="1" t="n">
         <v>160</v>
@@ -3976,17 +3905,16 @@
         <v>96</v>
       </c>
       <c r="N39" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="P39" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Q39" s="0"/>
       <c r="V39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="W39" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X39" s="4" t="s">
         <v>4</v>
@@ -4002,13 +3930,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B40" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>50</v>
@@ -4018,7 +3946,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="L40" s="1" t="n">
         <v>160</v>
@@ -4027,19 +3955,19 @@
         <v>96</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="P40" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="V40" s="1" t="n">
         <v>1</v>
       </c>
       <c r="W40" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X40" s="4" t="s">
         <v>4</v>
@@ -4055,29 +3983,29 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B41" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="E41" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="I41" s="5" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>160</v>
@@ -4086,19 +4014,19 @@
         <v>96</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="P41" s="1" t="n">
         <v>3</v>
       </c>
       <c r="T41" s="4" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="V41" s="1" t="n">
         <v>1</v>
       </c>
       <c r="W41" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X41" s="4" t="s">
         <v>4</v>
@@ -4114,26 +4042,26 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="B42" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="I42" s="5" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>64</v>
@@ -4142,16 +4070,16 @@
         <v>64</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="T42" s="4" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="V42" s="4" t="s">
         <v>50</v>
       </c>
       <c r="W42" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="X42" s="4" t="s">
         <v>4</v>
@@ -4213,7 +4141,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>12</v>
@@ -4222,15 +4150,15 @@
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>12</v>
@@ -4244,7 +4172,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -4255,7 +4183,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>19</v>
@@ -4329,85 +4257,85 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="T1" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="W1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>4</v>
@@ -4425,27 +4353,27 @@
         <v>5</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="L2" s="1" t="n">
         <v>64</v>
@@ -4457,10 +4385,10 @@
         <v>0</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="model_params" sheetId="1" state="visible" r:id="rId3"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="227">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -1858,8 +1858,8 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="22.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="22.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2906,7 +2906,7 @@
         <v>167</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>168</v>
@@ -2918,10 +2918,13 @@
         <v>20</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="N19" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L19" s="1" t="n">
         <v>160</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>96</v>
       </c>
       <c r="W19" s="1" t="s">
         <v>161</v>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -2087,7 +2087,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="17.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="15.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="22.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="15.48"/>
@@ -2703,6 +2704,12 @@
       </c>
       <c r="K13" s="1" t="s">
         <v>173</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>96</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>160</v>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="226">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -549,9 +549,6 @@
   </si>
   <si>
     <t xml:space="preserve">224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lits,drli,litqsmall</t>
   </si>
   <si>
     <t xml:space="preserve">lungs</t>
@@ -811,28 +808,32 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1036,419 +1037,419 @@
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="47.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="47.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="20.17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="n">
+      <c r="D3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="D4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="0" t="s">
+      <c r="I5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="0" t="s">
+      <c r="J5" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="0" t="s">
+      <c r="D8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="0" t="s">
+      <c r="D9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="0" t="s">
+      <c r="D10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="0" t="s">
+      <c r="D11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="0" t="s">
+      <c r="D12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="0" t="s">
+      <c r="D13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="0" t="s">
+      <c r="D14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="0" t="s">
+      <c r="D15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="0" t="s">
+      <c r="D16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="0" t="s">
+      <c r="D17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="0" t="s">
+      <c r="D18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="4" t="n">
+      <c r="D19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="0" t="s">
+      <c r="D21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="0" t="s">
+      <c r="D22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="0" t="n">
+      <c r="D23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="0" t="s">
+      <c r="D24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="0" t="n">
+      <c r="D25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="0" t="n">
+      <c r="D26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="0" t="n">
+      <c r="D27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -1471,139 +1472,139 @@
   <dimension ref="A1:K1048576"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="0" t="s">
+      <c r="I5" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="0" t="s">
+      <c r="D7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1634,220 +1635,220 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0" t="s">
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="0" t="s">
+      <c r="B3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="0" t="s">
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="0" t="s">
+      <c r="B5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="0" t="s">
+      <c r="B6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="0" t="s">
+      <c r="B7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="0" t="s">
+      <c r="B8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="0" t="s">
+      <c r="B9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1870,106 +1871,106 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="22.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="22.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="0" t="s">
+      <c r="D3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1993,79 +1994,79 @@
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="5" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2086,1960 +2087,1923 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AH40"/>
+  <dimension ref="A1:AH1048576"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="38.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="24.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="22.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="15.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="21.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="27.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="29.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="24.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="13.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="13.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="22.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="26" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="40.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="15.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="22.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="15.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="21.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="27.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="29.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="24.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="13.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="13.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="22.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="26" style="1" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="R1" s="0" t="s">
+      <c r="R1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="S1" s="0" t="s">
+      <c r="S1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="T1" s="0" t="s">
+      <c r="T1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="U1" s="0" t="s">
+      <c r="U1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="V1" s="0" t="s">
+      <c r="V1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="W1" s="0" t="s">
+      <c r="W1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="X1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y1" s="0" t="s">
+      <c r="X1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="Z1" s="0" t="s">
+      <c r="Z1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="AA1" s="0" t="s">
+      <c r="AA1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="AB1" s="0" t="s">
+      <c r="AB1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="AC1" s="0" t="s">
+      <c r="AC1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE1" s="0" t="s">
+      <c r="AD1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AF1" s="0" t="s">
+      <c r="AF1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="AG1" s="0" t="s">
+      <c r="AG1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AH1" s="0" t="s">
+      <c r="AH1" s="1" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M2" s="0" t="s">
+      <c r="M2" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="N2" s="0" t="s">
+      <c r="N2" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="V2" s="0" t="s">
+      <c r="V2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="W2" s="0" t="s">
+      <c r="W2" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="X2" s="0" t="s">
+      <c r="X2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Y2" s="5" t="b">
+      <c r="Y2" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z2" s="5" t="b">
+      <c r="Z2" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J3" s="0" t="s">
+      <c r="J3" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L3" s="0" t="s">
+      <c r="L3" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M3" s="0" t="s">
+      <c r="M3" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="N3" s="0" t="s">
+      <c r="N3" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="T3" s="0" t="s">
+      <c r="T3" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="V3" s="0" t="s">
+      <c r="V3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="W3" s="0" t="s">
+      <c r="W3" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="X3" s="0" t="s">
+      <c r="X3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Y3" s="5" t="b">
+      <c r="Y3" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z3" s="5" t="b">
+      <c r="Z3" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="E4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="0" t="s">
+      <c r="E4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L4" s="0" t="s">
+      <c r="L4" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M4" s="0" t="s">
+      <c r="M4" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="N4" s="0" t="s">
+      <c r="N4" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="W4" s="0" t="s">
+      <c r="W4" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="X4" s="0" t="s">
+      <c r="X4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Y4" s="5" t="b">
+      <c r="Y4" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z4" s="5" t="b">
+      <c r="Z4" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="0" t="s">
+      <c r="J5" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="M5" s="0" t="s">
+      <c r="M5" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="N5" s="0" t="s">
+      <c r="N5" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="V5" s="0" t="s">
+      <c r="V5" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="W5" s="0" t="s">
+      <c r="W5" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="X5" s="0" t="s">
+      <c r="X5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Y5" s="5" t="b">
+      <c r="Y5" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z5" s="5" t="b">
+      <c r="Z5" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="J6" s="0" t="s">
+      <c r="J6" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L6" s="0" t="s">
+      <c r="L6" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M6" s="0" t="s">
+      <c r="M6" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="N6" s="0" t="s">
+      <c r="N6" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="T6" s="0" t="s">
+      <c r="T6" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="V6" s="0" t="n">
+      <c r="V6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="W6" s="0" t="s">
+      <c r="W6" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="X6" s="0" t="s">
+      <c r="X6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Y6" s="5" t="b">
+      <c r="Y6" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z6" s="5" t="b">
+      <c r="Z6" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="J7" s="0" t="s">
+      <c r="J7" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="M7" s="0" t="s">
+      <c r="M7" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="N7" s="0" t="s">
+      <c r="N7" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="T7" s="0" t="s">
+      <c r="T7" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="V7" s="0" t="n">
+      <c r="V7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="W7" s="0" t="s">
+      <c r="W7" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="X7" s="0" t="s">
+      <c r="X7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Y7" s="5" t="b">
+      <c r="Y7" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z7" s="5" t="b">
+      <c r="Z7" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="J8" s="0" t="s">
+      <c r="J8" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="M8" s="0" t="s">
+      <c r="M8" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="N8" s="0" t="s">
+      <c r="N8" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="T8" s="0" t="s">
+      <c r="T8" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="V8" s="0" t="n">
+      <c r="V8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="W8" s="0" t="s">
+      <c r="W8" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="X8" s="0" t="s">
+      <c r="X8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Y8" s="5" t="b">
+      <c r="Y8" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z8" s="5" t="b">
+      <c r="Z8" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="0" t="s">
+      <c r="B9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J9" s="0" t="s">
+      <c r="J9" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L9" s="0" t="s">
+      <c r="L9" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M9" s="0" t="s">
+      <c r="M9" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="V9" s="0" t="s">
+      <c r="V9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="W9" s="0" t="s">
+      <c r="W9" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="Y9" s="5" t="b">
+      <c r="Y9" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z9" s="5" t="b">
+      <c r="Z9" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="J10" s="0" t="s">
+      <c r="J10" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="L10" s="0" t="s">
+      <c r="L10" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M10" s="0" t="s">
+      <c r="M10" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="V10" s="0" t="s">
+      <c r="V10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="W10" s="0" t="s">
+      <c r="W10" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="Y10" s="5" t="b">
+      <c r="Y10" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z10" s="5" t="b">
+      <c r="Z10" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="J11" s="0" t="s">
+      <c r="J11" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L11" s="0" t="s">
+      <c r="L11" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M11" s="0" t="s">
+      <c r="M11" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="V11" s="0" t="s">
+      <c r="V11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="W11" s="0" t="s">
+      <c r="W11" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="Y11" s="5" t="b">
+      <c r="Y11" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z11" s="5" t="b">
+      <c r="Z11" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="J12" s="0" t="s">
+      <c r="J12" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="K12" s="0" t="s">
+      <c r="K12" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="L12" s="0" t="n">
+      <c r="L12" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="M12" s="0" t="n">
+      <c r="M12" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="N12" s="0" t="s">
+      <c r="N12" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="V12" s="0" t="s">
+      <c r="V12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W12" s="0" t="s">
+      <c r="W12" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="Y12" s="5" t="b">
+      <c r="Y12" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z12" s="5" t="b">
+      <c r="Z12" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J13" s="0" t="s">
+      <c r="J13" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="L13" s="0" t="s">
+      <c r="L13" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M13" s="0" t="s">
+      <c r="M13" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="V13" s="0" t="s">
+      <c r="V13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="W13" s="0" t="s">
+      <c r="W13" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="Y13" s="5" t="b">
+      <c r="Y13" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z13" s="5" t="b">
+      <c r="Z13" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="J14" s="0" t="s">
+      <c r="J14" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L14" s="0" t="s">
+      <c r="L14" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M14" s="0" t="s">
+      <c r="M14" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="V14" s="0" t="s">
+      <c r="V14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="W14" s="0" t="s">
+      <c r="W14" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="Y14" s="5" t="b">
+      <c r="Y14" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z14" s="5" t="b">
+      <c r="Z14" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J15" s="0" t="s">
+      <c r="J15" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L15" s="0" t="s">
+      <c r="L15" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="M15" s="0" t="s">
+      <c r="M15" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="V15" s="0" t="s">
+      <c r="V15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="W15" s="0" t="s">
+      <c r="W15" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="Y15" s="5" t="b">
+      <c r="Y15" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z15" s="5" t="b">
+      <c r="Z15" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="0" t="s">
+      <c r="J16" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K16" s="6"/>
-      <c r="L16" s="0" t="n">
+      <c r="K16" s="7"/>
+      <c r="L16" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="M16" s="0" t="n">
+      <c r="M16" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="W16" s="3" t="s">
+      <c r="W16" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="Y16" s="5" t="b">
+      <c r="Y16" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z16" s="5" t="b">
+      <c r="Z16" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>165</v>
-      </c>
-      <c r="B17" s="0" t="n">
-        <v>13</v>
-      </c>
-      <c r="D17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E17" s="0" t="n">
-        <v>40</v>
-      </c>
-      <c r="F17" s="0" t="s">
+      <c r="B17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I17" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="T17" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="V17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y17" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z17" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I18" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="T18" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="V18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="W18" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="X18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z18" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I19" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="T19" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="V19" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="W19" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="X19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y19" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I20" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="V20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="X20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y20" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z20" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="I21" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="R21" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="V21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="X21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z21" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="J17" s="0" t="s">
+      <c r="I22" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="V22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="X22" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y22" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z22" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="K17" s="6"/>
-      <c r="L17" s="0" t="n">
+      <c r="L23" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="N23" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="M17" s="0" t="n">
+      <c r="R23" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="V23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="X23" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y23" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z23" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L24" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="W17" s="3" t="s">
+      <c r="M24" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="R24" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="V24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="X24" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y24" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z24" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="W25" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="Y17" s="5" t="b">
+      <c r="X25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y25" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z17" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="B18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="E18" s="0" t="s">
+      <c r="Z25" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH25" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y26" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH26" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G18" s="0" t="s">
+      <c r="J27" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="V27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y27" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z27" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH27" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y28" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z28" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH28" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="V29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="W29" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y29" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z29" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH29" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="V30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="X30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y30" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z30" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH30" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="V31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="W31" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="X31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y31" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z31" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="I18" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="s">
+      <c r="I32" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="L18" s="3" t="s">
+      <c r="L32" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="M18" s="3" t="s">
+      <c r="M32" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N18" s="3" t="s">
+      <c r="N32" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="V18" s="3" t="s">
+      <c r="T32" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="V32" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="W18" s="3" t="s">
+      <c r="W32" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="X18" s="3" t="s">
+      <c r="X32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="Y18" s="5" t="b">
+      <c r="Y32" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z18" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="B19" s="0" t="n">
+      <c r="Z32" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B33" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="E19" s="0" t="n">
+      <c r="D33" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E33" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="G19" s="0" t="s">
+      <c r="G33" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="I19" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="s">
+      <c r="I33" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="L19" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="M19" s="3" t="s">
+      <c r="L33" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="M33" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N19" s="3" t="s">
+      <c r="N33" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="T19" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="V19" s="3" t="s">
+      <c r="T33" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="V33" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="W19" s="3" t="s">
+      <c r="W33" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="X19" s="3" t="s">
+      <c r="X33" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="Y19" s="5" t="b">
+      <c r="Y33" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z19" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="B20" s="0" t="n">
+      <c r="Z33" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I34" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L34" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="O34" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="T34" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="V34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="X34" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y34" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z34" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I35" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L35" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="O35" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="T35" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="V35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="X35" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y35" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z35" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L36" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="M36" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="P36" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="E20" s="0" t="n">
+      <c r="V36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="X36" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y36" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z36" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E37" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="G20" s="0" t="s">
+      <c r="I37" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="L37" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="M37" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="P37" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q37" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="V37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="X37" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y37" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z37" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="I20" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
+      <c r="I38" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="N20" s="3" t="s">
+      <c r="L38" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="V20" s="3" t="s">
+      <c r="M38" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="P38" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="V38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="X38" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y38" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z38" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L39" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="M39" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="T39" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="V39" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="W20" s="3" t="s">
+      <c r="W39" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="X20" s="3" t="s">
+      <c r="X39" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="Y20" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z20" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="B21" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="E21" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="G21" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="I21" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="V21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y21" s="5" t="b">
+      <c r="Y39" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z21" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="B22" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D22" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="E22" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="I22" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="V22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y22" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z22" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="B23" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="D23" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="E23" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="V23" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y23" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z23" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="B24" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="D24" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="E24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="V24" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W24" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="X24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y24" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z24" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="B25" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="E25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="L25" s="0" t="n">
-        <v>96</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="R25" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="V25" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W25" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="X25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y25" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z25" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B26" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="E26" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="J26" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="L26" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="M26" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="W26" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="X26" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y26" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z26" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AH26" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B27" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="E27" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="J27" s="0" t="s">
-        <v>183</v>
-      </c>
-      <c r="K27" s="0" t="s">
-        <v>184</v>
-      </c>
-      <c r="L27" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="M27" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="S27" s="0" t="s">
-        <v>185</v>
-      </c>
-      <c r="X27" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y27" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z27" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AH27" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B28" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="E28" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="J28" s="0" t="s">
-        <v>163</v>
-      </c>
-      <c r="L28" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="M28" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="V28" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="W28" s="0" t="s">
-        <v>186</v>
-      </c>
-      <c r="X28" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y28" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z28" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AH28" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B29" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="D29" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="E29" s="0" t="s">
-        <v>187</v>
-      </c>
-      <c r="J29" s="0" t="s">
-        <v>163</v>
-      </c>
-      <c r="L29" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="M29" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="V29" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="W29" s="0" t="s">
-        <v>188</v>
-      </c>
-      <c r="X29" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y29" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z29" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AH29" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B30" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D30" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="E30" s="0" t="s">
-        <v>187</v>
-      </c>
-      <c r="J30" s="0" t="s">
-        <v>163</v>
-      </c>
-      <c r="L30" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="M30" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="R30" s="0" t="s">
-        <v>189</v>
-      </c>
-      <c r="V30" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="W30" s="0" t="s">
-        <v>188</v>
-      </c>
-      <c r="X30" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y30" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z30" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AH30" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B31" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="D31" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="E31" s="0" t="s">
-        <v>187</v>
-      </c>
-      <c r="J31" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="L31" s="0" t="s">
-        <v>190</v>
-      </c>
-      <c r="M31" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="O31" s="0" t="s">
-        <v>189</v>
-      </c>
-      <c r="V31" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="W31" s="0" t="s">
-        <v>188</v>
-      </c>
-      <c r="X31" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y31" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z31" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AH31" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>191</v>
-      </c>
-      <c r="B32" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="0" t="s">
-        <v>192</v>
-      </c>
-      <c r="E32" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="J32" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="L32" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="M32" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="V32" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="W32" s="0" t="s">
-        <v>188</v>
-      </c>
-      <c r="X32" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y32" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z32" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>194</v>
-      </c>
-      <c r="B33" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="0" t="s">
-        <v>195</v>
-      </c>
-      <c r="E33" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="G33" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="I33" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y33" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z33" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>194</v>
-      </c>
-      <c r="B34" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" s="0" t="s">
-        <v>195</v>
-      </c>
-      <c r="E34" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="G34" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="I34" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="L34" s="0" t="n">
-        <v>192</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="T34" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="V34" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="W34" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="X34" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y34" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z34" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>197</v>
-      </c>
-      <c r="B35" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="0" t="s">
-        <v>198</v>
-      </c>
-      <c r="E35" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="G35" s="0" t="s">
-        <v>199</v>
-      </c>
-      <c r="I35" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="L35" s="0" t="n">
-        <v>128</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="V35" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y35" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z35" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
-        <v>197</v>
-      </c>
-      <c r="B36" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" s="0" t="s">
-        <v>198</v>
-      </c>
-      <c r="E36" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="G36" s="0" t="s">
-        <v>199</v>
-      </c>
-      <c r="I36" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="L36" s="0" t="n">
-        <v>192</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="T36" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="V36" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W36" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="X36" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y36" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z36" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
-        <v>202</v>
-      </c>
-      <c r="B37" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="D37" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="E37" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="L37" s="0" t="n">
-        <v>160</v>
-      </c>
-      <c r="M37" s="0" t="n">
-        <v>96</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="P37" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="V37" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W37" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="X37" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y37" s="4" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z37" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>202</v>
-      </c>
-      <c r="B38" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="E38" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="L38" s="0" t="n">
-        <v>160</v>
-      </c>
-      <c r="M38" s="0" t="n">
-        <v>96</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="P38" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="V38" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W38" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="X38" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y38" s="4" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z38" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>202</v>
-      </c>
-      <c r="B39" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="C39" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="D39" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="E39" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="G39" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="L39" s="0" t="n">
-        <v>160</v>
-      </c>
-      <c r="M39" s="0" t="n">
-        <v>96</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="P39" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="T39" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="V39" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W39" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="X39" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y39" s="4" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z39" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="B40" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="G40" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="L40" s="0" t="n">
-        <v>64</v>
-      </c>
-      <c r="M40" s="0" t="n">
-        <v>64</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="T40" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="V40" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="W40" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="X40" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y40" s="4" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z40" s="4" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
+      <c r="Z39" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4059,89 +4023,89 @@
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="19.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="48.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="1" width="19.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C2" s="0" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>215</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="D3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="0" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>217</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>218</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="n">
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4149,28 +4113,28 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E9" s="4"/>
+      <c r="E9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E12" s="4"/>
+      <c r="E12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E13" s="4"/>
+      <c r="E13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E16" s="4"/>
+      <c r="E16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E17" s="4"/>
+      <c r="E17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E20" s="4"/>
+      <c r="E20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4193,149 +4157,149 @@
   <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="25.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="17.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="17" style="0" width="23.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="25.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="17.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="17" style="1" width="23.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="G1" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>135</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="L1" s="0" t="s">
-        <v>138</v>
-      </c>
-      <c r="M1" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="N1" s="0" t="s">
-        <v>140</v>
-      </c>
-      <c r="O1" s="0" t="s">
-        <v>141</v>
-      </c>
-      <c r="P1" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q1" s="0" t="s">
+      <c r="R1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="R1" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="S1" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="T1" s="0" t="s">
+      <c r="U1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="U1" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="V1" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="W1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="X1" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y1" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="Z1" s="0" t="s">
-        <v>152</v>
-      </c>
-      <c r="AA1" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="AB1" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE1" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF1" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG1" s="0" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>202</v>
-      </c>
-      <c r="B2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="L2" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="L2" s="0" t="n">
-        <v>64</v>
-      </c>
-      <c r="M2" s="0" t="n">
-        <v>64</v>
-      </c>
-      <c r="N2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="0" t="s">
+      <c r="T2" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="T2" s="0" t="s">
-        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="228">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -455,24 +455,24 @@
     <t xml:space="preserve">remapping_source</t>
   </si>
   <si>
+    <t xml:space="preserve">remapping_lbd_kbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remapping_whole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remapping_imported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remapping_train</t>
+  </si>
+  <si>
     <t xml:space="preserve">vip_label</t>
   </si>
   <si>
     <t xml:space="preserve">localiser_regions</t>
   </si>
   <si>
-    <t xml:space="preserve">remapping_lbd_kbd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remapping_whole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remapping_imported</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remapping_train</t>
-  </si>
-  <si>
     <t xml:space="preserve">samples_per_file</t>
   </si>
   <si>
@@ -663,6 +663,12 @@
   </si>
   <si>
     <t xml:space="preserve">TSL.label_region:TSL.lungs,None,None,None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drli_short,kits23_short</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None,{1:4,2:5,3:6}</t>
   </si>
   <si>
     <t xml:space="preserve">[ResNet3D]</t>
@@ -2087,7 +2093,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AH1048576"/>
+  <dimension ref="A1:AH40"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.67"/>
@@ -2096,19 +2102,20 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="40.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="17.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="15.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="22.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="15.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="21.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="27.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="29.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="24.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="13.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="21.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="21.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="27.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="29.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="24.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="22.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="15.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="13.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="13.83"/>
@@ -2294,7 +2301,7 @@
       <c r="N3" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>164</v>
       </c>
       <c r="V3" s="1" t="s">
@@ -2426,7 +2433,7 @@
       <c r="N6" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="T6" s="1" t="s">
+      <c r="R6" s="1" t="s">
         <v>164</v>
       </c>
       <c r="V6" s="1" t="n">
@@ -2475,7 +2482,7 @@
       <c r="N7" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="T7" s="1" t="s">
+      <c r="R7" s="1" t="s">
         <v>164</v>
       </c>
       <c r="V7" s="1" t="n">
@@ -2524,7 +2531,7 @@
       <c r="N8" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="T8" s="1" t="s">
+      <c r="R8" s="1" t="s">
         <v>164</v>
       </c>
       <c r="V8" s="1" t="n">
@@ -2877,7 +2884,7 @@
       <c r="N17" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="T17" s="4" t="s">
+      <c r="R17" s="4" t="s">
         <v>176</v>
       </c>
       <c r="V17" s="4" t="s">
@@ -2930,7 +2937,7 @@
       <c r="N18" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="T18" s="4" t="s">
+      <c r="R18" s="4" t="s">
         <v>176</v>
       </c>
       <c r="V18" s="4" t="s">
@@ -2983,10 +2990,10 @@
       <c r="N19" s="4" t="s">
         <v>160</v>
       </c>
+      <c r="P19" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="R19" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="T19" s="4" t="s">
         <v>176</v>
       </c>
       <c r="V19" s="4" t="s">
@@ -3039,10 +3046,10 @@
       <c r="N20" s="4" t="s">
         <v>160</v>
       </c>
+      <c r="P20" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="R20" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="T20" s="4" t="s">
         <v>176</v>
       </c>
       <c r="V20" s="1" t="n">
@@ -3092,7 +3099,7 @@
       <c r="N21" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="R21" s="4" t="s">
+      <c r="P21" s="4" t="s">
         <v>177</v>
       </c>
       <c r="V21" s="1" t="n">
@@ -3145,7 +3152,7 @@
       <c r="N22" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="R22" s="4" t="s">
+      <c r="P22" s="4" t="s">
         <v>177</v>
       </c>
       <c r="V22" s="1" t="n">
@@ -3195,7 +3202,7 @@
       <c r="N23" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="R23" s="4" t="s">
+      <c r="P23" s="4" t="s">
         <v>179</v>
       </c>
       <c r="V23" s="1" t="n">
@@ -3245,7 +3252,7 @@
       <c r="N24" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="R24" s="4" t="s">
+      <c r="P24" s="4" t="s">
         <v>179</v>
       </c>
       <c r="V24" s="1" t="n">
@@ -3331,7 +3338,7 @@
       <c r="M26" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="S26" s="1" t="s">
+      <c r="Q26" s="1" t="s">
         <v>184</v>
       </c>
       <c r="X26" s="1" t="s">
@@ -3457,7 +3464,7 @@
       <c r="M29" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="R29" s="1" t="s">
+      <c r="P29" s="1" t="s">
         <v>188</v>
       </c>
       <c r="V29" s="1" t="s">
@@ -3599,7 +3606,7 @@
       <c r="N32" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="T32" s="4" t="s">
+      <c r="R32" s="4" t="s">
         <v>195</v>
       </c>
       <c r="V32" s="4" t="s">
@@ -3652,7 +3659,7 @@
       <c r="N33" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="T33" s="4" t="s">
+      <c r="R33" s="4" t="s">
         <v>195</v>
       </c>
       <c r="V33" s="4" t="s">
@@ -3708,7 +3715,7 @@
       <c r="O34" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="T34" s="4" t="s">
+      <c r="R34" s="4" t="s">
         <v>200</v>
       </c>
       <c r="V34" s="1" t="n">
@@ -3764,7 +3771,7 @@
       <c r="O35" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="T35" s="4" t="s">
+      <c r="R35" s="4" t="s">
         <v>200</v>
       </c>
       <c r="V35" s="1" t="n">
@@ -3817,7 +3824,7 @@
       <c r="N36" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="P36" s="1" t="n">
+      <c r="T36" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V36" s="1" t="n">
@@ -3867,10 +3874,10 @@
       <c r="N37" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="P37" s="1" t="n">
+      <c r="T37" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Q37" s="4" t="s">
+      <c r="U37" s="4" t="s">
         <v>205</v>
       </c>
       <c r="V37" s="1" t="n">
@@ -3926,11 +3933,11 @@
       <c r="N38" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="P38" s="1" t="n">
+      <c r="R38" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="T38" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="T38" s="4" t="s">
-        <v>207</v>
       </c>
       <c r="V38" s="1" t="n">
         <v>1</v>
@@ -3982,7 +3989,7 @@
       <c r="O39" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="T39" s="4" t="s">
+      <c r="R39" s="4" t="s">
         <v>211</v>
       </c>
       <c r="V39" s="4" t="s">
@@ -4003,7 +4010,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L40" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="M40" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="R40" s="4"/>
+      <c r="V40" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="W40" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="X40" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y40" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z40" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4052,7 +4106,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>12</v>
@@ -4061,15 +4115,15 @@
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>12</v>
@@ -4083,7 +4137,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -4094,7 +4148,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>19</v>
@@ -4183,7 +4237,7 @@
         <v>131</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>133</v>
@@ -4213,19 +4267,19 @@
         <v>141</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>148</v>
@@ -4278,13 +4332,13 @@
         <v>203</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L2" s="1" t="n">
         <v>64</v>
@@ -4296,10 +4350,10 @@
         <v>0</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="231">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -431,265 +431,274 @@
     <t xml:space="preserve">imported_folder</t>
   </si>
   <si>
+    <t xml:space="preserve">merge_imported_labels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">localiser_regions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source_plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patch_dim0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patch_dim1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patch_overlap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remapping_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remapping_lbd_rbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remapping_whole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remapping_imported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remapping_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vip_label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samples_per_file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spacing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">use_fg_indices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nnz_allowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plan_valid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plan_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">periodict_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nodesthick,nodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8,.8,1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$cold_storage_folder/predictions/totalseg/LITS-1439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL.label_region:TSL.label_region,TSL.label_region:TSL.label_region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lits,drli,litq,litqsmall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8,0.8,1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4, lbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lungs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lidc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL.label_region:TSL.lungs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{1:1,2:1,3:2,4:3,5:3}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5, lbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{1:1,2:1,3:1,4:1,5:1}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.75, 0.75,0.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">totalseg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">whole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1, source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL.label_full:TSL.label_region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5, 1.5,1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,1,1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL.label_full:TSL.label_minimal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uls23_bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sourcepbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colonmsd10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL.label_region:TSL.gi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pancreas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pancreasmsd07, curvaspdac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DS.pancreasmsd07/lms,$cold_storage_folder/predictions/totalseg/LITS-1437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{1:0,2:1},None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{1:3},TSL.label_minimal: TSL.pancreas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kidneys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all labels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kits23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abdomen, pelvis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all labels, abdomen lbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL.label_region:TSL.abdomen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drli_short, lidc_short,kits23_short,nodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{1:0,2:1,3:1},{1:1,2:1,3:2,4:2,5:2},{1:1,2:2,3:2},None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL.label_region:TSL.lungs,None,None,None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drli_short,kits23_short</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None,{1:4,2:5,3:6}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL.label_region:TSL.kidney, TSL.label_region:TSL.liver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">totalseg_short</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ResNet3D]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ResNet3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resnet_depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[10,18,34,50,101,152]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_scalars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pretrained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expand_mode</t>
+  </si>
+  <si>
     <t xml:space="preserve">lm_groups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">merge_imported_labels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">source_plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patch_dim0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patch_dim1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patch_overlap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remapping_source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remapping_lbd_kbd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remapping_whole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remapping_imported</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remapping_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vip_label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">localiser_regions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">samples_per_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spacing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">use_fg_indices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nnz_allowed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plan_valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plan_test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">periodict_test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nodesthick,nodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8,.8,1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$cold_storage_folder/predictions/totalseg/LITS-1439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lbd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSL.label_region:TSL.label_region,TSL.label_region:TSL.label_region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">liver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lits,drli,litq,litqsmall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8,0.8,1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pbd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4, lbd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lungs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lidc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSL.label_region:TSL.lungs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{1:1,2:1,3:2,4:3,5:3}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5, lbd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{1:1,2:1,3:1,4:1,5:1}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75, 0.75,0.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">totalseg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">whole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1, source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSL.label_full:TSL.label_region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5, 1.5,1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,1,1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSL.label_full:TSL.label_minimal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uls23_bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sourcepbd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">colon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">colonmsd10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSL.label_region:TSL.gi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pancreas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pancreasmsd07, curvaspdac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DS.pancreasmsd07/lms,$cold_storage_folder/predictions/totalseg/LITS-1437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{1:0,2:1},None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{1:3},TSL.label_minimal: TSL.pancreas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kidneys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">all labels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kits23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kbd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abdomen, pelvis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">all labels, abdomen lbd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSL.label_region:TSL.abdomen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drli_short, lidc_short,kits23_short,nodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{1:0,2:1,3:1},{1:1,2:1,3:2,4:2,5:2},{1:1,2:2,3:2},None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSL.label_region:TSL.lungs,None,None,None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drli_short,kits23_short</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None,{1:4,2:5,3:6}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ResNet3D]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ResNet3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resnet_depth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[10,18,34,50,101,152]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_scalars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pretrained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expand_mode</t>
   </si>
   <si>
     <t xml:space="preserve">remapping_lbd</t>
@@ -2093,7 +2102,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AH40"/>
+  <dimension ref="A1:AH41"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.67"/>
@@ -2102,20 +2111,20 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="40.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="17.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="13.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="21.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="21.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="21.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="27.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="29.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="24.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="22.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="15.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="15.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="13.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="13.83"/>
@@ -2184,29 +2193,26 @@
       <c r="T1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="X1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="AC1" s="1" t="s">
         <v>4</v>
@@ -2224,39 +2230,39 @@
         <v>5</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="V2" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X2" s="1" t="s">
         <v>4</v>
@@ -2272,43 +2278,43 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="L3" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="V3" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X3" s="1" t="s">
         <v>4</v>
@@ -2324,31 +2330,31 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L4" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="X4" s="1" t="s">
         <v>4</v>
@@ -2364,34 +2370,34 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L5" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M5" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="V5" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X5" s="1" t="s">
         <v>4</v>
@@ -2407,40 +2413,40 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="L6" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="R6" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="V6" s="1" t="n">
         <v>2</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X6" s="1" t="s">
         <v>4</v>
@@ -2456,40 +2462,40 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="N7" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="R7" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X7" s="1" t="s">
         <v>4</v>
@@ -2505,40 +2511,40 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>75</v>
       </c>
       <c r="G8" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M8" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="R8" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V8" s="1" t="n">
         <v>2</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X8" s="1" t="s">
         <v>4</v>
@@ -2554,34 +2560,34 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L9" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V9" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Y9" s="6" t="b">
         <f aca="false">TRUE()</f>
@@ -2594,28 +2600,28 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V10" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Y10" s="6" t="b">
         <f aca="false">TRUE()</f>
@@ -2628,31 +2634,31 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L11" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V11" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Y11" s="6" t="b">
         <f aca="false">TRUE()</f>
@@ -2665,19 +2671,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J12" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="L12" s="1" t="n">
         <v>128</v>
@@ -2686,13 +2692,13 @@
         <v>96</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="V12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Y12" s="6" t="b">
         <f aca="false">TRUE()</f>
@@ -2705,31 +2711,31 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="J13" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L13" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="M13" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V13" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Y13" s="6" t="b">
         <f aca="false">TRUE()</f>
@@ -2742,31 +2748,31 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L14" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V14" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Y14" s="6" t="b">
         <f aca="false">TRUE()</f>
@@ -2779,31 +2785,31 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="V15" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Y15" s="6" t="b">
         <f aca="false">TRUE()</f>
@@ -2816,13 +2822,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>40</v>
@@ -2831,7 +2837,7 @@
         <v>20</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="1" t="n">
@@ -2841,7 +2847,7 @@
         <v>96</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Y16" s="6" t="b">
         <f aca="false">TRUE()</f>
@@ -2854,44 +2860,44 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H17" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="I17" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>163</v>
-      </c>
       <c r="L17" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="M17" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="N17" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N17" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="R17" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="V17" s="4" t="s">
         <v>50</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X17" s="4" t="s">
         <v>4</v>
@@ -2907,44 +2913,44 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H18" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="I18" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>163</v>
-      </c>
       <c r="L18" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="M18" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="M18" s="4" t="s">
+      <c r="N18" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N18" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="R18" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="V18" s="4" t="s">
         <v>50</v>
       </c>
       <c r="W18" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X18" s="4" t="s">
         <v>4</v>
@@ -2960,47 +2966,47 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H19" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="I19" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>163</v>
-      </c>
       <c r="L19" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="M19" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="M19" s="4" t="s">
+      <c r="N19" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N19" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="P19" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="V19" s="4" t="s">
         <v>50</v>
       </c>
       <c r="W19" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X19" s="4" t="s">
         <v>4</v>
@@ -3016,47 +3022,47 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H20" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="I20" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>163</v>
-      </c>
       <c r="L20" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="M20" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="M20" s="4" t="s">
+      <c r="N20" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N20" s="4" t="s">
+      <c r="P20" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="V20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="R20" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="V20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W20" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="X20" s="4" t="s">
         <v>4</v>
@@ -3072,41 +3078,41 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="I21" s="6" t="b">
+      <c r="H21" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L21" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="M21" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="M21" s="4" t="s">
+      <c r="N21" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N21" s="4" t="s">
+      <c r="P21" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="V21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="P21" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="V21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W21" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="X21" s="4" t="s">
         <v>4</v>
@@ -3122,44 +3128,44 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I22" s="6" t="b">
+      <c r="H22" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L22" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="M22" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="M22" s="4" t="s">
+      <c r="N22" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N22" s="4" t="s">
+      <c r="P22" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="V22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="V22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W22" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="X22" s="4" t="s">
         <v>4</v>
@@ -3175,41 +3181,41 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="6" t="b">
+      <c r="H23" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L23" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="M23" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="M23" s="4" t="s">
+      <c r="N23" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N23" s="4" t="s">
+      <c r="P23" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="V23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="P23" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="V23" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W23" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="X23" s="4" t="s">
         <v>4</v>
@@ -3225,41 +3231,41 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="6" t="b">
+      <c r="H24" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L24" s="1" t="n">
         <v>96</v>
       </c>
       <c r="M24" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="N24" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N24" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="P24" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="V24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" s="4" t="s">
         <v>179</v>
-      </c>
-      <c r="V24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W24" s="4" t="s">
-        <v>180</v>
       </c>
       <c r="X24" s="4" t="s">
         <v>4</v>
@@ -3275,28 +3281,28 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J25" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="M25" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M25" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="W25" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X25" s="1" t="s">
         <v>4</v>
@@ -3315,31 +3321,31 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>42</v>
       </c>
       <c r="J26" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="L26" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q26" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="X26" s="1" t="s">
         <v>4</v>
@@ -3358,31 +3364,31 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="V27" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="X27" s="1" t="s">
         <v>4</v>
@@ -3401,31 +3407,31 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L28" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="M28" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V28" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="X28" s="1" t="s">
         <v>4</v>
@@ -3444,34 +3450,34 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L29" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="M29" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M29" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="P29" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V29" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="X29" s="1" t="s">
         <v>4</v>
@@ -3490,34 +3496,34 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B30" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V30" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="X30" s="1" t="s">
         <v>4</v>
@@ -3536,31 +3542,31 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="B31" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L31" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="V31" s="1" t="s">
         <v>50</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="X31" s="1" t="s">
         <v>4</v>
@@ -3576,44 +3582,44 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G32" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H32" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="I32" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>163</v>
-      </c>
       <c r="L32" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="M32" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="M32" s="4" t="s">
+      <c r="N32" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N32" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="R32" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="V32" s="4" t="s">
         <v>50</v>
       </c>
       <c r="W32" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X32" s="4" t="s">
         <v>4</v>
@@ -3629,44 +3635,44 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G33" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H33" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="I33" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>163</v>
       </c>
       <c r="L33" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M33" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="N33" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N33" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="R33" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="V33" s="4" t="s">
         <v>50</v>
       </c>
       <c r="W33" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X33" s="4" t="s">
         <v>4</v>
@@ -3682,47 +3688,47 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="I34" s="6" t="b">
+        <v>197</v>
+      </c>
+      <c r="H34" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L34" s="1" t="n">
         <v>128</v>
       </c>
       <c r="M34" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="N34" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N34" s="4" t="s">
+      <c r="O34" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="R34" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="V34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="O34" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="R34" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="V34" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W34" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="X34" s="4" t="s">
         <v>4</v>
@@ -3738,47 +3744,47 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>100</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="I35" s="6" t="b">
+        <v>197</v>
+      </c>
+      <c r="H35" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L35" s="1" t="n">
         <v>192</v>
       </c>
       <c r="M35" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="N35" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N35" s="4" t="s">
+      <c r="O35" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="R35" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="V35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="O35" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="R35" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="V35" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W35" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="X35" s="4" t="s">
         <v>4</v>
@@ -3794,26 +3800,26 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B36" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="I36" s="5" t="n">
+      <c r="H36" s="5" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L36" s="1" t="n">
         <v>160</v>
@@ -3822,7 +3828,7 @@
         <v>96</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="T36" s="1" t="n">
         <v>3</v>
@@ -3831,7 +3837,7 @@
         <v>1</v>
       </c>
       <c r="W36" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X36" s="4" t="s">
         <v>4</v>
@@ -3847,20 +3853,23 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B37" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="I37" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="H37" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>204</v>
@@ -3872,19 +3881,16 @@
         <v>96</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="T37" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="U37" s="4" t="s">
-        <v>205</v>
-      </c>
       <c r="V37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="W37" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X37" s="4" t="s">
         <v>4</v>
@@ -3900,29 +3906,29 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B38" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G38" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>163</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>160</v>
@@ -3931,10 +3937,10 @@
         <v>96</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="R38" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T38" s="1" t="n">
         <v>3</v>
@@ -3943,7 +3949,7 @@
         <v>1</v>
       </c>
       <c r="W38" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X38" s="4" t="s">
         <v>4</v>
@@ -3959,26 +3965,26 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="B39" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G39" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>163</v>
       </c>
       <c r="L39" s="1" t="n">
         <v>64</v>
@@ -3987,16 +3993,16 @@
         <v>64</v>
       </c>
       <c r="O39" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="R39" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="R39" s="4" t="s">
-        <v>211</v>
       </c>
       <c r="V39" s="4" t="s">
         <v>50</v>
       </c>
       <c r="W39" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X39" s="4" t="s">
         <v>4</v>
@@ -4012,23 +4018,26 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B40" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I40" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="G40" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L40" s="1" t="n">
         <v>160</v>
@@ -4037,14 +4046,16 @@
         <v>96</v>
       </c>
       <c r="O40" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="R40" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="R40" s="4"/>
       <c r="V40" s="4" t="s">
         <v>50</v>
       </c>
       <c r="W40" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X40" s="4" t="s">
         <v>4</v>
@@ -4054,6 +4065,55 @@
         <v>1</v>
       </c>
       <c r="Z40" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H41" s="5"/>
+      <c r="I41" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="L41" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="M41" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="O41" s="4"/>
+      <c r="P41" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="R41" s="4"/>
+      <c r="V41" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="W41" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="X41" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y41" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z41" s="5" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4106,7 +4166,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>12</v>
@@ -4115,15 +4175,15 @@
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>12</v>
@@ -4137,7 +4197,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -4148,7 +4208,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>19</v>
@@ -4237,16 +4297,16 @@
         <v>131</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>136</v>
@@ -4270,7 +4330,7 @@
         <v>146</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>143</v>
@@ -4279,28 +4339,28 @@
         <v>144</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>4</v>
@@ -4318,27 +4378,27 @@
         <v>5</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L2" s="1" t="n">
         <v>64</v>
@@ -4350,10 +4410,10 @@
         <v>0</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -2124,7 +2124,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="29.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="24.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="22.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="15.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="15.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="13.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="13.83"/>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="231">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -596,6 +596,9 @@
     <t xml:space="preserve">192</t>
   </si>
   <si>
+    <t xml:space="preserve">rbd</t>
+  </si>
+  <si>
     <t xml:space="preserve">bones</t>
   </si>
   <si>
@@ -639,9 +642,6 @@
   </si>
   <si>
     <t xml:space="preserve">abdomen, pelvis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rbd</t>
   </si>
   <si>
     <t xml:space="preserve">all labels, abdomen lbd</t>
@@ -2102,14 +2102,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AH41"/>
+  <dimension ref="A1:AH42"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="40.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.5"/>
@@ -3542,26 +3543,29 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B31" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="L31" s="1" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>158</v>
       </c>
+      <c r="O31" s="1" t="s">
+        <v>187</v>
+      </c>
       <c r="V31" s="1" t="s">
         <v>50</v>
       </c>
@@ -3572,56 +3576,46 @@
         <v>4</v>
       </c>
       <c r="Y31" s="6" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="Z31" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="AH31" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B32" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E32" s="1" t="n">
+      <c r="L32" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V32" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H32" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="N32" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="R32" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="V32" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="W32" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="X32" s="4" t="s">
+      <c r="W32" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="X32" s="1" t="s">
         <v>4</v>
       </c>
       <c r="Y32" s="6" t="b">
@@ -3635,13 +3629,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>50</v>
@@ -3656,8 +3650,8 @@
       <c r="J33" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="L33" s="1" t="n">
-        <v>192</v>
+      <c r="L33" s="4" t="s">
+        <v>157</v>
       </c>
       <c r="M33" s="4" t="s">
         <v>158</v>
@@ -3666,7 +3660,7 @@
         <v>159</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="V33" s="4" t="s">
         <v>50</v>
@@ -3688,19 +3682,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>197</v>
+        <v>161</v>
       </c>
       <c r="H34" s="6" t="b">
         <f aca="false">FALSE()</f>
@@ -3710,7 +3704,7 @@
         <v>162</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="M34" s="4" t="s">
         <v>158</v>
@@ -3718,14 +3712,11 @@
       <c r="N34" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="O34" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="R34" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="V34" s="1" t="n">
-        <v>1</v>
+        <v>195</v>
+      </c>
+      <c r="V34" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="W34" s="4" t="s">
         <v>160</v>
@@ -3734,8 +3725,8 @@
         <v>4</v>
       </c>
       <c r="Y34" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="Z34" s="6" t="b">
         <f aca="false">FALSE()</f>
@@ -3744,19 +3735,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H35" s="6" t="b">
         <f aca="false">FALSE()</f>
@@ -3766,7 +3757,7 @@
         <v>162</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="M35" s="4" t="s">
         <v>158</v>
@@ -3775,10 +3766,10 @@
         <v>159</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="R35" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="V35" s="1" t="n">
         <v>1</v>
@@ -3800,21 +3791,21 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>201</v>
+        <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="H36" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H36" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3822,16 +3813,19 @@
         <v>162</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>160</v>
-      </c>
-      <c r="M36" s="1" t="n">
-        <v>96</v>
+        <v>192</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>158</v>
       </c>
       <c r="N36" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="T36" s="1" t="n">
-        <v>3</v>
+      <c r="O36" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="R36" s="4" t="s">
+        <v>200</v>
       </c>
       <c r="V36" s="1" t="n">
         <v>1</v>
@@ -3842,24 +3836,27 @@
       <c r="X36" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="Y36" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z36" s="5" t="n">
+      <c r="Y36" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z36" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>50</v>
@@ -3868,11 +3865,8 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I37" s="4" t="s">
-        <v>203</v>
-      </c>
       <c r="J37" s="4" t="s">
-        <v>204</v>
+        <v>162</v>
       </c>
       <c r="L37" s="1" t="n">
         <v>160</v>
@@ -3906,29 +3900,26 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>205</v>
+        <v>2</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="H38" s="5" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="I38" s="4" t="s">
+        <v>204</v>
+      </c>
       <c r="J38" s="4" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>160</v>
@@ -3939,9 +3930,6 @@
       <c r="N38" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="R38" s="4" t="s">
-        <v>206</v>
-      </c>
       <c r="T38" s="1" t="n">
         <v>3</v>
       </c>
@@ -3965,16 +3953,19 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>35</v>
+        <v>203</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>50</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>161</v>
@@ -3987,19 +3978,22 @@
         <v>162</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>64</v>
+        <v>160</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="O39" s="4" t="s">
-        <v>209</v>
+        <v>96</v>
+      </c>
+      <c r="N39" s="4" t="s">
+        <v>159</v>
       </c>
       <c r="R39" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="V39" s="4" t="s">
-        <v>50</v>
+        <v>206</v>
+      </c>
+      <c r="T39" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V39" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="W39" s="4" t="s">
         <v>160</v>
@@ -4021,10 +4015,10 @@
         <v>207</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>35</v>
@@ -4033,23 +4027,23 @@
         <v>161</v>
       </c>
       <c r="H40" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>162</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="R40" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="V40" s="4" t="s">
         <v>50</v>
@@ -4074,20 +4068,23 @@
         <v>207</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H41" s="5"/>
-      <c r="I41" s="1" t="s">
-        <v>215</v>
+      <c r="G41" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>204</v>
+        <v>162</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>160</v>
@@ -4095,11 +4092,12 @@
       <c r="M41" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="O41" s="4"/>
-      <c r="P41" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="R41" s="4"/>
+      <c r="O41" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="R41" s="4" t="s">
+        <v>213</v>
+      </c>
       <c r="V41" s="4" t="s">
         <v>50</v>
       </c>
@@ -4114,6 +4112,55 @@
         <v>1</v>
       </c>
       <c r="Z41" s="5" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H42" s="5"/>
+      <c r="I42" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="L42" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="M42" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="O42" s="4"/>
+      <c r="P42" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="R42" s="4"/>
+      <c r="V42" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="W42" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="X42" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y42" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z42" s="5" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4383,13 +4430,13 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>226</v>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -3552,7 +3552,7 @@
         <v>180</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>189</v>
@@ -3909,7 +3909,7 @@
         <v>203</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H38" s="5" t="n">
         <f aca="false">FALSE()</f>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="231">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -596,6 +596,9 @@
     <t xml:space="preserve">192</t>
   </si>
   <si>
+    <t xml:space="preserve">all</t>
+  </si>
+  <si>
     <t xml:space="preserve">rbd</t>
   </si>
   <si>
@@ -641,7 +644,7 @@
     <t xml:space="preserve">kits23</t>
   </si>
   <si>
-    <t xml:space="preserve">abdomen, pelvis</t>
+    <t xml:space="preserve">abdomen</t>
   </si>
   <si>
     <t xml:space="preserve">all labels, abdomen lbd</t>
@@ -672,9 +675,6 @@
   </si>
   <si>
     <t xml:space="preserve">totalseg_short</t>
-  </si>
-  <si>
-    <t xml:space="preserve">all</t>
   </si>
   <si>
     <t xml:space="preserve">[ResNet3D]</t>
@@ -3554,8 +3554,11 @@
       <c r="E31" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="I31" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="J31" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>188</v>
@@ -3589,19 +3592,19 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>157</v>
@@ -3629,13 +3632,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>50</v>
@@ -3660,7 +3663,7 @@
         <v>159</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="V33" s="4" t="s">
         <v>50</v>
@@ -3682,13 +3685,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B34" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>50</v>
@@ -3713,7 +3716,7 @@
         <v>159</v>
       </c>
       <c r="R34" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="V34" s="4" t="s">
         <v>50</v>
@@ -3735,19 +3738,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>50</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H35" s="6" t="b">
         <f aca="false">FALSE()</f>
@@ -3766,10 +3769,10 @@
         <v>159</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="R35" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="V35" s="1" t="n">
         <v>1</v>
@@ -3791,19 +3794,19 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B36" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>100</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H36" s="6" t="b">
         <f aca="false">FALSE()</f>
@@ -3822,10 +3825,10 @@
         <v>159</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="R36" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="V36" s="1" t="n">
         <v>1</v>
@@ -3847,16 +3850,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>50</v>
@@ -3900,13 +3903,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B38" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>0</v>
@@ -3916,10 +3919,10 @@
         <v>0</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>160</v>
@@ -3953,16 +3956,16 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B39" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>50</v>
@@ -3987,7 +3990,7 @@
         <v>159</v>
       </c>
       <c r="R39" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="T39" s="1" t="n">
         <v>3</v>
@@ -4012,13 +4015,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B40" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>35</v>
@@ -4040,10 +4043,10 @@
         <v>64</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="R40" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="V40" s="4" t="s">
         <v>50</v>
@@ -4065,13 +4068,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B41" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>35</v>
@@ -4093,10 +4096,10 @@
         <v>96</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="R41" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="V41" s="4" t="s">
         <v>50</v>
@@ -4118,23 +4121,23 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B42" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="1" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>160</v>
@@ -4430,13 +4433,13 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>226</v>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="231">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -581,6 +581,9 @@
     <t xml:space="preserve">TSL.label_full:TSL.label_region</t>
   </si>
   <si>
+    <t xml:space="preserve">TSL.label_full:TSL.label_minimal</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.5, 1.5,1.5</t>
   </si>
   <si>
@@ -588,9 +591,6 @@
   </si>
   <si>
     <t xml:space="preserve">1,1,1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSL.label_full:TSL.label_minimal</t>
   </si>
   <si>
     <t xml:space="preserve">192</t>
@@ -823,7 +823,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -848,12 +848,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2105,2065 +2113,2071 @@
   <dimension ref="A1:AH42"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="40.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="13.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="21.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="21.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="27.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="29.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="24.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="22.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="15.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="13.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="13.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="22.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="26" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="6.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="38.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="9.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="6" width="40.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="6" width="24.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="15.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="6" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="6" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="6" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="6" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="6" width="13.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="6" width="21.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="6" width="21.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="6" width="27.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="6" width="29.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="6" width="24.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="6" width="22.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="6" width="15.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="6" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="6" width="13.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="6" width="13.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="6" width="22.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="26" style="6" width="8.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="35" style="6" width="10.17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="X1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y1" s="1" t="s">
+      <c r="X1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AD1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="6" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="X2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Y2" s="6" t="b">
+      <c r="Y2" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z2" s="6" t="b">
+      <c r="Z2" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="V3" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="W3" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="X3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Y3" s="6" t="b">
+      <c r="Y3" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z3" s="6" t="b">
+      <c r="Z3" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="1" t="s">
+      <c r="E4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="N4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="W4" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="X4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Y4" s="6" t="b">
+      <c r="Y4" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z4" s="6" t="b">
+      <c r="Z4" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="L5" s="1" t="n">
+      <c r="L5" s="6" t="n">
         <v>192</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="M5" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="V5" s="1" t="s">
+      <c r="V5" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="W5" s="1" t="s">
+      <c r="W5" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="X5" s="1" t="s">
+      <c r="X5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Y5" s="6" t="b">
+      <c r="Y5" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z5" s="6" t="b">
+      <c r="Z5" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="M6" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="N6" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="R6" s="1" t="s">
+      <c r="R6" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="V6" s="1" t="n">
+      <c r="V6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="W6" s="1" t="s">
+      <c r="W6" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="X6" s="1" t="s">
+      <c r="X6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Y6" s="6" t="b">
+      <c r="Y6" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z6" s="6" t="b">
+      <c r="Z6" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="L7" s="6" t="n">
         <v>192</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="N7" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="R7" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="V7" s="1" t="n">
+      <c r="V7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="W7" s="1" t="s">
+      <c r="W7" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="X7" s="1" t="s">
+      <c r="X7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Y7" s="6" t="b">
+      <c r="Y7" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z7" s="6" t="b">
+      <c r="Z7" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="L8" s="1" t="n">
+      <c r="L8" s="6" t="n">
         <v>192</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="N8" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="R8" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="V8" s="1" t="n">
+      <c r="V8" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="W8" s="1" t="s">
+      <c r="W8" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="X8" s="1" t="s">
+      <c r="X8" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Y8" s="6" t="b">
+      <c r="Y8" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z8" s="6" t="b">
+      <c r="Z8" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="B9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M9" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="1" t="s">
+      <c r="V9" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="W9" s="1" t="s">
+      <c r="W9" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="Y9" s="6" t="b">
+      <c r="Y9" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z9" s="6" t="b">
+      <c r="Z9" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="L10" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="M10" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="V10" s="1" t="s">
+      <c r="V10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="W10" s="1" t="s">
+      <c r="W10" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="Y10" s="6" t="b">
+      <c r="Y10" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z10" s="6" t="b">
+      <c r="Z10" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="L11" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="M11" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="V11" s="1" t="s">
+      <c r="V11" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="W11" s="1" t="s">
+      <c r="W11" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="Y11" s="6" t="b">
+      <c r="Y11" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z11" s="6" t="b">
+      <c r="Z11" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="L12" s="1" t="n">
+      <c r="L12" s="6" t="n">
         <v>128</v>
       </c>
-      <c r="M12" s="1" t="n">
+      <c r="M12" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="N12" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="V12" s="1" t="s">
+      <c r="V12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="W12" s="1" t="s">
+      <c r="W12" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="Y12" s="6" t="b">
+      <c r="Y12" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z12" s="6" t="b">
+      <c r="Z12" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="L13" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="M13" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="V13" s="1" t="s">
+      <c r="V13" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="W13" s="1" t="s">
+      <c r="W13" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="Y13" s="6" t="b">
+      <c r="Y13" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z13" s="6" t="b">
+      <c r="Z13" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="L14" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="M14" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="V14" s="1" t="s">
+      <c r="V14" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="W14" s="1" t="s">
+      <c r="W14" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="Y14" s="6" t="b">
+      <c r="Y14" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z14" s="6" t="b">
+      <c r="Z14" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="L15" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="M15" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="V15" s="1" t="s">
+      <c r="V15" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="W15" s="1" t="s">
+      <c r="W15" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="Y15" s="6" t="b">
+      <c r="Y15" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z15" s="6" t="b">
+      <c r="Z15" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="E16" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="1" t="n">
+      <c r="K16" s="8"/>
+      <c r="L16" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="M16" s="1" t="n">
+      <c r="M16" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="W16" s="4" t="s">
+      <c r="W16" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="Y16" s="6" t="b">
+      <c r="Y16" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z16" s="6" t="b">
+      <c r="Z16" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="B17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="H17" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="s">
+      <c r="H17" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="L17" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="M17" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N17" s="4" t="s">
+      <c r="N17" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="R17" s="4" t="s">
+      <c r="R17" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="V17" s="4" t="s">
+      <c r="V17" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="W17" s="4" t="s">
+      <c r="W17" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="X17" s="4" t="s">
+      <c r="X17" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="Y17" s="6" t="b">
+      <c r="Y17" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z17" s="6" t="b">
+      <c r="Z17" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="H18" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="4" t="s">
+      <c r="H18" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="L18" s="4" t="s">
+      <c r="L18" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="M18" s="4" t="s">
+      <c r="M18" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N18" s="4" t="s">
+      <c r="N18" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="R18" s="4" t="s">
+      <c r="R18" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="V18" s="4" t="s">
+      <c r="V18" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="W18" s="4" t="s">
+      <c r="W18" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="X18" s="4" t="s">
+      <c r="X18" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="Y18" s="6" t="b">
+      <c r="Y18" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z18" s="6" t="b">
+      <c r="Z18" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="E19" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="H19" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="s">
+      <c r="H19" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="L19" s="4" t="s">
+      <c r="L19" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="M19" s="4" t="s">
+      <c r="M19" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N19" s="4" t="s">
+      <c r="N19" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="P19" s="4" t="s">
+      <c r="P19" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="R19" s="4" t="s">
+      <c r="R19" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="V19" s="4" t="s">
+      <c r="V19" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="W19" s="4" t="s">
+      <c r="W19" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="X19" s="4" t="s">
+      <c r="X19" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="Y19" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z19" s="6" t="b">
+      <c r="Y19" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="E20" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="H20" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="s">
+      <c r="H20" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="L20" s="4" t="s">
+      <c r="L20" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="M20" s="4" t="s">
+      <c r="M20" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N20" s="4" t="s">
+      <c r="N20" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="P20" s="4" t="s">
+      <c r="P20" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="R20" s="4" t="s">
+      <c r="R20" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="V20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W20" s="4" t="s">
+      <c r="V20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="X20" s="4" t="s">
+      <c r="X20" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="Y20" s="6" t="b">
+      <c r="Y20" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z20" s="6" t="b">
+      <c r="Z20" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="E21" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="H21" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="4" t="s">
+      <c r="H21" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="L21" s="4" t="s">
+      <c r="L21" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="M21" s="4" t="s">
+      <c r="M21" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N21" s="4" t="s">
+      <c r="N21" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="P21" s="4" t="s">
+      <c r="P21" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="V21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W21" s="4" t="s">
+      <c r="V21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="X21" s="4" t="s">
+      <c r="X21" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="Y21" s="6" t="b">
+      <c r="Y21" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z21" s="6" t="b">
+      <c r="Z21" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="E22" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="H22" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="4" t="s">
+      <c r="H22" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K22" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="L22" s="4" t="s">
+      <c r="L22" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="M22" s="4" t="s">
+      <c r="M22" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N22" s="4" t="s">
+      <c r="N22" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="P22" s="4" t="s">
+      <c r="P22" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="V22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W22" s="4" t="s">
+      <c r="V22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="X22" s="4" t="s">
+      <c r="X22" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="Y22" s="6" t="b">
+      <c r="Y22" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z22" s="6" t="b">
+      <c r="Z22" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="4" t="s">
+      <c r="E23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="L23" s="4" t="s">
+      <c r="L23" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="M23" s="4" t="s">
+      <c r="M23" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N23" s="4" t="s">
+      <c r="N23" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="P23" s="4" t="s">
+      <c r="P23" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="V23" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W23" s="4" t="s">
+      <c r="V23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="X23" s="4" t="s">
+      <c r="X23" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="Y23" s="6" t="b">
+      <c r="Y23" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z23" s="6" t="b">
+      <c r="Z23" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="s">
+      <c r="E24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="L24" s="1" t="n">
+      <c r="L24" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="M24" s="4" t="s">
+      <c r="M24" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N24" s="4" t="s">
+      <c r="N24" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="P24" s="4" t="s">
+      <c r="P24" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="V24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W24" s="4" t="s">
+      <c r="V24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="X24" s="4" t="s">
+      <c r="X24" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="Y24" s="6" t="b">
+      <c r="Y24" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z24" s="6" t="b">
+      <c r="Z24" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B25" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="1" t="s">
+      <c r="B25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="L25" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="M25" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="W25" s="1" t="s">
+      <c r="W25" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="X25" s="1" t="s">
+      <c r="X25" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Y25" s="6" t="b">
+      <c r="Y25" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z25" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AH25" s="1" t="n">
+      <c r="Z25" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH25" s="6" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J26" s="1" t="s">
+      <c r="E26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="K26" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="L26" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="M26" s="1" t="s">
+      <c r="M26" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="Q26" s="1" t="s">
+      <c r="Q26" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="X26" s="1" t="s">
+      <c r="X26" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Y26" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z26" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AH26" s="1" t="n">
+      <c r="Y26" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH26" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J27" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q27" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="V27" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W27" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="X27" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y27" s="7" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z27" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH27" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="J28" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="L27" s="1" t="s">
+      <c r="L28" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="M28" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="V28" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W28" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="X28" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y28" s="7" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z28" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH28" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="M29" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="V27" s="1" t="s">
+      <c r="P29" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="V29" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="W27" s="1" t="s">
+      <c r="W29" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="X29" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y29" s="7" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z29" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH29" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="O30" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="X27" s="1" t="s">
+      <c r="V30" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W30" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="X30" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Y27" s="6" t="b">
+      <c r="Y30" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z30" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH30" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="O31" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="V31" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W31" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="X31" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y31" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z31" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="AH31" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="V32" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W32" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="X32" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y32" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z27" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AH27" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B28" s="1" t="n">
+      <c r="Z32" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H33" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="N33" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="R33" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="V33" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="W33" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="X33" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J28" s="1" t="s">
+      <c r="Y33" s="7" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z33" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H34" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="L28" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="M28" s="1" t="s">
+      <c r="L34" s="6" t="n">
+        <v>192</v>
+      </c>
+      <c r="M34" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="V28" s="1" t="s">
+      <c r="N34" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="R34" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="V34" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="W28" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="X28" s="1" t="s">
+      <c r="W34" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="X34" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="Y28" s="6" t="b">
+      <c r="Y34" s="7" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z28" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AH28" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B29" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J29" s="1" t="s">
+      <c r="Z34" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H35" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="L29" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="M29" s="1" t="s">
+      <c r="L35" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="M35" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="P29" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="V29" s="1" t="s">
+      <c r="N35" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="R35" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="V35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="X35" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y35" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z35" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H36" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="L36" s="6" t="n">
+        <v>192</v>
+      </c>
+      <c r="M36" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="N36" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="O36" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="R36" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="V36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="X36" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y36" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="Z36" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E37" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="W29" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="X29" s="1" t="s">
+      <c r="H37" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="L37" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="M37" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="N37" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="T37" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="X37" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="Y29" s="6" t="b">
+      <c r="Y37" s="6" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z29" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AH29" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="V30" s="1" t="s">
+      <c r="Z37" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="L38" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="M38" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="N38" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="T38" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="X38" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y38" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z38" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E39" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="W30" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="X30" s="1" t="s">
+      <c r="G39" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="L39" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="M39" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="N39" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="R39" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="T39" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="X39" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="Y30" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z30" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AH30" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B31" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="I31" s="1" t="s">
+      <c r="Y39" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z39" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="L40" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="M40" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="O40" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="R40" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="V40" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="W40" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="X40" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y40" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z40" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="L41" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="M41" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="O41" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="R41" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="V41" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="W41" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="X41" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y41" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Z41" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J42" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="V31" s="1" t="s">
+      <c r="L42" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="O42" s="9"/>
+      <c r="P42" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="R42" s="9"/>
+      <c r="V42" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="W31" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="X31" s="1" t="s">
+      <c r="W42" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="X42" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="Y31" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z31" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="AH31" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="V32" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="W32" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="X32" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y32" s="6" t="b">
+      <c r="Y42" s="6" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="Z32" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H33" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="M33" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="N33" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="R33" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="V33" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="W33" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="X33" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y33" s="6" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z33" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H34" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="L34" s="1" t="n">
-        <v>192</v>
-      </c>
-      <c r="M34" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="N34" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="R34" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="V34" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="W34" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="X34" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y34" s="6" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z34" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="H35" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="L35" s="1" t="n">
-        <v>128</v>
-      </c>
-      <c r="M35" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="N35" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="O35" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="R35" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="V35" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W35" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="X35" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y35" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z35" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="H36" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="L36" s="1" t="n">
-        <v>192</v>
-      </c>
-      <c r="M36" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="N36" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="O36" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="R36" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="V36" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W36" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="X36" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y36" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="Z36" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="L37" s="1" t="n">
-        <v>160</v>
-      </c>
-      <c r="M37" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="N37" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="T37" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="V37" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W37" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="X37" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y37" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z37" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B38" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="L38" s="1" t="n">
-        <v>160</v>
-      </c>
-      <c r="M38" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="N38" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="T38" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="V38" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W38" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="X38" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y38" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z38" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B39" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E39" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="L39" s="1" t="n">
-        <v>160</v>
-      </c>
-      <c r="M39" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="N39" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="R39" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="T39" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="V39" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W39" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="X39" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y39" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z39" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B40" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="L40" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="M40" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="O40" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="R40" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="V40" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="W40" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="X40" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y40" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z40" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B41" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="L41" s="1" t="n">
-        <v>160</v>
-      </c>
-      <c r="M41" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="O41" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="R41" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="V41" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="W41" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="X41" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y41" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z41" s="5" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B42" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H42" s="5"/>
-      <c r="I42" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="L42" s="1" t="n">
-        <v>160</v>
-      </c>
-      <c r="M42" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="O42" s="4"/>
-      <c r="P42" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="R42" s="4"/>
-      <c r="V42" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="W42" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="X42" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y42" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="Z42" s="5" t="n">
+      <c r="Z42" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="model_params" sheetId="1" state="visible" r:id="rId3"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="230">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -258,9 +258,6 @@
   </si>
   <si>
     <t xml:space="preserve">[4,2,2,2,2,2]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fake_tumours</t>
   </si>
   <si>
     <t xml:space="preserve">random_sample</t>
@@ -1589,48 +1586,32 @@
         <v>77</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
+    </row>
+    <row r="1048568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1638,7 +1619,7 @@
     <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1673,13 +1654,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>4</v>
@@ -1690,114 +1671,114 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>0.1</v>
@@ -1808,53 +1789,53 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0</v>
@@ -1863,7 +1844,7 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>19</v>
@@ -1915,32 +1896,32 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>0</v>
@@ -1949,29 +1930,29 @@
         <v>35</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>0</v>
@@ -1982,19 +1963,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2033,12 +2014,12 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
@@ -2046,7 +2027,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>20</v>
@@ -2054,7 +2035,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -2065,18 +2046,18 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>0</v>
@@ -2087,7 +2068,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E7" s="5" t="n">
         <f aca="false">FALSE()</f>
@@ -2144,85 +2125,85 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="X1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>151</v>
-      </c>
-      <c r="AB1" s="6" t="s">
-        <v>152</v>
       </c>
       <c r="AC1" s="6" t="s">
         <v>4</v>
@@ -2240,39 +2221,39 @@
         <v>5</v>
       </c>
       <c r="AH1" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="B2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>35</v>
       </c>
       <c r="J2" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="V2" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W2" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X2" s="6" t="s">
         <v>4</v>
@@ -2288,43 +2269,43 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B3" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>35</v>
       </c>
       <c r="J3" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="R3" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="V3" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X3" s="6" t="s">
         <v>4</v>
@@ -2340,31 +2321,31 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>4</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L4" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M4" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="N4" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="W4" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="W4" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="X4" s="6" t="s">
         <v>4</v>
@@ -2380,34 +2361,34 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>35</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>192</v>
       </c>
       <c r="M5" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="N5" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="V5" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W5" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X5" s="6" t="s">
         <v>4</v>
@@ -2423,40 +2404,40 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>6</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>50</v>
       </c>
       <c r="G6" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="L6" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="R6" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="V6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="W6" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X6" s="6" t="s">
         <v>4</v>
@@ -2472,40 +2453,40 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>7</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>50</v>
       </c>
       <c r="G7" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>192</v>
       </c>
       <c r="M7" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="N7" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="N7" s="6" t="s">
-        <v>159</v>
-      </c>
       <c r="R7" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="V7" s="6" t="n">
         <v>2</v>
       </c>
       <c r="W7" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X7" s="6" t="s">
         <v>4</v>
@@ -2521,40 +2502,40 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B8" s="6" t="n">
         <v>8</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>75</v>
       </c>
       <c r="G8" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>192</v>
       </c>
       <c r="M8" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="N8" s="6" t="s">
-        <v>159</v>
-      </c>
       <c r="R8" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="V8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="W8" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X8" s="6" t="s">
         <v>4</v>
@@ -2570,34 +2551,34 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="E9" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>20</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L9" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M9" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="V9" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W9" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y9" s="7" t="b">
         <f aca="false">TRUE()</f>
@@ -2610,28 +2591,28 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J10" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="L10" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="M10" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="V10" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W10" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y10" s="7" t="b">
         <f aca="false">TRUE()</f>
@@ -2644,31 +2625,31 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B11" s="6" t="n">
         <v>4</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L11" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M11" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="V11" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W11" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y11" s="7" t="b">
         <f aca="false">TRUE()</f>
@@ -2681,19 +2662,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B12" s="6" t="n">
         <v>5</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J12" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="K12" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>170</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>128</v>
@@ -2702,13 +2683,13 @@
         <v>96</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="V12" s="6" t="s">
         <v>20</v>
       </c>
       <c r="W12" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y12" s="7" t="b">
         <f aca="false">TRUE()</f>
@@ -2721,31 +2702,31 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B13" s="6" t="n">
         <v>6</v>
       </c>
       <c r="D13" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>166</v>
-      </c>
       <c r="J13" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L13" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M13" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="V13" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W13" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y13" s="7" t="b">
         <f aca="false">TRUE()</f>
@@ -2758,31 +2739,31 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B14" s="6" t="n">
         <v>7</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L14" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M14" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="V14" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W14" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y14" s="7" t="b">
         <f aca="false">TRUE()</f>
@@ -2795,31 +2776,31 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B15" s="6" t="n">
         <v>9</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>35</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W15" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y15" s="7" t="b">
         <f aca="false">TRUE()</f>
@@ -2832,13 +2813,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B16" s="6" t="n">
         <v>12</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>40</v>
@@ -2847,7 +2828,7 @@
         <v>20</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K16" s="8"/>
       <c r="L16" s="6" t="n">
@@ -2857,7 +2838,7 @@
         <v>96</v>
       </c>
       <c r="W16" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y16" s="7" t="b">
         <f aca="false">TRUE()</f>
@@ -2870,44 +2851,44 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>35</v>
       </c>
       <c r="G17" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H17" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="H17" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>162</v>
-      </c>
       <c r="L17" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="M17" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="M17" s="9" t="s">
+      <c r="N17" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N17" s="9" t="s">
-        <v>159</v>
-      </c>
       <c r="R17" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="V17" s="9" t="s">
         <v>50</v>
       </c>
       <c r="W17" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X17" s="9" t="s">
         <v>4</v>
@@ -2923,44 +2904,44 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B18" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>50</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H18" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="H18" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>162</v>
-      </c>
       <c r="L18" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="M18" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="M18" s="9" t="s">
+      <c r="N18" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N18" s="9" t="s">
-        <v>159</v>
-      </c>
       <c r="R18" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="V18" s="9" t="s">
         <v>50</v>
       </c>
       <c r="W18" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X18" s="9" t="s">
         <v>4</v>
@@ -2976,47 +2957,47 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B19" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>50</v>
       </c>
       <c r="G19" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H19" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="H19" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>162</v>
-      </c>
       <c r="L19" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="M19" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="M19" s="9" t="s">
+      <c r="N19" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N19" s="9" t="s">
-        <v>159</v>
-      </c>
       <c r="P19" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="R19" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="V19" s="9" t="s">
         <v>50</v>
       </c>
       <c r="W19" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X19" s="9" t="s">
         <v>4</v>
@@ -3032,47 +3013,47 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B20" s="6" t="n">
         <v>4</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>50</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H20" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="H20" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>162</v>
-      </c>
       <c r="L20" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="M20" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="M20" s="9" t="s">
+      <c r="N20" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N20" s="9" t="s">
+      <c r="P20" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="R20" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="V20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="P20" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="R20" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="V20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W20" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="X20" s="9" t="s">
         <v>4</v>
@@ -3088,13 +3069,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B21" s="6" t="n">
         <v>5</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>50</v>
@@ -3104,25 +3085,25 @@
         <v>0</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L21" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="M21" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="M21" s="9" t="s">
+      <c r="N21" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N21" s="9" t="s">
+      <c r="P21" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="V21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="V21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W21" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="X21" s="9" t="s">
         <v>4</v>
@@ -3138,13 +3119,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B22" s="6" t="n">
         <v>6</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>20</v>
@@ -3154,28 +3135,28 @@
         <v>0</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L22" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="M22" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="M22" s="9" t="s">
+      <c r="N22" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N22" s="9" t="s">
+      <c r="P22" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="V22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="P22" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="V22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W22" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="X22" s="9" t="s">
         <v>4</v>
@@ -3191,13 +3172,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B23" s="6" t="n">
         <v>7</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>0</v>
@@ -3207,25 +3188,25 @@
         <v>0</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L23" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="M23" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="M23" s="9" t="s">
+      <c r="N23" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N23" s="9" t="s">
+      <c r="P23" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="V23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="P23" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="V23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W23" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="X23" s="9" t="s">
         <v>4</v>
@@ -3241,13 +3222,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B24" s="6" t="n">
         <v>8</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>0</v>
@@ -3257,25 +3238,25 @@
         <v>0</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>96</v>
       </c>
       <c r="M24" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="N24" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N24" s="9" t="s">
-        <v>159</v>
-      </c>
       <c r="P24" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="V24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" s="9" t="s">
         <v>178</v>
-      </c>
-      <c r="V24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W24" s="9" t="s">
-        <v>179</v>
       </c>
       <c r="X24" s="9" t="s">
         <v>4</v>
@@ -3291,28 +3272,28 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>35</v>
       </c>
       <c r="J25" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="L25" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="L25" s="6" t="s">
+      <c r="M25" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="M25" s="6" t="s">
-        <v>158</v>
-      </c>
       <c r="W25" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X25" s="6" t="s">
         <v>4</v>
@@ -3331,31 +3312,31 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B26" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="E26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="6" t="s">
+      <c r="K26" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="K26" s="6" t="s">
+      <c r="L26" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q26" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q26" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="X26" s="6" t="s">
         <v>4</v>
@@ -3374,22 +3355,22 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B27" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>35</v>
       </c>
       <c r="J27" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="K27" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>128</v>
@@ -3398,13 +3379,13 @@
         <v>128</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="V27" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W27" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="X27" s="6" t="s">
         <v>4</v>
@@ -3423,31 +3404,31 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B28" s="6" t="n">
         <v>4</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L28" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M28" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="M28" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="V28" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W28" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="X28" s="6" t="s">
         <v>4</v>
@@ -3466,34 +3447,34 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B29" s="6" t="n">
         <v>5</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L29" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M29" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="M29" s="6" t="s">
-        <v>158</v>
-      </c>
       <c r="P29" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="V29" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W29" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="X29" s="6" t="s">
         <v>4</v>
@@ -3512,34 +3493,34 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B30" s="6" t="n">
         <v>6</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="V30" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W30" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="X30" s="6" t="s">
         <v>4</v>
@@ -3558,37 +3539,37 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B31" s="6" t="n">
         <v>7</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>10</v>
       </c>
       <c r="I31" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="J31" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="J31" s="6" t="s">
-        <v>190</v>
-      </c>
       <c r="L31" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="V31" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W31" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="X31" s="6" t="s">
         <v>4</v>
@@ -3607,31 +3588,31 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>20</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L32" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M32" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="M32" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="V32" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W32" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="X32" s="6" t="s">
         <v>4</v>
@@ -3647,44 +3628,44 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>50</v>
       </c>
       <c r="G33" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H33" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="H33" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>162</v>
-      </c>
       <c r="L33" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="M33" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="M33" s="9" t="s">
+      <c r="N33" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N33" s="9" t="s">
-        <v>159</v>
-      </c>
       <c r="R33" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="V33" s="9" t="s">
         <v>50</v>
       </c>
       <c r="W33" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X33" s="9" t="s">
         <v>4</v>
@@ -3700,44 +3681,44 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B34" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>50</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H34" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="H34" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>192</v>
       </c>
       <c r="M34" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="N34" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N34" s="9" t="s">
-        <v>159</v>
-      </c>
       <c r="R34" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="V34" s="9" t="s">
         <v>50</v>
       </c>
       <c r="W34" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X34" s="9" t="s">
         <v>4</v>
@@ -3753,47 +3734,47 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="B35" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>50</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H35" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L35" s="6" t="n">
         <v>128</v>
       </c>
       <c r="M35" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="N35" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N35" s="9" t="s">
+      <c r="O35" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="R35" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="V35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="O35" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="R35" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="V35" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W35" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="X35" s="9" t="s">
         <v>4</v>
@@ -3809,47 +3790,47 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B36" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>100</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H36" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>192</v>
       </c>
       <c r="M36" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="N36" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N36" s="9" t="s">
+      <c r="O36" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="R36" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="V36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="O36" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="R36" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="V36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W36" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="X36" s="9" t="s">
         <v>4</v>
@@ -3865,16 +3846,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="B37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="6" t="s">
+      <c r="D37" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>50</v>
@@ -3884,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>160</v>
@@ -3893,7 +3874,7 @@
         <v>96</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="T37" s="6" t="n">
         <v>3</v>
@@ -3902,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="W37" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X37" s="9" t="s">
         <v>4</v>
@@ -3918,26 +3899,26 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B38" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D38" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I38" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="E38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>205</v>
-      </c>
       <c r="J38" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>160</v>
@@ -3946,7 +3927,7 @@
         <v>96</v>
       </c>
       <c r="N38" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="T38" s="6" t="n">
         <v>3</v>
@@ -3955,7 +3936,7 @@
         <v>1</v>
       </c>
       <c r="W38" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X38" s="9" t="s">
         <v>4</v>
@@ -3971,29 +3952,29 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B39" s="6" t="n">
         <v>9</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>50</v>
       </c>
       <c r="G39" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="H39" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>160</v>
@@ -4002,10 +3983,10 @@
         <v>96</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="R39" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T39" s="6" t="n">
         <v>3</v>
@@ -4014,7 +3995,7 @@
         <v>1</v>
       </c>
       <c r="W39" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X39" s="9" t="s">
         <v>4</v>
@@ -4030,26 +4011,26 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="B40" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>35</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="H40" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J40" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="L40" s="6" t="n">
         <v>64</v>
@@ -4058,16 +4039,16 @@
         <v>64</v>
       </c>
       <c r="O40" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="R40" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="R40" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="V40" s="9" t="s">
         <v>50</v>
       </c>
       <c r="W40" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X40" s="9" t="s">
         <v>4</v>
@@ -4083,26 +4064,26 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B41" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>35</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H41" s="6" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L41" s="6" t="n">
         <v>160</v>
@@ -4111,16 +4092,16 @@
         <v>96</v>
       </c>
       <c r="O41" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="R41" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="R41" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="V41" s="9" t="s">
         <v>50</v>
       </c>
       <c r="W41" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X41" s="9" t="s">
         <v>4</v>
@@ -4136,22 +4117,22 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B42" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>35</v>
       </c>
       <c r="I42" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="J42" s="9" t="s">
         <v>189</v>
-      </c>
-      <c r="J42" s="9" t="s">
-        <v>190</v>
       </c>
       <c r="L42" s="6" t="n">
         <v>160</v>
@@ -4161,14 +4142,14 @@
       </c>
       <c r="O42" s="9"/>
       <c r="P42" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="R42" s="9"/>
       <c r="V42" s="9" t="s">
         <v>50</v>
       </c>
       <c r="W42" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X42" s="9" t="s">
         <v>4</v>
@@ -4230,7 +4211,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>12</v>
@@ -4239,15 +4220,15 @@
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>219</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>12</v>
@@ -4261,7 +4242,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -4272,7 +4253,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>19</v>
@@ -4346,85 +4327,85 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="F1" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>4</v>
@@ -4442,27 +4423,27 @@
         <v>5</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="L2" s="1" t="n">
         <v>64</v>
@@ -4474,10 +4455,10 @@
         <v>0</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -3600,7 +3600,7 @@
         <v>179</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>155</v>

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -650,7 +650,7 @@
     <t xml:space="preserve">all labels, abdomen lbd</t>
   </si>
   <si>
-    <t xml:space="preserve">TSL.label_region:TSL.abdomen</t>
+    <t xml:space="preserve">TSL.label_minimal:TSL.kidneys </t>
   </si>
   <si>
     <t xml:space="preserve">test</t>
@@ -2103,7 +2103,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="38.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="9.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="6" width="40.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="6" width="55.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="6" width="24.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="15.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="6" width="8.67"/>
@@ -3630,7 +3630,7 @@
       <c r="V32" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="W32" s="0" t="s">
+      <c r="W32" s="1" t="s">
         <v>186</v>
       </c>
       <c r="X32" s="6" t="s">

--- a/configurations/experiment_configs.xlsx
+++ b/configurations/experiment_configs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="232">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -543,6 +543,9 @@
   </si>
   <si>
     <t xml:space="preserve">224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lits,litq,litqsmall</t>
   </si>
   <si>
     <t xml:space="preserve">lungs</t>
@@ -2822,7 +2825,7 @@
         <v>12</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>40</v>
@@ -2854,13 +2857,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>35</v>
@@ -2885,7 +2888,7 @@
         <v>158</v>
       </c>
       <c r="R17" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="V17" s="9" t="s">
         <v>50</v>
@@ -2907,13 +2910,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B18" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>50</v>
@@ -2938,7 +2941,7 @@
         <v>158</v>
       </c>
       <c r="R18" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="V18" s="9" t="s">
         <v>50</v>
@@ -2960,13 +2963,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B19" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>50</v>
@@ -2991,10 +2994,10 @@
         <v>158</v>
       </c>
       <c r="P19" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="R19" s="9" t="s">
         <v>175</v>
-      </c>
-      <c r="R19" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="V19" s="9" t="s">
         <v>50</v>
@@ -3016,13 +3019,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B20" s="6" t="n">
         <v>4</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>50</v>
@@ -3047,10 +3050,10 @@
         <v>158</v>
       </c>
       <c r="P20" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="R20" s="9" t="s">
         <v>175</v>
-      </c>
-      <c r="R20" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="V20" s="6" t="n">
         <v>1</v>
@@ -3072,13 +3075,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B21" s="6" t="n">
         <v>5</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>50</v>
@@ -3100,7 +3103,7 @@
         <v>158</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="V21" s="6" t="n">
         <v>1</v>
@@ -3122,13 +3125,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B22" s="6" t="n">
         <v>6</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>20</v>
@@ -3141,7 +3144,7 @@
         <v>168</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L22" s="9" t="s">
         <v>156</v>
@@ -3153,7 +3156,7 @@
         <v>158</v>
       </c>
       <c r="P22" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="V22" s="6" t="n">
         <v>1</v>
@@ -3175,13 +3178,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B23" s="6" t="n">
         <v>7</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>0</v>
@@ -3203,7 +3206,7 @@
         <v>158</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="V23" s="6" t="n">
         <v>1</v>
@@ -3225,13 +3228,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B24" s="6" t="n">
         <v>8</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>0</v>
@@ -3253,13 +3256,13 @@
         <v>158</v>
       </c>
       <c r="P24" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="V24" s="6" t="n">
         <v>1</v>
       </c>
       <c r="W24" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="X24" s="9" t="s">
         <v>4</v>
@@ -3275,13 +3278,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>35</v>
@@ -3315,22 +3318,22 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B26" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>157</v>
@@ -3339,7 +3342,7 @@
         <v>157</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="X26" s="6" t="s">
         <v>4</v>
@@ -3358,22 +3361,22 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B27" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>35</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>128</v>
@@ -3382,13 +3385,13 @@
         <v>128</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="V27" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W27" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="X27" s="6" t="s">
         <v>4</v>
@@ -3407,16 +3410,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B28" s="6" t="n">
         <v>4</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>161</v>
@@ -3431,7 +3434,7 @@
         <v>50</v>
       </c>
       <c r="W28" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="X28" s="6" t="s">
         <v>4</v>
@@ -3450,16 +3453,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B29" s="6" t="n">
         <v>5</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J29" s="6" t="s">
         <v>161</v>
@@ -3471,13 +3474,13 @@
         <v>157</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="V29" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W29" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="X29" s="6" t="s">
         <v>4</v>
@@ -3496,34 +3499,34 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B30" s="6" t="n">
         <v>6</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>155</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>157</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="V30" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W30" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="X30" s="6" t="s">
         <v>4</v>
@@ -3542,37 +3545,37 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B31" s="6" t="n">
         <v>7</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>10</v>
       </c>
       <c r="I31" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="L31" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>157</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="V31" s="6" t="s">
         <v>50</v>
       </c>
       <c r="W31" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="X31" s="6" t="s">
         <v>4</v>
@@ -3591,14 +3594,14 @@
     </row>
     <row r="32" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B32" s="6" t="n">
         <v>8</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>0</v>
@@ -3612,14 +3615,14 @@
       </c>
       <c r="K32" s="6"/>
       <c r="L32" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>157</v>
       </c>
       <c r="N32" s="6"/>
       <c r="O32" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P32" s="6"/>
       <c r="Q32" s="6"/>
@@ -3631,7 +3634,7 @@
         <v>50</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="X32" s="6" t="s">
         <v>4</v>
@@ -3657,19 +3660,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>20</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L33" s="6" t="s">
         <v>156</v>
@@ -3681,7 +3684,7 @@
         <v>50</v>
       </c>
       <c r="W33" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="X33" s="6" t="s">
         <v>4</v>
@@ -3697,13 +3700,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B34" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>50</v>
@@ -3728,7 +3731,7 @@
         <v>158</v>
       </c>
       <c r="R34" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V34" s="9" t="s">
         <v>50</v>
@@ -3750,13 +3753,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B35" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>50</v>
@@ -3781,7 +3784,7 @@
         <v>158</v>
       </c>
       <c r="R35" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V35" s="9" t="s">
         <v>50</v>
@@ -3803,19 +3806,19 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>50</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H36" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -3834,10 +3837,10 @@
         <v>158</v>
       </c>
       <c r="O36" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="R36" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="V36" s="6" t="n">
         <v>1</v>
@@ -3859,19 +3862,19 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B37" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>100</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H37" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -3890,10 +3893,10 @@
         <v>158</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="R37" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="V37" s="6" t="n">
         <v>1</v>
@@ -3915,16 +3918,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B38" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>50</v>
@@ -3968,13 +3971,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B39" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>0</v>
@@ -3984,10 +3987,10 @@
         <v>0</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>160</v>
@@ -4021,16 +4024,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B40" s="6" t="n">
         <v>9</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E40" s="6" t="n">
         <v>50</v>
@@ -4055,7 +4058,7 @@
         <v>158</v>
       </c>
       <c r="R40" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="T40" s="6" t="n">
         <v>3</v>
@@ -4080,16 +4083,16 @@
     </row>
     <row r="41" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B41" s="6" t="n">
         <v>3</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>0</v>
@@ -4148,13 +4151,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>35</v>
@@ -4176,10 +4179,10 @@
         <v>64</v>
       </c>
       <c r="O42" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="R42" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="V42" s="9" t="s">
         <v>50</v>
@@ -4201,13 +4204,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B43" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>35</v>
@@ -4229,10 +4232,10 @@
         <v>96</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R43" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="V43" s="9" t="s">
         <v>50</v>
@@ -4254,22 +4257,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B44" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>35</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>160</v>
@@ -4279,7 +4282,7 @@
       </c>
       <c r="O44" s="9"/>
       <c r="P44" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="R44" s="9"/>
       <c r="V44" s="9" t="s">
@@ -4348,7 +4351,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>12</v>
@@ -4357,15 +4360,15 @@
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>12</v>
@@ -4379,7 +4382,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -4390,7 +4393,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>19</v>
@@ -4479,13 +4482,13 @@
         <v>130</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>132</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>133</v>
@@ -4512,7 +4515,7 @@
         <v>145</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>142</v>
@@ -4521,7 +4524,7 @@
         <v>143</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>146</v>
@@ -4565,22 +4568,22 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L2" s="1" t="n">
         <v>64</v>
@@ -4592,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
